--- a/v3/outputs/FINAL_decision.xlsx
+++ b/v3/outputs/FINAL_decision.xlsx
@@ -36,7 +36,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -80,6 +80,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
@@ -107,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -136,10 +141,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -706,20 +714,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -740,40 +749,45 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>n_cells_in_anchor</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>cell_type_marker_genes</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>exclusion_markers</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>recommended_GPCR_panel</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>recommended_drugs_per_gene</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>n_genes_recommended</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>evidence_tier_per_gene</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>what_to_do</t>
         </is>
@@ -795,38 +809,43 @@
           <t>061 STR D1 Gaba</t>
         </is>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="n">
         <v>16660</v>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Drd1, Isl1, Pdyn, Tac1</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>Adora2a, Drd2, Penk</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>Drd1, Grm1, Htr1b, Chrm4, Cnr1</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>Drd1: Apomorphine (FDA) | Grm1: JNJ-16259685 (research) | Htr1b: Sumatriptan (FDA 1992) | Chrm4: Xanomeline (Cobenfy/KarXT) (FDA 2024) | Cnr1: Dronabinol (Marinol; THC) (FDA 1985)</t>
         </is>
       </c>
-      <c r="I2" s="8" t="n">
+      <c r="J2" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>Drd1=paper+allen_keep; Grm1=paper+allen_keep; Htr1b=paper+allen_keep; Chrm4=paper+allen_keep; Cnr1=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
@@ -848,38 +867,43 @@
           <t>063 STR D1 Sema5a Gaba</t>
         </is>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>780</v>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Drd1, Isl1, Pdyn, Tac1</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Adora2a, Drd2, Penk</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Drd1, Gabbr1, Gpr88, Grm5</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Drd1: Apomorphine (FDA) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gpr88: RTI-13951-33 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="J3" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Drd1=paper+allen_broadly_detectable; Gabbr1=paper+allen_broadly_detectable; Gpr88=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
@@ -901,38 +925,43 @@
           <t>062 STR D2 Gaba</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>18139</v>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Adora2a, Drd2, Gpr52, Gpr6, Penk, Sp9</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Drd1, Tac1</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Grm5, Gpr88, Drd2, Adora2a, Gpr6</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Grm5: Mavoglurant (AFQ056) (clinical-trial) | Gpr88: RTI-13951-33 (research) | Drd2: Risperidone (FDA 1993) | Adora2a: Istradefylline (Nourianz) (FDA 2019) | Gpr6: CVN424 (Cerevance) (clinical-trial)</t>
         </is>
       </c>
-      <c r="I4" s="8" t="n">
+      <c r="J4" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Grm5=paper+allen_keep; Gpr88=paper+allen_keep; Drd2=paper+allen_keep; Adora2a=paper+allen_keep; Gpr6=paper+allen_keep</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
@@ -946,46 +975,51 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Cholinergic interneuron</t>
+          <t>Patch/striosome SPN</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>058 PAL-STR Gaba-Chol</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Chat, Lhx8, Slc18a3, Slc5a7</t>
-        </is>
+          <t>061 STR D1 Gaba</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>16660</v>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Drd1, Drd2</t>
+          <t>Drd1, Foxp2, Mor1, Nnat, Oprm1, Pdyn, Tac1</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Gabbr1, Chrm2, Oprm1, Tacr3, Oprd1</t>
+          <t>Adora2a, Calb1, Drd2</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Chrm2: Donepezil (Aricept) (FDA 1996) | Oprm1: Morphine (FDA) | Tacr3: Fezolinetant (Veozah) (FDA 2023) | Oprd1: SNC80 (research)</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="n">
+          <t>Drd1, Grm1, Htr1b, Chrm4, Cnr1</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Drd1: Apomorphine (FDA) | Grm1: JNJ-16259685 (research) | Htr1b: Sumatriptan (FDA 1992) | Chrm4: Xanomeline (Cobenfy/KarXT) (FDA 2024) | Cnr1: Dronabinol (Marinol; THC) (FDA 1985)</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Gabbr1=paper+allen_keep; Chrm2=paper+allen_keep; Oprm1=paper+allen_keep; Tacr3=allen_only_keep; Oprd1=allen_only_keep</t>
-        </is>
-      </c>
       <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>Drd1=allen_only_keep; Grm1=allen_only_keep; Htr1b=allen_only_keep; Chrm4=allen_only_keep; Cnr1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
@@ -994,210 +1028,230 @@
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>BMAp</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Posterior BMA glutamatergic VGLUT1-like</t>
+          <t>Patch/striosome SPN</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>012 MEA Slc17a7 Glut</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>3984</v>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>C1ql2, Cartpt, Dcn, Gpr101, Meis2, Slc17a7</t>
-        </is>
+          <t>063 STR D1 Sema5a Gaba</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>780</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Gad1, Gad2, Slc32a1</t>
+          <t>Drd1, Foxp2, Mor1, Nnat, Oprm1, Pdyn, Tac1</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Gabbr1, Gabbr2, Grm5, Npy2r</t>
+          <t>Adora2a, Calb1, Drd2</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Npy2r: BIIE0246 (research)</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="n">
+          <t>Drd1, Gabbr1, Gpr88, Grm5</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Drd1: Apomorphine (FDA) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gpr88: RTI-13951-33 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable; Npy2r=allen_only_broadly_detectable</t>
-        </is>
-      </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
+          <t>Drd1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gpr88=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>BMAp</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Posterior BMA glutamatergic VGLUT1-like</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>113 MEA-COA-BMA Ccdc42 Glut</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>9654</v>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>C1ql2, Cartpt, Dcn, Gpr101, Meis2, Slc17a7</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Gad1, Gad2, Slc32a1</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1, Gabbr2, Grm5, Oprm1</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Oprm1: Morphine (FDA)</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable; Oprm1=paper+allen_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Matrix/exopatch SPN</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>061 STR D1 Gaba</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>16660</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Calb1, Drd1, Mef2c, Tac1</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Adora2a, Foxp2, Pdyn</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Drd1, Grm1, Htr1b, Chrm4, Cnr1</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Drd1: Apomorphine (FDA) | Grm1: JNJ-16259685 (research) | Htr1b: Sumatriptan (FDA 1992) | Chrm4: Xanomeline (Cobenfy/KarXT) (FDA 2024) | Cnr1: Dronabinol (Marinol; THC) (FDA 1985)</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>Drd1=allen_only_keep; Grm1=allen_only_keep; Htr1b=allen_only_keep; Chrm4=allen_only_keep; Cnr1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>RE</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Midline thalamic glutamatergic / reuniens</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>152 RE-Xi Nox4 Glut</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>5450</v>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>Gad1, Gad2</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1, Gabbr2, Grm1, Grm5</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Matrix/exopatch SPN</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>062 STR D2 Gaba</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>18139</v>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Calb1, Drd1, Mef2c, Tac1</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Adora2a, Foxp2, Pdyn</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Grm5, Gpr88, Drd2, Adora2a, Gpr6</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Grm5: Mavoglurant (AFQ056) (clinical-trial) | Gpr88: RTI-13951-33 (research) | Drd2: Risperidone (FDA 1993) | Adora2a: Istradefylline (Nourianz) (FDA 2019) | Gpr6: CVN424 (Cerevance) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>Grm5=allen_only_keep; Gpr88=allen_only_keep; Drd2=allen_only_keep; Adora2a=allen_only_keep; Gpr6=allen_only_keep</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Midline thalamic glutamatergic / reuniens</t>
+          <t>Cholinergic interneuron</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>149 PVT-PT Ntrk1 Glut</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>9854</v>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
-        </is>
+          <t>058 PAL-STR Gaba-Chol</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>30</v>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Gad1, Gad2</t>
+          <t>Chat, Lhx8, Slc18a3, Slc5a7</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Oprk1, Galr1, Oxtr, Cnr1, Oprm1</t>
+          <t>Drd1, Drd2</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Oprk1: Difelikefalin (Korsuva) (FDA 2021) | Galr1: M40 (galanin antagonist) (research) | Oxtr: Carbetocin (Pabal/Lonactene) (EU-only) | Cnr1: Dronabinol (Marinol; THC) (FDA 1985) | Oprm1: Morphine (FDA)</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="n">
+          <t>Gabbr1, Chrm2, Oprm1, Tacr3, Oprd1</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Chrm2: Donepezil (Aricept) (FDA 1996) | Oprm1: Morphine (FDA) | Tacr3: Fezolinetant (Veozah) (FDA 2023) | Oprd1: SNC80 (research)</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Oprk1=allen_only_keep; Galr1=allen_only_keep; Oxtr=allen_only_keep; Cnr1=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
-        </is>
-      </c>
       <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>Gabbr1=paper+allen_keep; Chrm2=paper+allen_keep; Oprm1=paper+allen_keep; Tacr3=allen_only_keep; Oprd1=allen_only_keep</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
@@ -1206,528 +1260,2608 @@
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>PV/SST/NPY interneurons</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>054 STR Prox1 Lhx6 Gaba</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>367</v>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Calb2, Lhx6, Nos1, Npy, Prox1, Pvalb, Sst</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Chat, Drd1, Drd2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Cnr1, Adcyap1r1, Gabbr1, Gabbr2, Grm1</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Cnr1: Dronabinol (Marinol; THC) (FDA 1985) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research)</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>Cnr1=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>PV/SST/NPY interneurons</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>056 Sst Chodl Gaba</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>230</v>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Calb2, Lhx6, Nos1, Npy, Prox1, Pvalb, Sst</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Chat, Drd1, Drd2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Tacr1, Npy2r, Galr1, Htr1a, Gpr101</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Tacr1: Aprepitant (Emend) (FDA 2003) | Npy2r: BIIE0246 (research) | Galr1: M40 (galanin antagonist) (research) | Htr1a: Buspirone (FDA 1986) | Gpr101: (no clinical drugs) (research)</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>Tacr1=allen_only_keep; Npy2r=allen_only_keep; Galr1=allen_only_keep; Htr1a=allen_only_keep; Gpr101=allen_only_keep</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Posterior BMA glutamatergic VGLUT1-like</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>012 MEA Slc17a7 Glut</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>3984</v>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>C1ql2, Cartpt, Dcn, Gpr101, Meis2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Slc17a6, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1, Gabbr2, Grm5, Npy2r</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Npy2r: BIIE0246 (research)</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable; Npy2r=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Posterior BMA glutamatergic VGLUT1-like</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>113 MEA-COA-BMA Ccdc42 Glut</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>9654</v>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>C1ql2, Cartpt, Dcn, Gpr101, Meis2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Slc17a6, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1, Gabbr2, Grm5, Oprm1</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Oprm1: Morphine (FDA)</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable; Oprm1=paper+allen_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>BMA/MEA VGLUT2-like excitatory</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>120 MEA Otp Foxp2 Glut</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>1504</v>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Foxp2, Otp, Slc17a6, Tac2, Zic2</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Gad1, Slc17a7, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1, Grm5, Htr2c, Oprm1</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Htr2c: Lorcaserin (Belviq) (FDA) | Oprm1: Morphine (FDA)</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Htr2c=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>BMA/MEA VGLUT2-like excitatory</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>121 MEA-BST Otp Zic2 Glut</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>1255</v>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Foxp2, Otp, Slc17a6, Tac2, Zic2</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Gad1, Slc17a7, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm5</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>BMA/MEA VGLUT2-like excitatory</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>119 SI-MA-LPO-LHA Skor1 Glut</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Foxp2, Otp, Slc17a6, Tac2, Zic2</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Gad1, Slc17a7, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1, Grm1, Grm5</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Amygdala GABA / striatal-like inhibitory neighbors</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>073 MEA-BST Sox6 Gaba</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>8705</v>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Ebf1, Gad1, Gad2, Lhx6, Slc32a1, Sox6, Sp9</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Meis2, Slc17a6, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm5</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>(counter-stain only; drugs not recommended)</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Amygdala GABA / striatal-like inhibitory neighbors</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>074 MEA-BST Lhx6 Sp9 Gaba</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Ebf1, Gad1, Gad2, Lhx6, Slc32a1, Sox6, Sp9</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Meis2, Slc17a6, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1, Grm5, Oprm1</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>(counter-stain only; drugs not recommended)</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Amygdala GABA / striatal-like inhibitory neighbors</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>082 CEA-BST Ebf1 Pdyn Gaba</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>6966</v>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Ebf1, Gad1, Gad2, Lhx6, Slc32a1, Sox6, Sp9</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Meis2, Slc17a6, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1, Gpr101, Grm5</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>(counter-stain only; drugs not recommended)</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1=allen_only_broadly_detectable; Gpr101=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
           <t>RE</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Midline thalamic glutamatergic / reuniens</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>152 RE-Xi Nox4 Glut</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>5450</v>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1, Gabbr2, Grm1, Grm5</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Midline thalamic glutamatergic / reuniens</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>149 PVT-PT Ntrk1 Glut</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>9854</v>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Oprk1, Galr1, Oxtr, Cnr1, Oprm1</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Oprk1: Difelikefalin (Korsuva) (FDA 2021) | Galr1: M40 (galanin antagonist) (research) | Oxtr: Carbetocin (Pabal/Lonactene) (EU-only) | Cnr1: Dronabinol (Marinol; THC) (FDA 1985) | Oprm1: Morphine (FDA)</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>Oprk1=allen_only_keep; Galr1=allen_only_keep; Oxtr=allen_only_keep; Cnr1=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Midline thalamic glutamatergic / reuniens</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>145 MH Tac2 Glut</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="n">
         <v>7972</v>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>Gad1, Gad2</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Gabbr1, Gabbr2, Sstr2, Tacr1</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Sstr2: Octreotide (FDA 1988) | Tacr1: Aprepitant (Emend) (FDA 2003)</t>
         </is>
       </c>
-      <c r="I10" s="8" t="n">
+      <c r="J22" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>Gabbr1=paper+allen_keep; Gabbr2=paper+allen_keep; Sstr2=paper+allen_keep; Tacr1=allen_only_keep</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="L22" s="8" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Reticular/inhibitory thalamic exclusion</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>093 RT-ZI Gnb3 Gaba</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>7452</v>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Gnb3, Otx2, Pvalb, Slc32a1</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Slc17a6, Slc17a7, Tcf7l2</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Chrm2</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>(counter-stain only; drugs not recommended)</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>Chrm2=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Reticular/inhibitory thalamic exclusion</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>109 LGv-ZI Otx2 Gaba</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>4380</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Gnb3, Otx2, Pvalb, Slc32a1</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Slc17a6, Slc17a7, Tcf7l2</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Grm5</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>(counter-stain only; drugs not recommended)</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>LM</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Lateral mammillary excitatory</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>144 MM Foxb1 Glut</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
         <v>8270</v>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>Foxb1, Lhx5, Pou4f1</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Slc32a1</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Gad1, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>Gabbr1, Gabbr2, Grm1</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research)</t>
         </is>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="J25" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="K25" s="9" t="inlineStr">
         <is>
           <t>Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>LM</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Lateral mammillary excitatory</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>143 MM-ant Foxb1 Glut</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="n">
         <v>5437</v>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>Foxb1, Lhx5, Pou4f1</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Slc32a1</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Gad1, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Htr2a, Gabbr1, Gabbr2, Grm1</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Htr2a: Pimavanserin (Nuplazid) (FDA 2016) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research)</t>
         </is>
       </c>
-      <c r="I12" s="8" t="n">
+      <c r="J26" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>Htr2a=allen_only_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic exclusion populations</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>132 AHN-RCH-LHA Otp Fezf1 Glut</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>4156</v>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Fezf1, Gad1, Gsx1, Otp, Pdrm12, Slc32a1</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>Foxb1, Lhx5, Pou4f1</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1, Grm5</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>(counter-stain only; drugs not recommended)</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic exclusion populations</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>098 AHN-SBPV-PVHd Pdrm12 Gaba</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>7028</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Fezf1, Gad1, Gsx1, Otp, Pdrm12, Slc32a1</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Foxb1, Lhx5, Pou4f1</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1, Grm5</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>(counter-stain only; drugs not recommended)</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic exclusion populations</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>102 DMH-LHA Gsx1 Gaba</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>6768</v>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Fezf1, Gad1, Gsx1, Otp, Pdrm12, Slc32a1</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Foxb1, Lhx5, Pou4f1</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>(counter-stain only; drugs not recommended)</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>ORBm</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>L2/3 IT excitatory</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>007 L2/3 IT CTX Glut</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n">
         <v>8869</v>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>Cdh13, Cux1, Cux2, Rorb, Satb2, Slc17a7</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>Gad1, Slc32a1</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Cckbr, Gabbr1, Gabbr2, Grm1, Grm5</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="J30" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>Cckbr=paper+allen_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="L30" s="8" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>L5 IT / L5 ET/PT output neurons</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>005 L5 IT CTX Glut</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>4419</v>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Bcl11b, Fezf2, Foxp2, Pcp4, Rprm, Slc17a7</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1, Gabbr2, Grm5</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>L5 IT / L5 ET/PT output neurons</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>022 L5 ET CTX Glut</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Bcl11b, Fezf2, Foxp2, Pcp4, Rprm, Slc17a7</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Gabbr1, Mc4r, Cckbr, Gabbr2, Grm5</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Mc4r: Setmelanotide (Imcivree) (FDA 2020) | Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>Gabbr1=allen_only_keep; Mc4r=allen_only_keep; Cckbr=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>L5 IT / L5 ET/PT output neurons</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>032 L5 NP CTX Glut</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>3988</v>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Bcl11b, Fezf2, Foxp2, Pcp4, Rprm, Slc17a7</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Htr2c, Avpr1a, Chrm2, Gabbr1, Grm5</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>Htr2c: Lorcaserin (Belviq) (FDA) | Avpr1a: Balovaptan (RG7314) (clinical-trial) | Chrm2: Donepezil (Aricept) (FDA 1996) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>Htr2c=allen_only_keep; Avpr1a=allen_only_keep; Chrm2=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>L6 CT / L6b</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>030 L6 CT CTX Glut</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>21453</v>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Cplx3, Ctgf, Foxp2, Nxph4, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1, Gabbr2, Grm5, Htr1f, Oprm1</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Htr1f: Lasmiditan (Reyvow) (FDA 2019) | Oprm1: Morphine (FDA)</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Htr1f=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>L6 CT / L6b</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>029 L6b CTX Glut</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>1586</v>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Cplx3, Ctgf, Foxp2, Nxph4, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>Cckbr, Gabbr1, Gabbr2, Oprm1</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Oprm1: Morphine (FDA)</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>Cckbr=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>L6 CT / L6b</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>004 L6 IT CTX Glut</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>11338</v>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Cplx3, Ctgf, Foxp2, Nxph4, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>Cckbr, Gabbr1, Gabbr2, Grm1, Grm5</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>Cckbr=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>052 Pvalb Gaba</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Oprd1, Adcyap1r1, Gabbr1, Gabbr2, Grm5</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>Oprd1: SNC80 (research) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>Oprd1=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>053 Sst Gaba</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>5377</v>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>046 Vip Gaba</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>3277</v>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Gabbr1, Npy1r</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Npy1r: BIBP3226 (research)</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Npy1r=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>049 Lamp5 Gaba</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>2339</v>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>Gabbr2, Adcyap1r1, Gabbr1, Grm5, Hcrtr2</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>Gabbr2: Baclofen (FDA 1977) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Hcrtr2: Suvorexant (Belsomra) (FDA 2014)</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>Gabbr2=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Hcrtr2=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>AId</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Upper-layer IT excitatory</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>007 L2/3 IT CTX Glut</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n">
         <v>7697</v>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>Cux1, Cux2, Rorb, Slc17a7</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>Gad1, Slc32a1</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>Gpr88, Cckbr, Gabbr1, Gabbr2, Grm5</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>Gpr88: RTI-13951-33 (research) | Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
-      <c r="I14" s="8" t="n">
+      <c r="J41" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="K41" s="8" t="inlineStr">
         <is>
           <t>Gpr88=allen_only_keep; Cckbr=paper+allen_broadly_detectable; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="L41" s="8" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>AId</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Upper-layer IT excitatory</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>006 L4/5 IT CTX Glut</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="n">
         <v>12177</v>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>Cux1, Cux2, Rorb, Slc17a7</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>Gad1, Slc32a1</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>Crhr1, Gabbr1, Gabbr2, Grm5, Htr2a</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>Crhr1: Verucerfont (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Htr2a: Pimavanserin (Nuplazid) (FDA 2016)</t>
         </is>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="J42" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="K42" s="8" t="inlineStr">
         <is>
           <t>Crhr1=allen_only_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable; Htr2a=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="L42" s="8" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Deep-layer output neurons</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>030 L6 CT CTX Glut</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>13072</v>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Bcl11b, Ctgf, Fezf2, Foxp2, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1, Gabbr2, Grm5, Htr1f</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Htr1f: Lasmiditan (Reyvow) (FDA 2019)</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Htr1f=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Deep-layer output neurons</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>022 L5 ET CTX Glut</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>1134</v>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Bcl11b, Ctgf, Fezf2, Foxp2, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Htr1f, Htr1b, Mc4r, Cckbr, Gabbr1</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>Htr1f: Lasmiditan (Reyvow) (FDA 2019) | Htr1b: Sumatriptan (FDA 1992) | Mc4r: Setmelanotide (Imcivree) (FDA 2020) | Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977)</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>Htr1f=allen_only_keep; Htr1b=allen_only_keep; Mc4r=allen_only_keep; Cckbr=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Deep-layer output neurons</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>032 L5 NP CTX Glut</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>3409</v>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Bcl11b, Ctgf, Fezf2, Foxp2, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Grm5, Avpr1a, Chrm2, Gabbr1, Htr2c</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>Grm5: Mavoglurant (AFQ056) (clinical-trial) | Avpr1a: Balovaptan (RG7314) (clinical-trial) | Chrm2: Donepezil (Aricept) (FDA 1996) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Htr2c: Lorcaserin (Belviq) (FDA)</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>Grm5=allen_only_keep; Avpr1a=allen_only_keep; Chrm2=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Htr2c=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L45" s="8" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>Deep-layer output neurons</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>029 L6b CTX Glut</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>439</v>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>Bcl11b, Ctgf, Fezf2, Foxp2, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>Cckbr, Drd1, Gabbr1, Gabbr2, Grm5</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>Cckbr: Netazepide (YF476) (clinical-trial) | Drd1: Apomorphine (FDA) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>Cckbr=allen_only_broadly_detectable; Drd1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>053 Sst Gaba</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>5983</v>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>052 Pvalb Gaba</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>3617</v>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm5, Oprd1</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Oprd1: SNC80 (research)</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Oprd1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>046 Vip Gaba</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>3706</v>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Gpr101, Adcyap1r1, Gabbr1, Grm5, Npy1r</t>
+        </is>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>Gpr101: (no clinical drugs) (research) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Npy1r: BIBP3226 (research)</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>Gpr101=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Npy1r=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>049 Lamp5 Gaba</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>3704</v>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Gabbr2, Gpr6, Adcyap1r1, Gabbr1, Grm5</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>Gabbr2: Baclofen (FDA 1977) | Gpr6: CVN424 (Cerevance) (clinical-trial) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>Gabbr2=allen_only_keep; Gpr6=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>CA1 pyramidal</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>016 CA1-ProS Glut</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="n">
         <v>24868</v>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>Fibcd1, Mpped1, Pou3f1, Slc17a7, Spink8, Wfs1</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>Calb1, Cnih3, Prox1, Rgs14</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>Htr1a, Mc4r, Gabbr1, Gabbr2, Grm1</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="I51" s="8" t="inlineStr">
         <is>
           <t>Htr1a: Buspirone (FDA 1986) | Mc4r: Setmelanotide (Imcivree) (FDA 2020) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research)</t>
         </is>
       </c>
-      <c r="I16" s="8" t="n">
+      <c r="J51" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="K51" s="8" t="inlineStr">
         <is>
           <t>Htr1a=paper+allen_keep; Mc4r=allen_only_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="L51" s="8" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>CA2 pyramidal</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>025 CA2-FC-IG Glut</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="n">
         <v>327</v>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>Amigo2, Avpr1b, Cacng5, Map3k15, Pcp4, Rgs14, Slc17a7</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>Cnih3, Prox1, Wfs1</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>Avpr1b, Gabbr1, Gabbr2, Grm5</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>Avpr1b: Nelivaptan (SSR149415) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="J52" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="K52" s="8" t="inlineStr">
         <is>
           <t>Avpr1b=paper+allen_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="L52" s="8" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>CA3 pyramidal</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>017 CA3 Glut</t>
         </is>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="n">
         <v>4799</v>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>Calb2, Cnih3, Coch, Lct, Slc17a7</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>Prox1, Rgs14, Wfs1</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>Npy2r, Hcrtr1, Gabbr1, Gabbr2, Grm1</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>Npy2r: BIIE0246 (research) | Hcrtr1: SB-334867 (research) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research)</t>
         </is>
       </c>
-      <c r="I18" s="8" t="n">
+      <c r="J53" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="K53" s="8" t="inlineStr">
         <is>
           <t>Npy2r=allen_only_keep; Hcrtr1=allen_only_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="L53" s="8" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>DG granule cell</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>037 DG Glut</t>
         </is>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="n">
         <v>80255</v>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="F54" s="9" t="inlineStr">
         <is>
           <t>C1ql2, Calb1, Dock10, Dsp, Prox1, Slc17a7</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="G54" s="9" t="inlineStr">
         <is>
           <t>Cnih3, Rgs14, Wfs1</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="H54" s="9" t="inlineStr">
         <is>
           <t>Grm1, Grm5</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="I54" s="9" t="inlineStr">
         <is>
           <t>Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="J54" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="K54" s="9" t="inlineStr">
         <is>
           <t>Grm1=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="L54" s="9" t="inlineStr">
         <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
@@ -1744,24 +3878,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:P54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="130" customWidth="1" min="9" max="9"/>
-    <col width="90" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="90" customWidth="1" min="13" max="13"/>
-    <col width="110" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="130" customWidth="1" min="10" max="10"/>
+    <col width="90" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="90" customWidth="1" min="14" max="14"/>
+    <col width="110" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1782,60 +3917,65 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>anchor_role</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>n_cells_in_anchor</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>cell_type_marker_genes</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>exclusion_markers</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>paper_suggested_gpcrs</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>allen_validated_top_picks</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>combined_GPCRs_for_probe</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>combined_evidence_summary</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>n_GPCRs_keep</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>n_broadly_detectable</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>existing_drugs_for_picks</t>
         </is>
       </c>
-      <c r="N1" s="11" t="inlineStr">
+      <c r="O1" s="12" t="inlineStr">
         <is>
           <t>drugs_with_sources_per_picks</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>warning</t>
         </is>
@@ -1857,52 +3997,57 @@
           <t>061 STR D1 Gaba</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>16660</v>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Drd1, Isl1, Pdyn, Tac1</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Adora2a, Drd2, Penk</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Chrm4, Cnr1, Drd1, Gabbr1, Gpr88, Grm1, Grm5, Htr1b, Oprd1, Oprm1</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Drd1(spec=0.44, log2=8.77, pct=100%, status=keep); Grm1(spec=0.22, log2=8.99, pct=99%, status=keep); Htr1b(spec=0.15, log2=6.50, pct=93%, status=keep); Chrm4(spec=0.00, log2=0.27, pct=6%, status=candidate_to_validate)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Drd1[paper+allen_keep, spec=+0.44, log2=8.77, pct=100%; drugs: Apomorphine (mixed); Pergolide (partial)]; Grm1[paper+allen_keep, spec=+0.22, log2=8.99, pct=99%; drugs: research_only_or_none]; Htr1b[paper+allen_keep, spec=+0.15, log2=6.50, pct=93%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Chrm4[paper+allen_keep, spec=+0.00, log2=0.27, pct=6%; drugs: Xanomeline (in KarXT/Cobenfy; FDA Sept 2024 for schizophrenia)]; Cnr1[paper+allen_broadly_detectable, spec=-1.92, log2=7.76, pct=93%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Gabbr1[paper+allen_broadly_detectable, spec=-0.59, log2=8.59, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gpr88[paper+allen_broadly_detectable, spec=-0.76, log2=10.17, pct=100%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-0.02, log2=11.36, pct=100%; drugs: research_only_or_none]; Htr2c[allen_only_broadly_detectable, spec=-0.75, log2=7.00, pct=94%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Oprd1[paper_only_allen_downgrade, spec=-5.76, log2=0.13, pct=2%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-5.12, log2=2.83, pct=44%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>both_keep: Drd1, Grm1, Htr1b, Chrm4 | paper+broadly_detectable: Cnr1, Gabbr1, Gpr88, Grm5 | allen_only_broadly_detectable: Htr2c | paper_only: Oprd1(downgrade,spec=-5.76,log2=0.13); Oprm1(downgrade,spec=-5.12,log2=2.83)</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="L2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="M2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Chrm4 | FDA: Xanomeline (in KarXT/Cobenfy; FDA Sept 2024 for schizophrenia) | indication: schizophrenia || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gpr88 | clinical/research: RTI-13951-33 (research agonist) | indication: obsessive-compulsive disorder; addiction (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="110" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -1920,48 +4065,53 @@
           <t>063 STR D1 Sema5a Gaba</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Drd1, Isl1, Pdyn, Tac1</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Adora2a, Drd2, Penk</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Chrm4, Cnr1, Drd1, Gabbr1, Gpr88, Grm1, Grm5, Htr1b, Oprd1, Oprm1</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Drd1[paper+allen_broadly_detectable, spec=-0.44, log2=8.33, pct=99%; drugs: Apomorphine (mixed); Pergolide (partial)]; Gabbr1[paper+allen_broadly_detectable, spec=-0.65, log2=8.53, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gpr88[paper+allen_broadly_detectable, spec=-0.22, log2=10.70, pct=100%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-1.04, log2=10.34, pct=100%; drugs: research_only_or_none]; Chrm4[paper_only_allen_downgrade, spec=-0.00, log2=0.27, pct=6%; drugs: Xanomeline (in KarXT/Cobenfy; FDA Sept 2024 for schizophrenia)]; Cnr1[paper_only_allen_downgrade, spec=-2.88, log2=6.79, pct=85%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Grm1[paper_only_allen_downgrade, spec=-4.63, log2=4.36, pct=68%; drugs: research_only_or_none]; Htr1b[paper_only_allen_downgrade, spec=-3.19, log2=3.31, pct=55%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Oprd1[paper_only_allen_downgrade, spec=-5.21, log2=0.68, pct=13%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-3.98, log2=3.97, pct=61%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>paper+broadly_detectable: Drd1, Gabbr1, Gpr88, Grm5 | paper_only: Chrm4(downgrade,spec=-0.00,log2=0.27); Cnr1(downgrade,spec=-2.88,log2=6.79); Grm1(downgrade,spec=-4.63,log2=4.36); Htr1b(downgrade,spec=-3.19,log2=3.31); Oprd1(downgrade,spec=-5.21,log2=0.68); Oprm1(downgrade,spec=-3.98,log2=3.97)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="L3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="M3" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gpr88 | clinical/research: RTI-13951-33 (research agonist) | indication: obsessive-compulsive disorder; addiction (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Chrm4 | FDA: Xanomeline (in KarXT/Cobenfy; FDA Sept 2024 for schizophrenia) | indication: schizophrenia || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
         </is>
@@ -1983,52 +4133,57 @@
           <t>062 STR D2 Gaba</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>18139</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Adora2a, Drd2, Gpr52, Gpr6, Penk, Sp9</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Drd1, Tac1</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Adora2a, Chrm4, Cnr1, Drd2, Gpr52, Gpr6, Gpr88, Grm1, Grm5, Oprd1</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Grm5(spec=0.02, log2=11.38, pct=100%, status=keep); Gpr88(spec=0.22, log2=10.92, pct=100%, status=keep); Drd2(spec=0.24, log2=9.26, pct=99%, status=keep); Adora2a(spec=4.32, log2=9.20, pct=99%, status=keep); Gpr6(spec=5.74, log2=6.45, pct=93%, status=keep); Gpr52(spec=2.26, log2=2.78, pct=50%, status=keep)</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Grm5[paper+allen_keep, spec=+0.02, log2=11.38, pct=100%; drugs: research_only_or_none]; Gpr88[paper+allen_keep, spec=+0.22, log2=10.92, pct=100%; drugs: research_only_or_none]; Drd2[paper+allen_keep, spec=+0.24, log2=9.26, pct=99%; drugs: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect)]; Adora2a[paper+allen_keep, spec=+4.32, log2=9.20, pct=99%; drugs: Istradefylline (Nourianz; FDA 2019)]; Gpr6[paper+allen_keep, spec=+5.74, log2=6.45, pct=93%; drugs: research_only_or_none]; Gpr52[paper+allen_keep, spec=+2.26, log2=2.78, pct=50%; drugs: research_only_or_none]; Grm1[paper+allen_broadly_detectable, spec=-0.22, log2=8.77, pct=98%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.69, log2=8.49, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Htr1b[allen_only_broadly_detectable, spec=-0.15, log2=6.35, pct=90%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Htr2c[allen_only_broadly_detectable, spec=-0.41, log2=7.34, pct=94%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Chrm4[paper_only_allen_downgrade, spec=-0.27, log2=0.01, pct=0%; drugs: Xanomeline (in KarXT/Cobenfy; FDA Sept 2024 for schizophrenia)]; Cnr1[paper_only_allen_downgrade, spec=-2.40, log2=7.28, pct=88%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Oprd1[paper_only_allen_downgrade, spec=-2.02, log2=3.86, pct=64%; drugs: research_only_or_none]</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>both_keep: Grm5, Gpr88, Drd2, Adora2a, Gpr6, Gpr52 | paper+broadly_detectable: Grm1 | allen_only_broadly_detectable: Gabbr1, Htr1b, Htr2c | paper_only: Chrm4(downgrade,spec=-0.27,log2=0.01); Cnr1(downgrade,spec=-2.40,log2=7.28); Oprd1(downgrade,spec=-2.02,log2=3.86)</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="L4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="M4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Gpr88 | clinical/research: RTI-13951-33 (research agonist) | indication: obsessive-compulsive disorder; addiction (preclinical) || Drd2 | FDA: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect) | clinical/research: many | indication: schizophrenia; bipolar; Parkinson disease; hyperprolactinemia || Adora2a | FDA: Istradefylline (Nourianz; FDA 2019) | clinical/research: Caffeine (non-selective); Preladenant (discontinued); Tozadenant | indication: Parkinson disease (adjunct to levodopa) || Gpr6 | clinical/research: research antagonists for Parkinson disease | indication: Parkinson research (preclinical) || Gpr52 | clinical/research: FTBMT (research agonist for Huntington); experimental Lundbeck/Mitsubishi compounds | indication: Huntington disease; schizophrenia (preclinical) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Chrm4 | FDA: Xanomeline (in KarXT/Cobenfy; FDA Sept 2024 for schizophrenia) | indication: schizophrenia || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical)</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="110" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2038,119 +4193,121 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Cholinergic interneuron</t>
+          <t>Patch/striosome SPN</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>058 PAL-STR Gaba-Chol</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Chat, Lhx8, Slc18a3, Slc5a7</t>
-        </is>
+          <t>061 STR D1 Gaba</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>16660</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Drd1, Drd2</t>
+          <t>Drd1, Foxp2, Mor1, Nnat, Oprm1, Pdyn, Tac1</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Adora2a, Chrm2, Chrm4, Cnr1, Drd2, Gabbr1, Oprm1, Tacr1</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Gabbr1(spec=0.59, log2=9.18, pct=100%, status=keep); Chrm2(spec=0.32, log2=8.97, pct=100%, status=keep); Oprm1(spec=1.08, log2=7.95, pct=100%, status=keep); Tacr3(spec=3.71, log2=7.12, pct=93%, status=keep); Oprd1(spec=2.02, log2=5.88, pct=97%, status=keep); Hcrtr2(spec=3.07, log2=4.37, pct=77%, status=keep); Crhr1(spec=0.14, log2=3.07, pct=67%, status=keep)</t>
-        </is>
-      </c>
+          <t>Adora2a, Calb1, Drd2</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1[paper+allen_keep, spec=+0.59, log2=9.18, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Chrm2[paper+allen_keep, spec=+0.32, log2=8.97, pct=100%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Oprm1[paper+allen_keep, spec=+1.08, log2=7.95, pct=100%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Tacr3[allen_only_keep, spec=+3.71, log2=7.12, pct=93%; drugs: Fezolinetant (Veozah; FDA 2023); Elinzanetant (in trials)]; Oprd1[allen_only_keep, spec=+2.02, log2=5.88, pct=97%; drugs: research_only_or_none]; Hcrtr2[allen_only_keep, spec=+3.07, log2=4.37, pct=77%; drugs: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2]; Crhr1[allen_only_keep, spec=+0.14, log2=3.07, pct=67%; drugs: research_only_or_none]; Drd2[paper+allen_broadly_detectable, spec=-0.24, log2=9.02, pct=100%; drugs: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect)]; Tacr1[paper+allen_broadly_detectable, spec=-0.52, log2=9.99, pct=100%; drugs: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet)]; Adcyap1r1[allen_only_broadly_detectable, spec=-1.85, log2=4.69, pct=87%; drugs: research_only_or_none]; Htr2c[allen_only_broadly_detectable, spec=-1.75, log2=6.00, pct=93%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Adora2a[paper_only_allen_downgrade, spec=-7.84, log2=1.36, pct=33%; drugs: Istradefylline (Nourianz; FDA 2019)]; Chrm4[paper_only_allen_downgrade, spec=-0.27, log2=0.00, pct=0%; drugs: Xanomeline (in KarXT/Cobenfy; FDA Sept 2024 for schizophrenia)]; Cnr1[paper_only_allen_downgrade, spec=-7.31, log2=2.37, pct=50%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]</t>
+          <t>Drd1(spec=0.44, log2=8.77, pct=100%, status=keep); Grm1(spec=0.22, log2=8.99, pct=99%, status=keep); Htr1b(spec=0.15, log2=6.50, pct=93%, status=keep); Chrm4(spec=0.00, log2=0.27, pct=6%, status=candidate_to_validate)</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>both_keep: Gabbr1, Chrm2, Oprm1 | allen_only_keep: Tacr3, Oprd1, Hcrtr2, Crhr1 | paper+broadly_detectable: Drd2, Tacr1 | allen_only_broadly_detectable: Adcyap1r1, Htr2c | paper_only: Adora2a(downgrade,spec=-7.84,log2=1.36); Chrm4(downgrade,spec=-0.27,log2=0.00); Cnr1(downgrade,spec=-7.31,log2=2.37)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>7</v>
+          <t>Drd1[allen_only_keep, spec=+0.44, log2=8.77, pct=100%; drugs: Apomorphine (mixed); Pergolide (partial)]; Grm1[allen_only_keep, spec=+0.22, log2=8.99, pct=99%; drugs: research_only_or_none]; Htr1b[allen_only_keep, spec=+0.15, log2=6.50, pct=93%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Chrm4[allen_only_keep, spec=+0.00, log2=0.27, pct=6%; drugs: Xanomeline (in KarXT/Cobenfy; FDA Sept 2024 for schizophrenia)]; Cnr1[allen_only_broadly_detectable, spec=-1.92, log2=7.76, pct=93%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Gabbr1[allen_only_broadly_detectable, spec=-0.59, log2=8.59, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gpr88[allen_only_broadly_detectable, spec=-0.76, log2=10.17, pct=100%; drugs: research_only_or_none]; Grm5[allen_only_broadly_detectable, spec=-0.02, log2=11.36, pct=100%; drugs: research_only_or_none]; Htr2c[allen_only_broadly_detectable, spec=-0.75, log2=7.00, pct=94%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Drd1, Grm1, Htr1b, Chrm4 | allen_only_broadly_detectable: Cnr1, Gabbr1, Gpr88, Grm5, Htr2c</t>
+        </is>
       </c>
       <c r="L5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Tacr3 | FDA: Fezolinetant (Veozah; FDA 2023); Elinzanetant (in trials) | clinical/research: MK-3207 | indication: vasomotor symptoms (menopausal hot flashes) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Hcrtr2 | FDA: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2 | clinical/research: JNJ-42847922 (selective OX2R) | indication: insomnia || Crhr1 | clinical/research: Verucerfont; Pexacerfont; Antalarmin; Emicerfont (depression/PTSD trials mostly failed) | indication: PTSD; major depression; alcohol use disorder (mostly failed) || Drd2 | FDA: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect) | clinical/research: many | indication: schizophrenia; bipolar; Parkinson disease; hyperprolactinemia || Tacr1 | FDA: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet) | indication: chemotherapy-induced nausea/vomiting (CINV); postoperative nausea || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Adora2a | FDA: Istradefylline (Nourianz; FDA 2019) | clinical/research: Caffeine (non-selective); Preladenant (discontinued); Tozadenant | indication: Parkinson disease (adjunct to levodopa) || Chrm4 | FDA: Xanomeline (in KarXT/Cobenfy; FDA Sept 2024 for schizophrenia) | indication: schizophrenia || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD)</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Chrm4 | FDA: Xanomeline (in KarXT/Cobenfy; FDA Sept 2024 for schizophrenia) | indication: schizophrenia || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gpr88 | clinical/research: RTI-13951-33 (research agonist) | indication: obsessive-compulsive disorder; addiction (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="110" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BMAp</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Posterior BMA glutamatergic VGLUT1-like</t>
+          <t>Patch/striosome SPN</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>012 MEA Slc17a7 Glut</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>3984</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>C1ql2, Cartpt, Dcn, Gpr101, Meis2, Slc17a7</t>
-        </is>
+          <t>063 STR D1 Sema5a Gaba</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>780</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Gad1, Gad2, Slc32a1</t>
+          <t>Drd1, Foxp2, Mor1, Nnat, Oprm1, Pdyn, Tac1</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Cckbr, Cnr1, Crhr1, Gabbr1, Gabbr2, Gpr101, Grm5, Htr2c, Npy1r, Oprd1, Oprm1, Sstr2, Tacr1</t>
+          <t>Adora2a, Calb1, Drd2</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Gabbr1[paper+allen_broadly_detectable, spec=-0.71, log2=8.18, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.23, log2=8.68, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-0.93, log2=10.54, pct=100%; drugs: research_only_or_none]; Npy2r[allen_only_broadly_detectable, spec=-0.62, log2=5.07, pct=76%; drugs: research_only_or_none]; Cckbr[paper_only_allen_downgrade, spec=-3.12, log2=3.31, pct=58%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-7.56, log2=3.94, pct=65%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Crhr1[paper_only_allen_downgrade, spec=-1.34, log2=2.20, pct=41%; drugs: research_only_or_none]; Gpr101[paper_only_allen_downgrade, spec=-4.05, log2=2.94, pct=44%; drugs: research_only_or_none]; Htr2c[paper_only_allen_downgrade, spec=-5.59, log2=3.99, pct=59%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Npy1r[paper_only_allen_downgrade, spec=-3.69, log2=3.64, pct=62%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-4.98, log2=0.56, pct=11%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-3.70, log2=3.70, pct=61%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-2.64, log2=2.11, pct=40%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]; Tacr1[paper_only_allen_downgrade, spec=-3.02, log2=3.94, pct=62%; drugs: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet)]</t>
-        </is>
-      </c>
+      <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>paper+broadly_detectable: Gabbr1, Gabbr2, Grm5 | allen_only_broadly_detectable: Npy2r | paper_only: Cckbr(downgrade,spec=-3.12,log2=3.31); Cnr1(downgrade,spec=-7.56,log2=3.94); Crhr1(downgrade,spec=-1.34,log2=2.20); Gpr101(downgrade,spec=-4.05,log2=2.94); Htr2c(downgrade,spec=-5.59,log2=3.99); Npy1r(downgrade,spec=-3.69,log2=3.64); Oprd1(downgrade,spec=-4.98,log2=0.56); Oprm1(downgrade,spec=-3.70,log2=3.70); Sstr2(downgrade,spec=-2.64,log2=2.11); Tacr1(downgrade,spec=-3.02,log2=3.94)</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="n">
+          <t>Drd1[allen_only_broadly_detectable, spec=-0.44, log2=8.33, pct=99%; drugs: Apomorphine (mixed); Pergolide (partial)]; Gabbr1[allen_only_broadly_detectable, spec=-0.65, log2=8.53, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gpr88[allen_only_broadly_detectable, spec=-0.22, log2=10.70, pct=100%; drugs: research_only_or_none]; Grm5[allen_only_broadly_detectable, spec=-1.04, log2=10.34, pct=100%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Drd1, Gabbr1, Gpr88, Grm5</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="M6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Npy2r | clinical/research: BIIE-0246 (research antagonist) | indication: food intake; anxiety (preclinical) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Crhr1 | clinical/research: Verucerfont; Pexacerfont; Antalarmin; Emicerfont (depression/PTSD trials mostly failed) | indication: PTSD; major depression; alcohol use disorder (mostly failed) || Gpr101 | clinical/research: research only (orphan) | indication: X-LAG / X-linked acrogigantism research || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease || Tacr1 | FDA: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet) | indication: chemotherapy-induced nausea/vomiting (CINV); postoperative nausea</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gpr88 | clinical/research: RTI-13951-33 (research agonist) | indication: obsessive-compulsive disorder; addiction (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
         </is>
@@ -2159,817 +4316,3130 @@
     <row r="7" ht="110" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>BMAp</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Posterior BMA glutamatergic VGLUT1-like</t>
+          <t>Matrix/exopatch SPN</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>113 MEA-COA-BMA Ccdc42 Glut</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>9654</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>C1ql2, Cartpt, Dcn, Gpr101, Meis2, Slc17a7</t>
-        </is>
+          <t>061 STR D1 Gaba</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>16660</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Gad1, Gad2, Slc32a1</t>
+          <t>Calb1, Drd1, Mef2c, Tac1</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Cckbr, Cnr1, Crhr1, Gabbr1, Gabbr2, Gpr101, Grm5, Htr2c, Npy1r, Oprd1, Oprm1, Sstr2, Tacr1</t>
+          <t>Adora2a, Foxp2, Pdyn</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1[paper+allen_broadly_detectable, spec=-0.61, log2=8.28, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.53, log2=8.38, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-1.12, log2=10.36, pct=100%; drugs: research_only_or_none]; Oprm1[paper+allen_broadly_detectable, spec=-1.67, log2=5.73, pct=82%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Cckbr[paper_only_allen_downgrade, spec=-3.22, log2=3.22, pct=56%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-10.94, log2=0.57, pct=10%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Crhr1[paper_only_allen_downgrade, spec=-1.36, log2=2.19, pct=39%; drugs: research_only_or_none]; Gpr101[paper_only_allen_downgrade, spec=-3.42, log2=3.57, pct=57%; drugs: research_only_or_none]; Htr2c[paper_only_allen_downgrade, spec=-2.20, log2=7.38, pct=87%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Npy1r[paper_only_allen_downgrade, spec=-3.62, log2=3.71, pct=62%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-3.55, log2=1.98, pct=36%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-2.28, log2=2.47, pct=44%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]; Tacr1[paper_only_allen_downgrade, spec=-6.77, log2=0.19, pct=4%; drugs: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet)]</t>
+          <t>Drd1(spec=0.44, log2=8.77, pct=100%, status=keep); Grm1(spec=0.22, log2=8.99, pct=99%, status=keep); Htr1b(spec=0.15, log2=6.50, pct=93%, status=keep); Chrm4(spec=0.00, log2=0.27, pct=6%, status=candidate_to_validate)</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>paper+broadly_detectable: Gabbr1, Gabbr2, Grm5, Oprm1 | paper_only: Cckbr(downgrade,spec=-3.22,log2=3.22); Cnr1(downgrade,spec=-10.94,log2=0.57); Crhr1(downgrade,spec=-1.36,log2=2.19); Gpr101(downgrade,spec=-3.42,log2=3.57); Htr2c(downgrade,spec=-2.20,log2=7.38); Npy1r(downgrade,spec=-3.62,log2=3.71); Oprd1(downgrade,spec=-3.55,log2=1.98); Sstr2(downgrade,spec=-2.28,log2=2.47); Tacr1(downgrade,spec=-6.77,log2=0.19)</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0</v>
+          <t>Drd1[allen_only_keep, spec=+0.44, log2=8.77, pct=100%; drugs: Apomorphine (mixed); Pergolide (partial)]; Grm1[allen_only_keep, spec=+0.22, log2=8.99, pct=99%; drugs: research_only_or_none]; Htr1b[allen_only_keep, spec=+0.15, log2=6.50, pct=93%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Chrm4[allen_only_keep, spec=+0.00, log2=0.27, pct=6%; drugs: Xanomeline (in KarXT/Cobenfy; FDA Sept 2024 for schizophrenia)]; Cnr1[allen_only_broadly_detectable, spec=-1.92, log2=7.76, pct=93%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Gabbr1[allen_only_broadly_detectable, spec=-0.59, log2=8.59, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gpr88[allen_only_broadly_detectable, spec=-0.76, log2=10.17, pct=100%; drugs: research_only_or_none]; Grm5[allen_only_broadly_detectable, spec=-0.02, log2=11.36, pct=100%; drugs: research_only_or_none]; Htr2c[allen_only_broadly_detectable, spec=-0.75, log2=7.00, pct=94%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Drd1, Grm1, Htr1b, Chrm4 | allen_only_broadly_detectable: Cnr1, Gabbr1, Gpr88, Grm5, Htr2c</t>
+        </is>
       </c>
       <c r="L7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Crhr1 | clinical/research: Verucerfont; Pexacerfont; Antalarmin; Emicerfont (depression/PTSD trials mostly failed) | indication: PTSD; major depression; alcohol use disorder (mostly failed) || Gpr101 | clinical/research: research only (orphan) | indication: X-LAG / X-linked acrogigantism research || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease || Tacr1 | FDA: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet) | indication: chemotherapy-induced nausea/vomiting (CINV); postoperative nausea</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Chrm4 | FDA: Xanomeline (in KarXT/Cobenfy; FDA Sept 2024 for schizophrenia) | indication: schizophrenia || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gpr88 | clinical/research: RTI-13951-33 (research agonist) | indication: obsessive-compulsive disorder; addiction (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="110" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Midline thalamic glutamatergic / reuniens</t>
+          <t>Matrix/exopatch SPN</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>152 RE-Xi Nox4 Glut</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>5450</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
-        </is>
+          <t>062 STR D2 Gaba</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>18139</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Gad1, Gad2</t>
+          <t>Calb1, Drd1, Mef2c, Tac1</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1, Chrm2, Gabbr1, Gabbr2, Grm1, Grm5, Htr2a, Ntsr1, Ntsr2, Sstr2</t>
+          <t>Adora2a, Foxp2, Pdyn</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1[paper+allen_broadly_detectable, spec=-1.71, log2=9.35, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.58, log2=9.23, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-1.19, log2=8.82, pct=98%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-1.51, log2=10.02, pct=100%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-5.37, log2=2.78, pct=46%; drugs: research_only_or_none]; Chrm2[paper_only_allen_downgrade, spec=-2.93, log2=6.27, pct=81%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Htr2a[paper_only_allen_downgrade, spec=-3.09, log2=0.04, pct=1%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Ntsr1[paper_only_allen_downgrade, spec=-1.23, log2=0.33, pct=6%; drugs: research_only_or_none]; Ntsr2[paper_only_allen_downgrade, spec=-9.00, log2=0.04, pct=1%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-4.46, log2=0.20, pct=4%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+          <t>Grm5(spec=0.02, log2=11.38, pct=100%, status=keep); Gpr88(spec=0.22, log2=10.92, pct=100%, status=keep); Drd2(spec=0.24, log2=9.26, pct=99%, status=keep); Adora2a(spec=4.32, log2=9.20, pct=99%, status=keep); Gpr6(spec=5.74, log2=6.45, pct=93%, status=keep); Gpr52(spec=2.26, log2=2.78, pct=50%, status=keep)</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>paper+broadly_detectable: Gabbr1, Gabbr2, Grm1, Grm5 | paper_only: Adcyap1r1(downgrade,spec=-5.37,log2=2.78); Chrm2(downgrade,spec=-2.93,log2=6.27); Htr2a(downgrade,spec=-3.09,log2=0.04); Ntsr1(downgrade,spec=-1.23,log2=0.33); Ntsr2(downgrade,spec=-9.00,log2=0.04); Sstr2(downgrade,spec=-4.46,log2=0.20)</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0</v>
+          <t>Grm5[allen_only_keep, spec=+0.02, log2=11.38, pct=100%; drugs: research_only_or_none]; Gpr88[allen_only_keep, spec=+0.22, log2=10.92, pct=100%; drugs: research_only_or_none]; Drd2[allen_only_keep, spec=+0.24, log2=9.26, pct=99%; drugs: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect)]; Adora2a[allen_only_keep, spec=+4.32, log2=9.20, pct=99%; drugs: Istradefylline (Nourianz; FDA 2019)]; Gpr6[allen_only_keep, spec=+5.74, log2=6.45, pct=93%; drugs: research_only_or_none]; Gpr52[allen_only_keep, spec=+2.26, log2=2.78, pct=50%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.69, log2=8.49, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm1[allen_only_broadly_detectable, spec=-0.22, log2=8.77, pct=98%; drugs: research_only_or_none]; Htr1b[allen_only_broadly_detectable, spec=-0.15, log2=6.35, pct=90%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Htr2c[allen_only_broadly_detectable, spec=-0.41, log2=7.34, pct=94%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Grm5, Gpr88, Drd2, Adora2a, Gpr6, Gpr52 | allen_only_broadly_detectable: Gabbr1, Grm1, Htr1b, Htr2c</t>
+        </is>
       </c>
       <c r="L8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Ntsr1 | clinical/research: SR-48692 (research antagonist); SR-142948 | indication: thermal pain; addiction (preclinical) || Ntsr2 | clinical/research: research | indication: pain (preclinical) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
-        </is>
-      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Gpr88 | clinical/research: RTI-13951-33 (research agonist) | indication: obsessive-compulsive disorder; addiction (preclinical) || Drd2 | FDA: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect) | clinical/research: many | indication: schizophrenia; bipolar; Parkinson disease; hyperprolactinemia || Adora2a | FDA: Istradefylline (Nourianz; FDA 2019) | clinical/research: Caffeine (non-selective); Preladenant (discontinued); Tozadenant | indication: Parkinson disease (adjunct to levodopa) || Gpr6 | clinical/research: research antagonists for Parkinson disease | indication: Parkinson research (preclinical) || Gpr52 | clinical/research: FTBMT (research agonist for Huntington); experimental Lundbeck/Mitsubishi compounds | indication: Huntington disease; schizophrenia (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="110" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Midline thalamic glutamatergic / reuniens</t>
+          <t>Cholinergic interneuron</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>149 PVT-PT Ntrk1 Glut</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>9854</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
-        </is>
+          <t>058 PAL-STR Gaba-Chol</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Gad1, Gad2</t>
+          <t>Chat, Lhx8, Slc18a3, Slc5a7</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1, Chrm2, Gabbr1, Gabbr2, Grm1, Grm5, Htr2a, Ntsr1, Ntsr2, Sstr2</t>
+          <t>Drd1, Drd2</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Oprk1(spec=1.42, log2=4.18, pct=66%, status=keep); Galr1(spec=0.23, log2=2.12, pct=35%, status=keep); Oxtr(spec=0.50, log2=1.89, pct=34%, status=keep)</t>
+          <t>Adora2a, Chrm2, Chrm4, Cnr1, Drd2, Gabbr1, Oprm1, Tacr1</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Oprk1[allen_only_keep, spec=+1.42, log2=4.18, pct=66%; drugs: Difelikefalin (Korsuva; FDA 2021)]; Galr1[allen_only_keep, spec=+0.23, log2=2.12, pct=35%; drugs: research_only_or_none]; Oxtr[allen_only_keep, spec=+0.50, log2=1.89, pct=34%; drugs: research_only_or_none]; Cnr1[allen_only_broadly_detectable, spec=-0.69, log2=5.48, pct=78%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Oprm1[allen_only_broadly_detectable, spec=-0.58, log2=6.85, pct=84%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Adcyap1r1[paper_only_allen_downgrade, spec=-2.91, log2=5.24, pct=81%; drugs: research_only_or_none]; Chrm2[paper_only_allen_downgrade, spec=-5.90, log2=3.30, pct=48%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Gabbr1[paper_only_allen_downgrade, spec=-2.30, log2=8.76, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper_only_allen_downgrade, spec=-2.01, log2=8.80, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper_only_allen_downgrade, spec=-2.93, log2=7.07, pct=87%; drugs: research_only_or_none]; Grm5[paper_only_allen_downgrade, spec=-2.67, log2=8.86, pct=99%; drugs: research_only_or_none]; Htr2a[paper_only_allen_downgrade, spec=-3.10, log2=0.03, pct=1%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Ntsr1[paper_only_allen_downgrade, spec=-1.24, log2=0.32, pct=6%; drugs: research_only_or_none]; Ntsr2[paper_only_allen_downgrade, spec=-8.68, log2=0.36, pct=7%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-4.18, log2=0.48, pct=9%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+          <t>Gabbr1(spec=0.59, log2=9.18, pct=100%, status=keep); Chrm2(spec=0.32, log2=8.97, pct=100%, status=keep); Oprm1(spec=1.08, log2=7.95, pct=100%, status=keep); Tacr3(spec=3.71, log2=7.12, pct=93%, status=keep); Oprd1(spec=2.02, log2=5.88, pct=97%, status=keep); Hcrtr2(spec=3.07, log2=4.37, pct=77%, status=keep); Crhr1(spec=0.14, log2=3.07, pct=67%, status=keep)</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Oprk1, Galr1, Oxtr | allen_only_broadly_detectable: Cnr1, Oprm1 | paper_only: Adcyap1r1(downgrade,spec=-2.91,log2=5.24); Chrm2(downgrade,spec=-5.90,log2=3.30); Gabbr1(downgrade,spec=-2.30,log2=8.76); Gabbr2(downgrade,spec=-2.01,log2=8.80); Grm1(downgrade,spec=-2.93,log2=7.07); Grm5(downgrade,spec=-2.67,log2=8.86); Htr2a(downgrade,spec=-3.10,log2=0.03); Ntsr1(downgrade,spec=-1.24,log2=0.32); Ntsr2(downgrade,spec=-8.68,log2=0.36); Sstr2(downgrade,spec=-4.18,log2=0.48)</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>3</v>
+          <t>Gabbr1[paper+allen_keep, spec=+0.59, log2=9.18, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Chrm2[paper+allen_keep, spec=+0.32, log2=8.97, pct=100%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Oprm1[paper+allen_keep, spec=+1.08, log2=7.95, pct=100%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Tacr3[allen_only_keep, spec=+3.71, log2=7.12, pct=93%; drugs: Fezolinetant (Veozah; FDA 2023); Elinzanetant (in trials)]; Oprd1[allen_only_keep, spec=+2.02, log2=5.88, pct=97%; drugs: research_only_or_none]; Hcrtr2[allen_only_keep, spec=+3.07, log2=4.37, pct=77%; drugs: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2]; Crhr1[allen_only_keep, spec=+0.14, log2=3.07, pct=67%; drugs: research_only_or_none]; Drd2[paper+allen_broadly_detectable, spec=-0.24, log2=9.02, pct=100%; drugs: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect)]; Tacr1[paper+allen_broadly_detectable, spec=-0.52, log2=9.99, pct=100%; drugs: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet)]; Adcyap1r1[allen_only_broadly_detectable, spec=-1.85, log2=4.69, pct=87%; drugs: research_only_or_none]; Htr2c[allen_only_broadly_detectable, spec=-1.75, log2=6.00, pct=93%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Adora2a[paper_only_allen_downgrade, spec=-7.84, log2=1.36, pct=33%; drugs: Istradefylline (Nourianz; FDA 2019)]; Chrm4[paper_only_allen_downgrade, spec=-0.27, log2=0.00, pct=0%; drugs: Xanomeline (in KarXT/Cobenfy; FDA Sept 2024 for schizophrenia)]; Cnr1[paper_only_allen_downgrade, spec=-7.31, log2=2.37, pct=50%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>both_keep: Gabbr1, Chrm2, Oprm1 | allen_only_keep: Tacr3, Oprd1, Hcrtr2, Crhr1 | paper+broadly_detectable: Drd2, Tacr1 | allen_only_broadly_detectable: Adcyap1r1, Htr2c | paper_only: Adora2a(downgrade,spec=-7.84,log2=1.36); Chrm4(downgrade,spec=-0.27,log2=0.00); Cnr1(downgrade,spec=-7.31,log2=2.37)</t>
+        </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>Oprk1 | FDA: Difelikefalin (Korsuva; FDA 2021) | clinical/research: Nalfurafine (Japan); Buprenorphine (mixed); CR845 | indication: uremic pruritus (Difelikefalin); depression research || Galr1 | clinical/research: research only | indication: epilepsy; depression (preclinical) || Oxtr | clinical/research: Intranasal oxytocin (autism/social trials; mostly failed); Carbetocin (Pabal - postpartum hemorrhage outside USA) | indication: autism research; social cognition; postpartum hemorrhage (Carbetocin EU) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Ntsr1 | clinical/research: SR-48692 (research antagonist); SR-142948 | indication: thermal pain; addiction (preclinical) || Ntsr2 | clinical/research: research | indication: pain (preclinical) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Tacr3 | FDA: Fezolinetant (Veozah; FDA 2023); Elinzanetant (in trials) | clinical/research: MK-3207 | indication: vasomotor symptoms (menopausal hot flashes) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Hcrtr2 | FDA: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2 | clinical/research: JNJ-42847922 (selective OX2R) | indication: insomnia || Crhr1 | clinical/research: Verucerfont; Pexacerfont; Antalarmin; Emicerfont (depression/PTSD trials mostly failed) | indication: PTSD; major depression; alcohol use disorder (mostly failed) || Drd2 | FDA: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect) | clinical/research: many | indication: schizophrenia; bipolar; Parkinson disease; hyperprolactinemia || Tacr1 | FDA: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet) | indication: chemotherapy-induced nausea/vomiting (CINV); postoperative nausea || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Adora2a | FDA: Istradefylline (Nourianz; FDA 2019) | clinical/research: Caffeine (non-selective); Preladenant (discontinued); Tozadenant | indication: Parkinson disease (adjunct to levodopa) || Chrm4 | FDA: Xanomeline (in KarXT/Cobenfy; FDA Sept 2024 for schizophrenia) | indication: schizophrenia || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD)</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="110" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Midline thalamic glutamatergic / reuniens</t>
+          <t>PV/SST/NPY interneurons</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>145 MH Tac2 Glut</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>7972</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
-        </is>
+          <t>054 STR Prox1 Lhx6 Gaba</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>367</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Gad1, Gad2</t>
+          <t>Calb2, Lhx6, Nos1, Npy, Prox1, Pvalb, Sst</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1, Chrm2, Gabbr1, Gabbr2, Grm1, Grm5, Htr2a, Ntsr1, Ntsr2, Sstr2</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Gabbr1(spec=1.44, log2=11.06, pct=100%, status=keep); Gabbr2(spec=0.83, log2=10.81, pct=99%, status=keep); Tacr1(spec=1.61, log2=6.00, pct=78%, status=keep); Sstr2(spec=2.64, log2=4.66, pct=68%, status=keep)</t>
-        </is>
-      </c>
+          <t>Chat, Drd1, Drd2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1[paper+allen_keep, spec=+1.44, log2=11.06, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_keep, spec=+0.83, log2=10.81, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Sstr2[paper+allen_keep, spec=+2.64, log2=4.66, pct=68%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]; Tacr1[allen_only_keep, spec=+1.61, log2=6.00, pct=78%; drugs: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet)]; Adcyap1r1[paper_only_allen_downgrade, spec=-7.94, log2=0.22, pct=4%; drugs: research_only_or_none]; Chrm2[paper_only_allen_downgrade, spec=-8.87, log2=0.33, pct=5%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Grm1[paper_only_allen_downgrade, spec=-7.57, log2=2.43, pct=35%; drugs: research_only_or_none]; Grm5[paper_only_allen_downgrade, spec=-7.53, log2=3.99, pct=53%; drugs: research_only_or_none]; Htr2a[paper_only_allen_downgrade, spec=-2.68, log2=0.45, pct=7%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Ntsr1[paper_only_allen_downgrade, spec=-1.54, log2=0.02, pct=0%; drugs: research_only_or_none]; Ntsr2[paper_only_allen_downgrade, spec=-8.96, log2=0.08, pct=2%; drugs: research_only_or_none]</t>
+          <t>Cnr1(spec=1.43, log2=9.68, pct=99%, status=keep)</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>both_keep: Gabbr1, Gabbr2, Sstr2 | allen_only_keep: Tacr1 | paper_only: Adcyap1r1(downgrade,spec=-7.94,log2=0.22); Chrm2(downgrade,spec=-8.87,log2=0.33); Grm1(downgrade,spec=-7.57,log2=2.43); Grm5(downgrade,spec=-7.53,log2=3.99); Htr2a(downgrade,spec=-2.68,log2=0.45); Ntsr1(downgrade,spec=-1.54,log2=0.02); Ntsr2(downgrade,spec=-8.96,log2=0.08)</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>4</v>
+          <t>Cnr1[allen_only_keep, spec=+1.43, log2=9.68, pct=99%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Adcyap1r1[allen_only_broadly_detectable, spec=-0.99, log2=5.55, pct=86%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.74, log2=8.44, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.64, log2=7.93, pct=98%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[allen_only_broadly_detectable, spec=-0.52, log2=8.47, pct=98%; drugs: research_only_or_none]; Grm5[allen_only_broadly_detectable, spec=-1.15, log2=10.24, pct=100%; drugs: research_only_or_none]; Htr2a[allen_only_broadly_detectable, spec=-1.70, log2=4.88, pct=79%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Cnr1 | allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5, Htr2a</t>
+        </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease || Tacr1 | FDA: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet) | indication: chemotherapy-induced nausea/vomiting (CINV); postoperative nausea || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Ntsr1 | clinical/research: SR-48692 (research antagonist); SR-142948 | indication: thermal pain; addiction (preclinical) || Ntsr2 | clinical/research: research | indication: pain (preclinical)</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials)</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
     </row>
     <row r="11" ht="110" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>LM</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Lateral mammillary excitatory</t>
+          <t>PV/SST/NPY interneurons</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>144 MM Foxb1 Glut</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>8270</v>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Foxb1, Lhx5, Pou4f1</t>
-        </is>
+          <t>056 Sst Chodl Gaba</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>230</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Slc32a1</t>
+          <t>Calb2, Lhx6, Nos1, Npy, Prox1, Pvalb, Sst</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1, Avpr1a, Cckbr, Gabbr1, Gabbr2, Grm1, Hcrtr1, Hcrtr2, Mc4r, Oxtr, Sstr2</t>
+          <t>Chat, Drd1, Drd2, Slc17a7</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1[paper+allen_broadly_detectable, spec=-1.00, log2=8.28, pct=98%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.75, log2=8.35, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-0.13, log2=9.71, pct=100%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-4.76, log2=2.64, pct=47%; drugs: research_only_or_none]; Avpr1a[paper_only_allen_downgrade, spec=-2.15, log2=0.01, pct=0%; drugs: research_only_or_none]; Cckbr[paper_only_allen_downgrade, spec=-4.07, log2=0.28, pct=6%; drugs: research_only_or_none]; Hcrtr1[paper_only_allen_downgrade, spec=-1.61, log2=0.02, pct=0%; drugs: research_only_or_none]; Hcrtr2[paper_only_allen_downgrade, spec=-4.36, log2=1.25, pct=21%; drugs: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2]; Mc4r[paper_only_allen_downgrade, spec=-1.20, log2=0.00, pct=0%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Oxtr[paper_only_allen_downgrade, spec=-3.63, log2=0.01, pct=0%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-2.19, log2=0.37, pct=7%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+          <t>Tacr1(spec=0.52, log2=10.51, pct=100%, status=keep); Npy2r(spec=6.19, log2=7.00, pct=96%, status=keep); Galr1(spec=6.58, log2=6.71, pct=87%, status=keep); Htr1a(spec=0.40, log2=2.55, pct=45%, status=keep); Gpr101(spec=0.30, log2=0.92, pct=17%, status=keep_validate_spatially)</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>paper+broadly_detectable: Gabbr1, Gabbr2, Grm1 | paper_only: Adcyap1r1(downgrade,spec=-4.76,log2=2.64); Avpr1a(downgrade,spec=-2.15,log2=0.01); Cckbr(downgrade,spec=-4.07,log2=0.28); Hcrtr1(downgrade,spec=-1.61,log2=0.02); Hcrtr2(downgrade,spec=-4.36,log2=1.25); Mc4r(downgrade,spec=-1.20,log2=0.00); Oxtr(downgrade,spec=-3.63,log2=0.01); Sstr2(downgrade,spec=-2.19,log2=0.37)</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>0</v>
+          <t>Tacr1[allen_only_keep, spec=+0.52, log2=10.51, pct=100%; drugs: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet)]; Npy2r[allen_only_keep, spec=+6.19, log2=7.00, pct=96%; drugs: research_only_or_none]; Galr1[allen_only_keep, spec=+6.58, log2=6.71, pct=87%; drugs: research_only_or_none]; Htr1a[allen_only_keep, spec=+0.40, log2=2.55, pct=45%; drugs: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone]; Gpr101[allen_only_keep, spec=+0.30, log2=0.92, pct=17%; drugs: research_only_or_none]; Chrm2[allen_only_broadly_detectable, spec=-0.32, log2=8.65, pct=99%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Gabbr1[allen_only_broadly_detectable, spec=-0.70, log2=8.48, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.40, log2=8.17, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Htr2c[allen_only_broadly_detectable, spec=-0.81, log2=6.94, pct=86%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Tacr1, Npy2r, Galr1, Htr1a, Gpr101 | allen_only_broadly_detectable: Chrm2, Gabbr1, Gabbr2, Htr2c</t>
+        </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Hcrtr1 | clinical/research: SB-334867 (research selective antagonist) | indication: addiction; anxiety (preclinical) || Hcrtr2 | FDA: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2 | clinical/research: JNJ-42847922 (selective OX2R) | indication: insomnia || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Oxtr | clinical/research: Intranasal oxytocin (autism/social trials; mostly failed); Carbetocin (Pabal - postpartum hemorrhage outside USA) | indication: autism research; social cognition; postpartum hemorrhage (Carbetocin EU) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>no cell-type-specific GPCR; relying on 3 broadly_expressed_detectable candidates</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Tacr1 | FDA: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet) | indication: chemotherapy-induced nausea/vomiting (CINV); postoperative nausea || Npy2r | clinical/research: BIIE-0246 (research antagonist) | indication: food intake; anxiety (preclinical) || Galr1 | clinical/research: research only | indication: epilepsy; depression (preclinical) || Htr1a | FDA: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone | clinical/research: NLX-101 (depression) | indication: generalized anxiety; major depression || Gpr101 | clinical/research: research only (orphan) | indication: X-LAG / X-linked acrogigantism research || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="110" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>LM</t>
+          <t>BMAp</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Lateral mammillary excitatory</t>
+          <t>Posterior BMA glutamatergic VGLUT1-like</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>143 MM-ant Foxb1 Glut</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>5437</v>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Foxb1, Lhx5, Pou4f1</t>
-        </is>
+          <t>012 MEA Slc17a7 Glut</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>3984</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Slc32a1</t>
+          <t>C1ql2, Cartpt, Dcn, Gpr101, Meis2, Slc17a7</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1, Avpr1a, Cckbr, Gabbr1, Gabbr2, Grm1, Hcrtr1, Hcrtr2, Mc4r, Oxtr, Sstr2</t>
+          <t>Gad1, Gad2, Slc17a6, Slc32a1</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Htr2a(spec=1.70, log2=5.18, pct=73%, status=keep)</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Htr2a[allen_only_keep, spec=+1.70, log2=5.18, pct=73%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Gabbr1[paper+allen_broadly_detectable, spec=-1.09, log2=8.19, pct=97%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.74, log2=8.36, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-0.99, log2=8.85, pct=97%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-4.46, log2=2.93, pct=49%; drugs: research_only_or_none]; Avpr1a[paper_only_allen_downgrade, spec=-2.15, log2=0.00, pct=0%; drugs: research_only_or_none]; Cckbr[paper_only_allen_downgrade, spec=-2.99, log2=1.36, pct=24%; drugs: research_only_or_none]; Hcrtr1[paper_only_allen_downgrade, spec=-1.58, log2=0.05, pct=1%; drugs: research_only_or_none]; Hcrtr2[paper_only_allen_downgrade, spec=-4.97, log2=0.64, pct=11%; drugs: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2]; Mc4r[paper_only_allen_downgrade, spec=-1.20, log2=0.01, pct=0%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Oxtr[paper_only_allen_downgrade, spec=-3.63, log2=0.00, pct=0%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-1.93, log2=0.63, pct=12%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
-        </is>
-      </c>
+          <t>Cckbr, Cnr1, Crhr1, Gabbr1, Gabbr2, Gpr101, Grm5, Htr2c, Npy1r, Oprd1, Oprm1, Sstr2, Tacr1</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Htr2a | paper+broadly_detectable: Gabbr1, Gabbr2, Grm1 | paper_only: Adcyap1r1(downgrade,spec=-4.46,log2=2.93); Avpr1a(downgrade,spec=-2.15,log2=0.00); Cckbr(downgrade,spec=-2.99,log2=1.36); Hcrtr1(downgrade,spec=-1.58,log2=0.05); Hcrtr2(downgrade,spec=-4.97,log2=0.64); Mc4r(downgrade,spec=-1.20,log2=0.01); Oxtr(downgrade,spec=-3.63,log2=0.00); Sstr2(downgrade,spec=-1.93,log2=0.63)</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>1</v>
+          <t>Gabbr1[paper+allen_broadly_detectable, spec=-0.71, log2=8.18, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.23, log2=8.68, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-0.93, log2=10.54, pct=100%; drugs: research_only_or_none]; Npy2r[allen_only_broadly_detectable, spec=-0.62, log2=5.07, pct=76%; drugs: research_only_or_none]; Cckbr[paper_only_allen_downgrade, spec=-3.12, log2=3.31, pct=58%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-7.56, log2=3.94, pct=65%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Crhr1[paper_only_allen_downgrade, spec=-1.34, log2=2.20, pct=41%; drugs: research_only_or_none]; Gpr101[paper_only_allen_downgrade, spec=-4.05, log2=2.94, pct=44%; drugs: research_only_or_none]; Htr2c[paper_only_allen_downgrade, spec=-5.59, log2=3.99, pct=59%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Npy1r[paper_only_allen_downgrade, spec=-3.69, log2=3.64, pct=62%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-4.98, log2=0.56, pct=11%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-3.70, log2=3.70, pct=61%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-2.64, log2=2.11, pct=40%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]; Tacr1[paper_only_allen_downgrade, spec=-3.02, log2=3.94, pct=62%; drugs: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet)]</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>paper+broadly_detectable: Gabbr1, Gabbr2, Grm5 | allen_only_broadly_detectable: Npy2r | paper_only: Cckbr(downgrade,spec=-3.12,log2=3.31); Cnr1(downgrade,spec=-7.56,log2=3.94); Crhr1(downgrade,spec=-1.34,log2=2.20); Gpr101(downgrade,spec=-4.05,log2=2.94); Htr2c(downgrade,spec=-5.59,log2=3.99); Npy1r(downgrade,spec=-3.69,log2=3.64); Oprd1(downgrade,spec=-4.98,log2=0.56); Oprm1(downgrade,spec=-3.70,log2=3.70); Sstr2(downgrade,spec=-2.64,log2=2.11); Tacr1(downgrade,spec=-3.02,log2=3.94)</t>
+        </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Hcrtr1 | clinical/research: SB-334867 (research selective antagonist) | indication: addiction; anxiety (preclinical) || Hcrtr2 | FDA: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2 | clinical/research: JNJ-42847922 (selective OX2R) | indication: insomnia || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Oxtr | clinical/research: Intranasal oxytocin (autism/social trials; mostly failed); Carbetocin (Pabal - postpartum hemorrhage outside USA) | indication: autism research; social cognition; postpartum hemorrhage (Carbetocin EU) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Npy2r | clinical/research: BIIE-0246 (research antagonist) | indication: food intake; anxiety (preclinical) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Crhr1 | clinical/research: Verucerfont; Pexacerfont; Antalarmin; Emicerfont (depression/PTSD trials mostly failed) | indication: PTSD; major depression; alcohol use disorder (mostly failed) || Gpr101 | clinical/research: research only (orphan) | indication: X-LAG / X-linked acrogigantism research || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease || Tacr1 | FDA: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet) | indication: chemotherapy-induced nausea/vomiting (CINV); postoperative nausea</t>
+        </is>
+      </c>
       <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="110" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>ORBm</t>
+          <t>BMAp</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>L2/3 IT excitatory</t>
+          <t>Posterior BMA glutamatergic VGLUT1-like</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>007 L2/3 IT CTX Glut</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>8869</v>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Cdh13, Cux1, Cux2, Rorb, Satb2, Slc17a7</t>
-        </is>
+          <t>113 MEA-COA-BMA Ccdc42 Glut</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>9654</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Gad1, Slc32a1</t>
+          <t>C1ql2, Cartpt, Dcn, Gpr101, Meis2, Slc17a7</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Cckbr, Cnr1, Gabbr1, Gabbr2, Grm1, Grm5, Htr2a, Npy1r, Oprd1, Oprm1, Sstr2</t>
+          <t>Gad1, Gad2, Slc17a6, Slc32a1</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Cckbr(spec=0.08, log2=4.87, pct=73%, status=keep)</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>Cckbr[paper+allen_keep, spec=+0.08, log2=4.87, pct=73%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.34, log2=8.47, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.59, log2=9.02, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-0.90, log2=7.68, pct=94%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-0.82, log2=10.48, pct=100%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-6.50, log2=5.66, pct=83%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Htr2a[paper_only_allen_downgrade, spec=-4.91, log2=2.84, pct=45%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Npy1r[paper_only_allen_downgrade, spec=-2.34, log2=4.06, pct=64%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-3.19, log2=1.39, pct=25%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-3.60, log2=2.01, pct=35%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-7.42, log2=0.37, pct=7%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
-        </is>
-      </c>
+          <t>Cckbr, Cnr1, Crhr1, Gabbr1, Gabbr2, Gpr101, Grm5, Htr2c, Npy1r, Oprd1, Oprm1, Sstr2, Tacr1</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>both_keep: Cckbr | paper+broadly_detectable: Gabbr1, Gabbr2, Grm1, Grm5 | paper_only: Cnr1(downgrade,spec=-6.50,log2=5.66); Htr2a(downgrade,spec=-4.91,log2=2.84); Npy1r(downgrade,spec=-2.34,log2=4.06); Oprd1(downgrade,spec=-3.19,log2=1.39); Oprm1(downgrade,spec=-3.60,log2=2.01); Sstr2(downgrade,spec=-7.42,log2=0.37)</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>1</v>
+          <t>Gabbr1[paper+allen_broadly_detectable, spec=-0.61, log2=8.28, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.53, log2=8.38, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-1.12, log2=10.36, pct=100%; drugs: research_only_or_none]; Oprm1[paper+allen_broadly_detectable, spec=-1.67, log2=5.73, pct=82%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Cckbr[paper_only_allen_downgrade, spec=-3.22, log2=3.22, pct=56%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-10.94, log2=0.57, pct=10%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Crhr1[paper_only_allen_downgrade, spec=-1.36, log2=2.19, pct=39%; drugs: research_only_or_none]; Gpr101[paper_only_allen_downgrade, spec=-3.42, log2=3.57, pct=57%; drugs: research_only_or_none]; Htr2c[paper_only_allen_downgrade, spec=-2.20, log2=7.38, pct=87%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Npy1r[paper_only_allen_downgrade, spec=-3.62, log2=3.71, pct=62%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-3.55, log2=1.98, pct=36%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-2.28, log2=2.47, pct=44%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]; Tacr1[paper_only_allen_downgrade, spec=-6.77, log2=0.19, pct=4%; drugs: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet)]</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>paper+broadly_detectable: Gabbr1, Gabbr2, Grm5, Oprm1 | paper_only: Cckbr(downgrade,spec=-3.22,log2=3.22); Cnr1(downgrade,spec=-10.94,log2=0.57); Crhr1(downgrade,spec=-1.36,log2=2.19); Gpr101(downgrade,spec=-3.42,log2=3.57); Htr2c(downgrade,spec=-2.20,log2=7.38); Npy1r(downgrade,spec=-3.62,log2=3.71); Oprd1(downgrade,spec=-3.55,log2=1.98); Sstr2(downgrade,spec=-2.28,log2=2.47); Tacr1(downgrade,spec=-6.77,log2=0.19)</t>
+        </is>
       </c>
       <c r="L13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Crhr1 | clinical/research: Verucerfont; Pexacerfont; Antalarmin; Emicerfont (depression/PTSD trials mostly failed) | indication: PTSD; major depression; alcohol use disorder (mostly failed) || Gpr101 | clinical/research: research only (orphan) | indication: X-LAG / X-linked acrogigantism research || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease || Tacr1 | FDA: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet) | indication: chemotherapy-induced nausea/vomiting (CINV); postoperative nausea</t>
+        </is>
+      </c>
       <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="110" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>AId</t>
+          <t>BMAp</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Upper-layer IT excitatory</t>
+          <t>BMA/MEA VGLUT2-like excitatory</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>007 L2/3 IT CTX Glut</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>7697</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Cux1, Cux2, Rorb, Slc17a7</t>
-        </is>
+          <t>120 MEA Otp Foxp2 Glut</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1504</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Gad1, Slc32a1</t>
+          <t>Foxp2, Otp, Slc17a6, Tac2, Zic2</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Cckbr, Cnr1, Gabbr1, Gabbr2, Grm5, Htr2a, Npy1r, Oprd1, Oprm1, Sstr2</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Gpr88(spec=0.33, log2=4.77, pct=74%, status=keep)</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Gpr88[allen_only_keep, spec=+0.33, log2=4.77, pct=74%; drugs: research_only_or_none]; Cckbr[paper+allen_broadly_detectable, spec=-1.05, log2=4.52, pct=71%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.76, log2=8.52, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.45, log2=9.12, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-0.28, log2=10.52, pct=100%; drugs: research_only_or_none]; Grm1[allen_only_broadly_detectable, spec=-0.92, log2=7.76, pct=96%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-6.83, log2=5.24, pct=81%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Htr2a[paper_only_allen_downgrade, spec=-2.79, log2=4.48, pct=69%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Npy1r[paper_only_allen_downgrade, spec=-2.04, log2=3.75, pct=62%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-2.71, log2=1.63, pct=30%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-4.68, log2=2.21, pct=39%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-6.30, log2=0.56, pct=11%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
-        </is>
-      </c>
+          <t>Gad1, Slc17a7, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Gpr88 | paper+broadly_detectable: Cckbr, Gabbr1, Gabbr2, Grm5 | allen_only_broadly_detectable: Grm1 | paper_only: Cnr1(downgrade,spec=-6.83,log2=5.24); Htr2a(downgrade,spec=-2.79,log2=4.48); Npy1r(downgrade,spec=-2.04,log2=3.75); Oprd1(downgrade,spec=-2.71,log2=1.63); Oprm1(downgrade,spec=-4.68,log2=2.21); Sstr2(downgrade,spec=-6.30,log2=0.56)</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>1</v>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.44, log2=8.44, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-1.36, log2=10.12, pct=100%; drugs: research_only_or_none]; Htr2c[allen_only_broadly_detectable, spec=-0.39, log2=9.19, pct=98%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Oprm1[allen_only_broadly_detectable, spec=-0.67, log2=6.73, pct=92%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Gabbr1, Grm5, Htr2c, Oprm1</t>
+        </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>Gpr88 | clinical/research: RTI-13951-33 (research agonist) | indication: obsessive-compulsive disorder; addiction (preclinical) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="110" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>AId</t>
+          <t>BMAp</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Upper-layer IT excitatory</t>
+          <t>BMA/MEA VGLUT2-like excitatory</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>006 L4/5 IT CTX Glut</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>12177</v>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Cux1, Cux2, Rorb, Slc17a7</t>
-        </is>
+          <t>121 MEA-BST Otp Zic2 Glut</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1255</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Gad1, Slc32a1</t>
+          <t>Foxp2, Otp, Slc17a6, Tac2, Zic2</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Cckbr, Cnr1, Gabbr1, Gabbr2, Grm5, Htr2a, Npy1r, Oprd1, Oprm1, Sstr2</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Crhr1(spec=0.13, log2=3.94, pct=64%, status=keep)</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Crhr1[allen_only_keep, spec=+0.13, log2=3.94, pct=64%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.58, log2=8.70, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.61, log2=8.96, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-1.07, log2=9.73, pct=100%; drugs: research_only_or_none]; Htr2a[paper+allen_broadly_detectable, spec=-0.69, log2=6.59, pct=91%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Htr1f[allen_only_broadly_detectable, spec=-1.26, log2=6.28, pct=86%; drugs: Lasmiditan (Reyvow; FDA 2019)]; Cckbr[paper_only_allen_downgrade, spec=-1.60, log2=3.96, pct=64%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-5.56, log2=6.51, pct=89%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Npy1r[paper_only_allen_downgrade, spec=-2.45, log2=3.34, pct=56%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-3.12, log2=1.22, pct=22%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-4.84, log2=2.05, pct=36%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-5.69, log2=1.16, pct=20%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
-        </is>
-      </c>
+          <t>Gad1, Slc17a7, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Crhr1 | paper+broadly_detectable: Gabbr1, Gabbr2, Grm5, Htr2a | allen_only_broadly_detectable: Htr1f | paper_only: Cckbr(downgrade,spec=-1.60,log2=3.96); Cnr1(downgrade,spec=-5.56,log2=6.51); Npy1r(downgrade,spec=-2.45,log2=3.34); Oprd1(downgrade,spec=-3.12,log2=1.22); Oprm1(downgrade,spec=-4.84,log2=2.05); Sstr2(downgrade,spec=-5.69,log2=1.16)</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>1</v>
+          <t>Adcyap1r1[allen_only_broadly_detectable, spec=-1.63, log2=4.97, pct=79%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.48, log2=8.40, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.72, log2=8.18, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-0.58, log2=10.90, pct=100%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Gabbr2, Grm5</t>
+        </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>Crhr1 | clinical/research: Verucerfont; Pexacerfont; Antalarmin; Emicerfont (depression/PTSD trials mostly failed) | indication: PTSD; major depression; alcohol use disorder (mostly failed) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Htr1f | FDA: Lasmiditan (Reyvow; FDA 2019) | indication: migraine (acute attack) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="110" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>BMAp</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>CA1 pyramidal</t>
+          <t>BMA/MEA VGLUT2-like excitatory</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>016 CA1-ProS Glut</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>24868</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Fibcd1, Mpped1, Pou3f1, Slc17a7, Spink8, Wfs1</t>
-        </is>
+          <t>119 SI-MA-LPO-LHA Skor1 Glut</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>2180</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Calb1, Cnih3, Prox1, Rgs14</t>
+          <t>Foxp2, Otp, Slc17a6, Tac2, Zic2</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1, Cnr1, Drd1, Drd2, Gabbr1, Gabbr2, Grm1, Grm5, Htr1a, Htr1b, Htr2c, Oprm1, Sstr2</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Htr1a(spec=0.96, log2=3.33, pct=55%, status=keep); Mc4r(spec=0.08, log2=1.12, pct=21%, status=keep)</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>Htr1a[paper+allen_keep, spec=+0.96, log2=3.33, pct=55%; drugs: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone]; Mc4r[allen_only_keep, spec=+0.08, log2=1.12, pct=21%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Gabbr1[paper+allen_broadly_detectable, spec=-0.45, log2=8.70, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.96, log2=7.93, pct=96%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-1.93, log2=6.56, pct=85%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-0.36, log2=10.79, pct=100%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-4.69, log2=1.63, pct=29%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-7.05, log2=5.38, pct=80%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Drd1[paper_only_allen_downgrade, spec=-1.77, log2=0.02, pct=0%; drugs: Apomorphine (mixed); Pergolide (partial)]; Drd2[paper_only_allen_downgrade, spec=-1.50, log2=0.01, pct=0%; drugs: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect)]; Htr1b[paper_only_allen_downgrade, spec=-1.27, log2=2.14, pct=38%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Htr2c[paper_only_allen_downgrade, spec=-10.14, log2=1.80, pct=29%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Oprm1[paper_only_allen_downgrade, spec=-6.78, log2=0.18, pct=3%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-3.27, log2=0.51, pct=10%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
-        </is>
-      </c>
+          <t>Gad1, Slc17a7, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>both_keep: Htr1a | allen_only_keep: Mc4r | paper+broadly_detectable: Gabbr1, Gabbr2, Grm1, Grm5 | paper_only: Adcyap1r1(downgrade,spec=-4.69,log2=1.63); Cnr1(downgrade,spec=-7.05,log2=5.38); Drd1(downgrade,spec=-1.77,log2=0.02); Drd2(downgrade,spec=-1.50,log2=0.01); Htr1b(downgrade,spec=-1.27,log2=2.14); Htr2c(downgrade,spec=-10.14,log2=1.80); Oprm1(downgrade,spec=-6.78,log2=0.18); Sstr2(downgrade,spec=-3.27,log2=0.51)</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>2</v>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.53, log2=8.35, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm1[allen_only_broadly_detectable, spec=-1.66, log2=9.21, pct=97%; drugs: research_only_or_none]; Grm5[allen_only_broadly_detectable, spec=-1.82, log2=9.65, pct=99%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Gabbr1, Grm1, Grm5</t>
+        </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>Htr1a | FDA: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone | clinical/research: NLX-101 (depression) | indication: generalized anxiety; major depression || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Drd2 | FDA: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect) | clinical/research: many | indication: schizophrenia; bipolar; Parkinson disease; hyperprolactinemia || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 3 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="110" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>BMAp</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>CA2 pyramidal</t>
+          <t>Amygdala GABA / striatal-like inhibitory neighbors</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>025 CA2-FC-IG Glut</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>327</v>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Amigo2, Avpr1b, Cacng5, Map3k15, Pcp4, Rgs14, Slc17a7</t>
-        </is>
+          <t>073 MEA-BST Sox6 Gaba</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>8705</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Cnih3, Prox1, Wfs1</t>
+          <t>Ebf1, Gad1, Gad2, Lhx6, Slc32a1, Sox6, Sp9</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Avpr1a, Avpr1b, Cnr1, Drd1, Gabbr1, Gabbr2, Grm1, Grm5, Htr1a, Oxtr</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Avpr1b(spec=0.77, log2=0.81, pct=17%, status=keep_validate_spatially)</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>Avpr1b[paper+allen_keep, spec=+0.77, log2=0.81, pct=17%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.99, log2=8.16, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.64, log2=8.25, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-0.81, log2=10.35, pct=100%; drugs: research_only_or_none]; Avpr1a[paper_only_allen_downgrade, spec=-0.08, log2=0.03, pct=1%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-6.66, log2=5.77, pct=87%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Drd1[paper_only_allen_downgrade, spec=-0.64, log2=1.15, pct=21%; drugs: Apomorphine (mixed); Pergolide (partial)]; Grm1[paper_only_allen_downgrade, spec=-2.06, log2=6.43, pct=89%; drugs: research_only_or_none]; Htr1a[paper_only_allen_downgrade, spec=-3.00, log2=0.33, pct=7%; drugs: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone]; Oxtr[paper_only_allen_downgrade, spec=-0.07, log2=1.27, pct=24%; drugs: research_only_or_none]</t>
-        </is>
-      </c>
+          <t>Meis2, Slc17a6, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>both_keep: Avpr1b | paper+broadly_detectable: Gabbr1, Gabbr2, Grm5 | paper_only: Avpr1a(downgrade,spec=-0.08,log2=0.03); Cnr1(downgrade,spec=-6.66,log2=5.77); Drd1(downgrade,spec=-0.64,log2=1.15); Grm1(downgrade,spec=-2.06,log2=6.43); Htr1a(downgrade,spec=-3.00,log2=0.33); Oxtr(downgrade,spec=-0.07,log2=1.27)</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>1</v>
+          <t>Adcyap1r1[allen_only_broadly_detectable, spec=-1.92, log2=4.68, pct=76%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.62, log2=8.26, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.97, log2=7.93, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-1.12, log2=10.36, pct=100%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Gabbr2, Grm5</t>
+        </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>Avpr1b | clinical/research: Nelivaptan / SSR149415 (depression trials failed); ABT-558 | indication: major depression; PTSD; anxiety (failed/discontinued) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Htr1a | FDA: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone | clinical/research: NLX-101 (depression) | indication: generalized anxiety; major depression || Oxtr | clinical/research: Intranasal oxytocin (autism/social trials; mostly failed); Carbetocin (Pabal - postpartum hemorrhage outside USA) | indication: autism research; social cognition; postpartum hemorrhage (Carbetocin EU)</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="110" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>BMAp</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>CA3 pyramidal</t>
+          <t>Amygdala GABA / striatal-like inhibitory neighbors</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>017 CA3 Glut</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>4799</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Calb2, Cnih3, Coch, Lct, Slc17a7</t>
-        </is>
+          <t>074 MEA-BST Lhx6 Sp9 Gaba</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>6461</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Prox1, Rgs14, Wfs1</t>
+          <t>Ebf1, Gad1, Gad2, Lhx6, Slc32a1, Sox6, Sp9</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1, Cnr1, Drd2, Gabbr1, Gabbr2, Grm1, Grm5, Htr1a, Htr1b, Oprm1</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Npy2r(spec=2.24, log2=5.61, pct=85%, status=keep); Hcrtr1(spec=0.01, log2=0.28, pct=6%, status=candidate_to_validate)</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>Npy2r[allen_only_keep, spec=+2.24, log2=5.61, pct=85%; drugs: research_only_or_none]; Hcrtr1[allen_only_keep, spec=+0.01, log2=0.28, pct=6%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.90, log2=8.25, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.87, log2=9.02, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-1.10, log2=7.39, pct=93%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-0.96, log2=10.19, pct=100%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-5.28, log2=1.04, pct=20%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-5.87, log2=6.56, pct=94%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Drd2[paper_only_allen_downgrade, spec=-1.32, log2=0.19, pct=3%; drugs: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect)]; Htr1a[paper_only_allen_downgrade, spec=-1.93, log2=1.39, pct=28%; drugs: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone]; Htr1b[paper_only_allen_downgrade, spec=-3.36, log2=0.05, pct=1%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Oprm1[paper_only_allen_downgrade, spec=-6.77, log2=0.19, pct=4%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
-        </is>
-      </c>
+          <t>Meis2, Slc17a6, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Npy2r, Hcrtr1 | paper+broadly_detectable: Gabbr1, Gabbr2, Grm1, Grm5 | paper_only: Adcyap1r1(downgrade,spec=-5.28,log2=1.04); Cnr1(downgrade,spec=-5.87,log2=6.56); Drd2(downgrade,spec=-1.32,log2=0.19); Htr1a(downgrade,spec=-1.93,log2=1.39); Htr1b(downgrade,spec=-3.36,log2=0.05); Oprm1(downgrade,spec=-6.77,log2=0.19)</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>2</v>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.65, log2=8.23, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-1.09, log2=10.38, pct=100%; drugs: research_only_or_none]; Oprm1[allen_only_broadly_detectable, spec=-1.04, log2=6.36, pct=88%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Gabbr1, Grm5, Oprm1</t>
+        </is>
       </c>
       <c r="L18" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>Npy2r | clinical/research: BIIE-0246 (research antagonist) | indication: food intake; anxiety (preclinical) || Hcrtr1 | clinical/research: SB-334867 (research selective antagonist) | indication: addiction; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Drd2 | FDA: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect) | clinical/research: many | indication: schizophrenia; bipolar; Parkinson disease; hyperprolactinemia || Htr1a | FDA: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone | clinical/research: NLX-101 (depression) | indication: generalized anxiety; major depression || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 3 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="110" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Amygdala GABA / striatal-like inhibitory neighbors</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>082 CEA-BST Ebf1 Pdyn Gaba</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>6966</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Ebf1, Gad1, Gad2, Lhx6, Slc32a1, Sox6, Sp9</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Meis2, Slc17a6, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.44, log2=8.44, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gpr101[allen_only_broadly_detectable, spec=-1.33, log2=5.66, pct=79%; drugs: research_only_or_none]; Grm5[allen_only_broadly_detectable, spec=-1.42, log2=10.06, pct=99%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Gabbr1, Gpr101, Grm5</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gpr101 | clinical/research: research only (orphan) | indication: X-LAG / X-linked acrogigantism research || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 3 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="110" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Midline thalamic glutamatergic / reuniens</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>152 RE-Xi Nox4 Glut</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>5450</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Chrm2, Gabbr1, Gabbr2, Grm1, Grm5, Htr2a, Ntsr1, Ntsr2, Sstr2</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1[paper+allen_broadly_detectable, spec=-1.71, log2=9.35, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.58, log2=9.23, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-1.19, log2=8.82, pct=98%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-1.51, log2=10.02, pct=100%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-5.37, log2=2.78, pct=46%; drugs: research_only_or_none]; Chrm2[paper_only_allen_downgrade, spec=-2.93, log2=6.27, pct=81%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Htr2a[paper_only_allen_downgrade, spec=-3.09, log2=0.04, pct=1%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Ntsr1[paper_only_allen_downgrade, spec=-1.23, log2=0.33, pct=6%; drugs: research_only_or_none]; Ntsr2[paper_only_allen_downgrade, spec=-9.00, log2=0.04, pct=1%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-4.46, log2=0.20, pct=4%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>paper+broadly_detectable: Gabbr1, Gabbr2, Grm1, Grm5 | paper_only: Adcyap1r1(downgrade,spec=-5.37,log2=2.78); Chrm2(downgrade,spec=-2.93,log2=6.27); Htr2a(downgrade,spec=-3.09,log2=0.04); Ntsr1(downgrade,spec=-1.23,log2=0.33); Ntsr2(downgrade,spec=-9.00,log2=0.04); Sstr2(downgrade,spec=-4.46,log2=0.20)</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Ntsr1 | clinical/research: SR-48692 (research antagonist); SR-142948 | indication: thermal pain; addiction (preclinical) || Ntsr2 | clinical/research: research | indication: pain (preclinical) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="110" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Midline thalamic glutamatergic / reuniens</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>149 PVT-PT Ntrk1 Glut</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>9854</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Chrm2, Gabbr1, Gabbr2, Grm1, Grm5, Htr2a, Ntsr1, Ntsr2, Sstr2</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Oprk1(spec=1.42, log2=4.18, pct=66%, status=keep); Galr1(spec=0.23, log2=2.12, pct=35%, status=keep); Oxtr(spec=0.50, log2=1.89, pct=34%, status=keep)</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Oprk1[allen_only_keep, spec=+1.42, log2=4.18, pct=66%; drugs: Difelikefalin (Korsuva; FDA 2021)]; Galr1[allen_only_keep, spec=+0.23, log2=2.12, pct=35%; drugs: research_only_or_none]; Oxtr[allen_only_keep, spec=+0.50, log2=1.89, pct=34%; drugs: research_only_or_none]; Cnr1[allen_only_broadly_detectable, spec=-0.69, log2=5.48, pct=78%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Oprm1[allen_only_broadly_detectable, spec=-0.58, log2=6.85, pct=84%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Adcyap1r1[paper_only_allen_downgrade, spec=-2.91, log2=5.24, pct=81%; drugs: research_only_or_none]; Chrm2[paper_only_allen_downgrade, spec=-5.90, log2=3.30, pct=48%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Gabbr1[paper_only_allen_downgrade, spec=-2.30, log2=8.76, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper_only_allen_downgrade, spec=-2.01, log2=8.80, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper_only_allen_downgrade, spec=-2.93, log2=7.07, pct=87%; drugs: research_only_or_none]; Grm5[paper_only_allen_downgrade, spec=-2.67, log2=8.86, pct=99%; drugs: research_only_or_none]; Htr2a[paper_only_allen_downgrade, spec=-3.10, log2=0.03, pct=1%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Ntsr1[paper_only_allen_downgrade, spec=-1.24, log2=0.32, pct=6%; drugs: research_only_or_none]; Ntsr2[paper_only_allen_downgrade, spec=-8.68, log2=0.36, pct=7%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-4.18, log2=0.48, pct=9%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Oprk1, Galr1, Oxtr | allen_only_broadly_detectable: Cnr1, Oprm1 | paper_only: Adcyap1r1(downgrade,spec=-2.91,log2=5.24); Chrm2(downgrade,spec=-5.90,log2=3.30); Gabbr1(downgrade,spec=-2.30,log2=8.76); Gabbr2(downgrade,spec=-2.01,log2=8.80); Grm1(downgrade,spec=-2.93,log2=7.07); Grm5(downgrade,spec=-2.67,log2=8.86); Htr2a(downgrade,spec=-3.10,log2=0.03); Ntsr1(downgrade,spec=-1.24,log2=0.32); Ntsr2(downgrade,spec=-8.68,log2=0.36); Sstr2(downgrade,spec=-4.18,log2=0.48)</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Oprk1 | FDA: Difelikefalin (Korsuva; FDA 2021) | clinical/research: Nalfurafine (Japan); Buprenorphine (mixed); CR845 | indication: uremic pruritus (Difelikefalin); depression research || Galr1 | clinical/research: research only | indication: epilepsy; depression (preclinical) || Oxtr | clinical/research: Intranasal oxytocin (autism/social trials; mostly failed); Carbetocin (Pabal - postpartum hemorrhage outside USA) | indication: autism research; social cognition; postpartum hemorrhage (Carbetocin EU) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Ntsr1 | clinical/research: SR-48692 (research antagonist); SR-142948 | indication: thermal pain; addiction (preclinical) || Ntsr2 | clinical/research: research | indication: pain (preclinical) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="110" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Midline thalamic glutamatergic / reuniens</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>145 MH Tac2 Glut</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>7972</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Chrm2, Gabbr1, Gabbr2, Grm1, Grm5, Htr2a, Ntsr1, Ntsr2, Sstr2</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1(spec=1.44, log2=11.06, pct=100%, status=keep); Gabbr2(spec=0.83, log2=10.81, pct=99%, status=keep); Tacr1(spec=1.61, log2=6.00, pct=78%, status=keep); Sstr2(spec=2.64, log2=4.66, pct=68%, status=keep)</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1[paper+allen_keep, spec=+1.44, log2=11.06, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_keep, spec=+0.83, log2=10.81, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Sstr2[paper+allen_keep, spec=+2.64, log2=4.66, pct=68%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]; Tacr1[allen_only_keep, spec=+1.61, log2=6.00, pct=78%; drugs: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet)]; Adcyap1r1[paper_only_allen_downgrade, spec=-7.94, log2=0.22, pct=4%; drugs: research_only_or_none]; Chrm2[paper_only_allen_downgrade, spec=-8.87, log2=0.33, pct=5%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Grm1[paper_only_allen_downgrade, spec=-7.57, log2=2.43, pct=35%; drugs: research_only_or_none]; Grm5[paper_only_allen_downgrade, spec=-7.53, log2=3.99, pct=53%; drugs: research_only_or_none]; Htr2a[paper_only_allen_downgrade, spec=-2.68, log2=0.45, pct=7%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Ntsr1[paper_only_allen_downgrade, spec=-1.54, log2=0.02, pct=0%; drugs: research_only_or_none]; Ntsr2[paper_only_allen_downgrade, spec=-8.96, log2=0.08, pct=2%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>both_keep: Gabbr1, Gabbr2, Sstr2 | allen_only_keep: Tacr1 | paper_only: Adcyap1r1(downgrade,spec=-7.94,log2=0.22); Chrm2(downgrade,spec=-8.87,log2=0.33); Grm1(downgrade,spec=-7.57,log2=2.43); Grm5(downgrade,spec=-7.53,log2=3.99); Htr2a(downgrade,spec=-2.68,log2=0.45); Ntsr1(downgrade,spec=-1.54,log2=0.02); Ntsr2(downgrade,spec=-8.96,log2=0.08)</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease || Tacr1 | FDA: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet) | indication: chemotherapy-induced nausea/vomiting (CINV); postoperative nausea || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Ntsr1 | clinical/research: SR-48692 (research antagonist); SR-142948 | indication: thermal pain; addiction (preclinical) || Ntsr2 | clinical/research: research | indication: pain (preclinical)</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="110" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Reticular/inhibitory thalamic exclusion</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>093 RT-ZI Gnb3 Gaba</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>7452</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Gnb3, Otx2, Pvalb, Slc32a1</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Slc17a6, Slc17a7, Tcf7l2</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Chrm2[allen_only_broadly_detectable, spec=-1.96, log2=7.24, pct=88%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Chrm2</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 1 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="110" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Reticular/inhibitory thalamic exclusion</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>109 LGv-ZI Otx2 Gaba</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>4380</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Gnb3, Otx2, Pvalb, Slc32a1</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Slc17a6, Slc17a7, Tcf7l2</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Grm5[allen_only_broadly_detectable, spec=-1.36, log2=10.17, pct=99%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Grm5</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 1 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="110" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Lateral mammillary excitatory</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>144 MM Foxb1 Glut</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>8270</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Foxb1, Lhx5, Pou4f1</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Avpr1a, Cckbr, Gabbr1, Gabbr2, Grm1, Hcrtr1, Hcrtr2, Mc4r, Oxtr, Sstr2</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1[paper+allen_broadly_detectable, spec=-1.00, log2=8.28, pct=98%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.75, log2=8.35, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-0.13, log2=9.71, pct=100%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-4.76, log2=2.64, pct=47%; drugs: research_only_or_none]; Avpr1a[paper_only_allen_downgrade, spec=-2.15, log2=0.01, pct=0%; drugs: research_only_or_none]; Cckbr[paper_only_allen_downgrade, spec=-4.07, log2=0.28, pct=6%; drugs: research_only_or_none]; Hcrtr1[paper_only_allen_downgrade, spec=-1.61, log2=0.02, pct=0%; drugs: research_only_or_none]; Hcrtr2[paper_only_allen_downgrade, spec=-4.36, log2=1.25, pct=21%; drugs: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2]; Mc4r[paper_only_allen_downgrade, spec=-1.20, log2=0.00, pct=0%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Oxtr[paper_only_allen_downgrade, spec=-3.63, log2=0.01, pct=0%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-2.19, log2=0.37, pct=7%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>paper+broadly_detectable: Gabbr1, Gabbr2, Grm1 | paper_only: Adcyap1r1(downgrade,spec=-4.76,log2=2.64); Avpr1a(downgrade,spec=-2.15,log2=0.01); Cckbr(downgrade,spec=-4.07,log2=0.28); Hcrtr1(downgrade,spec=-1.61,log2=0.02); Hcrtr2(downgrade,spec=-4.36,log2=1.25); Mc4r(downgrade,spec=-1.20,log2=0.00); Oxtr(downgrade,spec=-3.63,log2=0.01); Sstr2(downgrade,spec=-2.19,log2=0.37)</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Hcrtr1 | clinical/research: SB-334867 (research selective antagonist) | indication: addiction; anxiety (preclinical) || Hcrtr2 | FDA: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2 | clinical/research: JNJ-42847922 (selective OX2R) | indication: insomnia || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Oxtr | clinical/research: Intranasal oxytocin (autism/social trials; mostly failed); Carbetocin (Pabal - postpartum hemorrhage outside USA) | indication: autism research; social cognition; postpartum hemorrhage (Carbetocin EU) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 3 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="110" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Lateral mammillary excitatory</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>143 MM-ant Foxb1 Glut</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>5437</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Foxb1, Lhx5, Pou4f1</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Avpr1a, Cckbr, Gabbr1, Gabbr2, Grm1, Hcrtr1, Hcrtr2, Mc4r, Oxtr, Sstr2</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Htr2a(spec=1.70, log2=5.18, pct=73%, status=keep)</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Htr2a[allen_only_keep, spec=+1.70, log2=5.18, pct=73%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Gabbr1[paper+allen_broadly_detectable, spec=-1.09, log2=8.19, pct=97%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.74, log2=8.36, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-0.99, log2=8.85, pct=97%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-4.46, log2=2.93, pct=49%; drugs: research_only_or_none]; Avpr1a[paper_only_allen_downgrade, spec=-2.15, log2=0.00, pct=0%; drugs: research_only_or_none]; Cckbr[paper_only_allen_downgrade, spec=-2.99, log2=1.36, pct=24%; drugs: research_only_or_none]; Hcrtr1[paper_only_allen_downgrade, spec=-1.58, log2=0.05, pct=1%; drugs: research_only_or_none]; Hcrtr2[paper_only_allen_downgrade, spec=-4.97, log2=0.64, pct=11%; drugs: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2]; Mc4r[paper_only_allen_downgrade, spec=-1.20, log2=0.01, pct=0%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Oxtr[paper_only_allen_downgrade, spec=-3.63, log2=0.00, pct=0%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-1.93, log2=0.63, pct=12%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Htr2a | paper+broadly_detectable: Gabbr1, Gabbr2, Grm1 | paper_only: Adcyap1r1(downgrade,spec=-4.46,log2=2.93); Avpr1a(downgrade,spec=-2.15,log2=0.00); Cckbr(downgrade,spec=-2.99,log2=1.36); Hcrtr1(downgrade,spec=-1.58,log2=0.05); Hcrtr2(downgrade,spec=-4.97,log2=0.64); Mc4r(downgrade,spec=-1.20,log2=0.01); Oxtr(downgrade,spec=-3.63,log2=0.00); Sstr2(downgrade,spec=-1.93,log2=0.63)</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Hcrtr1 | clinical/research: SB-334867 (research selective antagonist) | indication: addiction; anxiety (preclinical) || Hcrtr2 | FDA: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2 | clinical/research: JNJ-42847922 (selective OX2R) | indication: insomnia || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Oxtr | clinical/research: Intranasal oxytocin (autism/social trials; mostly failed); Carbetocin (Pabal - postpartum hemorrhage outside USA) | indication: autism research; social cognition; postpartum hemorrhage (Carbetocin EU) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="110" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic exclusion populations</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>132 AHN-RCH-LHA Otp Fezf1 Glut</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>4156</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Fezf1, Gad1, Gsx1, Otp, Pdrm12, Slc32a1</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Foxb1, Lhx5, Pou4f1</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.94, log2=8.33, pct=98%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-1.09, log2=10.18, pct=99%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Gabbr1, Grm5</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 2 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="110" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic exclusion populations</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>098 AHN-SBPV-PVHd Pdrm12 Gaba</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>7028</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Fezf1, Gad1, Gsx1, Otp, Pdrm12, Slc32a1</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Foxb1, Lhx5, Pou4f1</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-1.45, log2=7.83, pct=95%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-1.37, log2=9.89, pct=97%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Gabbr1, Grm5</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 2 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="110" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic exclusion populations</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>102 DMH-LHA Gsx1 Gaba</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>exclusion_counterstain</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>6768</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Fezf1, Gad1, Gsx1, Otp, Pdrm12, Slc32a1</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Foxb1, Lhx5, Pou4f1</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-1.59, log2=7.69, pct=94%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Gabbr1</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label)</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 1 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="110" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>L2/3 IT excitatory</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>007 L2/3 IT CTX Glut</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>8869</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Cdh13, Cux1, Cux2, Rorb, Satb2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Cckbr, Cnr1, Gabbr1, Gabbr2, Grm1, Grm5, Htr2a, Npy1r, Oprd1, Oprm1, Sstr2</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Cckbr(spec=0.08, log2=4.87, pct=73%, status=keep)</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Cckbr[paper+allen_keep, spec=+0.08, log2=4.87, pct=73%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.34, log2=8.47, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.59, log2=9.02, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-0.90, log2=7.68, pct=94%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-0.82, log2=10.48, pct=100%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-6.50, log2=5.66, pct=83%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Htr2a[paper_only_allen_downgrade, spec=-4.91, log2=2.84, pct=45%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Npy1r[paper_only_allen_downgrade, spec=-2.34, log2=4.06, pct=64%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-3.19, log2=1.39, pct=25%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-3.60, log2=2.01, pct=35%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-7.42, log2=0.37, pct=7%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>both_keep: Cckbr | paper+broadly_detectable: Gabbr1, Gabbr2, Grm1, Grm5 | paper_only: Cnr1(downgrade,spec=-6.50,log2=5.66); Htr2a(downgrade,spec=-4.91,log2=2.84); Npy1r(downgrade,spec=-2.34,log2=4.06); Oprd1(downgrade,spec=-3.19,log2=1.39); Oprm1(downgrade,spec=-3.60,log2=2.01); Sstr2(downgrade,spec=-7.42,log2=0.37)</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="110" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>L5 IT / L5 ET/PT output neurons</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>005 L5 IT CTX Glut</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>4419</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Bcl11b, Fezf2, Foxp2, Pcp4, Rprm, Slc17a7</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.23, log2=8.58, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.38, log2=9.23, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-1.77, log2=9.53, pct=100%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Gabbr1, Gabbr2, Grm5</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 3 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="110" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>L5 IT / L5 ET/PT output neurons</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>022 L5 ET CTX Glut</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Bcl11b, Fezf2, Foxp2, Pcp4, Rprm, Slc17a7</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1(spec=0.11, log2=8.81, pct=100%, status=keep); Mc4r(spec=0.81, log2=1.11, pct=20%, status=keep)</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1[allen_only_keep, spec=+0.11, log2=8.81, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Mc4r[allen_only_keep, spec=+0.81, log2=1.11, pct=20%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Cckbr[allen_only_broadly_detectable, spec=-0.08, log2=4.78, pct=74%; drugs: research_only_or_none]; Gabbr2[allen_only_broadly_detectable, spec=-1.65, log2=7.96, pct=98%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-0.87, log2=10.43, pct=100%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Gabbr1, Mc4r | allen_only_broadly_detectable: Cckbr, Gabbr2, Grm5</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="110" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>L5 IT / L5 ET/PT output neurons</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>032 L5 NP CTX Glut</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>3988</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Bcl11b, Fezf2, Foxp2, Pcp4, Rprm, Slc17a7</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Htr2c(spec=1.12, log2=8.34, pct=90%, status=keep); Avpr1a(spec=0.38, log2=0.46, pct=8%, status=candidate_to_validate)</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Htr2c[allen_only_keep, spec=+1.12, log2=8.34, pct=90%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Avpr1a[allen_only_keep, spec=+0.38, log2=0.46, pct=8%; drugs: research_only_or_none]; Chrm2[allen_only_broadly_detectable, spec=-1.33, log2=7.84, pct=91%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Gabbr1[allen_only_broadly_detectable, spec=-0.98, log2=7.83, pct=96%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-0.25, log2=11.06, pct=100%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Htr2c, Avpr1a | allen_only_broadly_detectable: Chrm2, Gabbr1, Grm5</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="110" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>L6 CT / L6b</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>030 L6 CT CTX Glut</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>21453</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Cplx3, Ctgf, Foxp2, Nxph4, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.27, log2=8.53, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.48, log2=9.13, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-1.85, log2=9.46, pct=99%; drugs: research_only_or_none]; Htr1f[allen_only_broadly_detectable, spec=-1.80, log2=7.53, pct=94%; drugs: Lasmiditan (Reyvow; FDA 2019)]; Oprm1[allen_only_broadly_detectable, spec=-0.83, log2=4.77, pct=72%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Gabbr1, Gabbr2, Grm5, Htr1f, Oprm1</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr1f | FDA: Lasmiditan (Reyvow; FDA 2019) | indication: migraine (acute attack) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 5 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="110" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>L6 CT / L6b</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>029 L6b CTX Glut</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>1586</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Cplx3, Ctgf, Foxp2, Nxph4, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Cckbr[allen_only_broadly_detectable, spec=-0.08, log2=4.79, pct=73%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.11, log2=8.69, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.35, log2=8.26, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Oprm1[allen_only_broadly_detectable, spec=-0.09, log2=5.51, pct=80%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Cckbr, Gabbr1, Gabbr2, Oprm1</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="110" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>L6 CT / L6b</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>004 L6 IT CTX Glut</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>11338</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Cplx3, Ctgf, Foxp2, Nxph4, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>Cckbr[allen_only_broadly_detectable, spec=-0.56, log2=4.31, pct=67%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.52, log2=8.29, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.26, log2=9.35, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[allen_only_broadly_detectable, spec=-1.93, log2=6.65, pct=88%; drugs: research_only_or_none]; Grm5[allen_only_broadly_detectable, spec=-1.57, log2=9.74, pct=100%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Cckbr, Gabbr1, Gabbr2, Grm1, Grm5</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 5 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="110" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>052 Pvalb Gaba</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Oprd1(spec=0.17, log2=4.58, pct=68%, status=keep)</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>Oprd1[allen_only_keep, spec=+0.17, log2=4.58, pct=68%; drugs: research_only_or_none]; Adcyap1r1[allen_only_broadly_detectable, spec=-0.75, log2=5.35, pct=77%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.97, log2=7.84, pct=96%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.82, log2=8.79, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-0.84, log2=10.46, pct=100%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Oprd1 | allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Gabbr2, Grm5</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="110" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>053 Sst Gaba</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>5377</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1[allen_only_broadly_detectable, spec=-0.35, log2=5.75, pct=80%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.38, log2=8.43, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.24, log2=8.36, pct=98%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[allen_only_broadly_detectable, spec=-0.02, log2=8.56, pct=94%; drugs: research_only_or_none]; Grm5[allen_only_broadly_detectable, spec=-1.33, log2=9.97, pct=100%; drugs: research_only_or_none]; Oprm1[allen_only_broadly_detectable, spec=-0.82, log2=4.78, pct=67%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5, Oprm1</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 6 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="110" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>046 Vip Gaba</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>3277</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1[allen_only_broadly_detectable, spec=-2.00, log2=4.11, pct=57%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-1.02, log2=7.79, pct=93%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Npy1r[allen_only_broadly_detectable, spec=-1.29, log2=5.11, pct=68%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Npy1r</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical)</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 3 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="110" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>049 Lamp5 Gaba</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>2339</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr2(spec=0.15, log2=9.61, pct=100%, status=keep)</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr2[allen_only_keep, spec=+0.15, log2=9.61, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Adcyap1r1[allen_only_broadly_detectable, spec=-1.66, log2=4.45, pct=66%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.50, log2=8.30, pct=98%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-0.89, log2=10.41, pct=100%; drugs: research_only_or_none]; Hcrtr2[allen_only_broadly_detectable, spec=-1.94, log2=5.08, pct=67%; drugs: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2]</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Gabbr2 | allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Grm5, Hcrtr2</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Hcrtr2 | FDA: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2 | clinical/research: JNJ-42847922 (selective OX2R) | indication: insomnia</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41" ht="110" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Upper-layer IT excitatory</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>007 L2/3 IT CTX Glut</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>7697</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Rorb, Slc17a7</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Cckbr, Cnr1, Gabbr1, Gabbr2, Grm5, Htr2a, Npy1r, Oprd1, Oprm1, Sstr2</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Gpr88(spec=0.33, log2=4.77, pct=74%, status=keep)</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>Gpr88[allen_only_keep, spec=+0.33, log2=4.77, pct=74%; drugs: research_only_or_none]; Cckbr[paper+allen_broadly_detectable, spec=-1.05, log2=4.52, pct=71%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.76, log2=8.52, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.45, log2=9.12, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-0.28, log2=10.52, pct=100%; drugs: research_only_or_none]; Grm1[allen_only_broadly_detectable, spec=-0.92, log2=7.76, pct=96%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-6.83, log2=5.24, pct=81%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Htr2a[paper_only_allen_downgrade, spec=-2.79, log2=4.48, pct=69%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Npy1r[paper_only_allen_downgrade, spec=-2.04, log2=3.75, pct=62%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-2.71, log2=1.63, pct=30%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-4.68, log2=2.21, pct=39%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-6.30, log2=0.56, pct=11%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Gpr88 | paper+broadly_detectable: Cckbr, Gabbr1, Gabbr2, Grm5 | allen_only_broadly_detectable: Grm1 | paper_only: Cnr1(downgrade,spec=-6.83,log2=5.24); Htr2a(downgrade,spec=-2.79,log2=4.48); Npy1r(downgrade,spec=-2.04,log2=3.75); Oprd1(downgrade,spec=-2.71,log2=1.63); Oprm1(downgrade,spec=-4.68,log2=2.21); Sstr2(downgrade,spec=-6.30,log2=0.56)</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Gpr88 | clinical/research: RTI-13951-33 (research agonist) | indication: obsessive-compulsive disorder; addiction (preclinical) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="110" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Upper-layer IT excitatory</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>006 L4/5 IT CTX Glut</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>12177</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Rorb, Slc17a7</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Slc32a1</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Cckbr, Cnr1, Gabbr1, Gabbr2, Grm5, Htr2a, Npy1r, Oprd1, Oprm1, Sstr2</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Crhr1(spec=0.13, log2=3.94, pct=64%, status=keep)</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Crhr1[allen_only_keep, spec=+0.13, log2=3.94, pct=64%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.58, log2=8.70, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.61, log2=8.96, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-1.07, log2=9.73, pct=100%; drugs: research_only_or_none]; Htr2a[paper+allen_broadly_detectable, spec=-0.69, log2=6.59, pct=91%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Htr1f[allen_only_broadly_detectable, spec=-1.26, log2=6.28, pct=86%; drugs: Lasmiditan (Reyvow; FDA 2019)]; Cckbr[paper_only_allen_downgrade, spec=-1.60, log2=3.96, pct=64%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-5.56, log2=6.51, pct=89%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Npy1r[paper_only_allen_downgrade, spec=-2.45, log2=3.34, pct=56%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-3.12, log2=1.22, pct=22%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-4.84, log2=2.05, pct=36%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-5.69, log2=1.16, pct=20%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Crhr1 | paper+broadly_detectable: Gabbr1, Gabbr2, Grm5, Htr2a | allen_only_broadly_detectable: Htr1f | paper_only: Cckbr(downgrade,spec=-1.60,log2=3.96); Cnr1(downgrade,spec=-5.56,log2=6.51); Npy1r(downgrade,spec=-2.45,log2=3.34); Oprd1(downgrade,spec=-3.12,log2=1.22); Oprm1(downgrade,spec=-4.84,log2=2.05); Sstr2(downgrade,spec=-5.69,log2=1.16)</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Crhr1 | clinical/research: Verucerfont; Pexacerfont; Antalarmin; Emicerfont (depression/PTSD trials mostly failed) | indication: PTSD; major depression; alcohol use disorder (mostly failed) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Htr1f | FDA: Lasmiditan (Reyvow; FDA 2019) | indication: migraine (acute attack) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr"/>
+      <c r="P42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="110" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Deep-layer output neurons</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>030 L6 CT CTX Glut</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>13072</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Bcl11b, Ctgf, Fezf2, Foxp2, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.73, log2=8.56, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.59, log2=8.98, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-1.39, log2=9.41, pct=99%; drugs: research_only_or_none]; Htr1f[allen_only_broadly_detectable, spec=-0.45, log2=7.10, pct=89%; drugs: Lasmiditan (Reyvow; FDA 2019)]</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Gabbr1, Gabbr2, Grm5, Htr1f</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr1f | FDA: Lasmiditan (Reyvow; FDA 2019) | indication: migraine (acute attack)</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="110" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Deep-layer output neurons</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>022 L5 ET CTX Glut</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>1134</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Bcl11b, Ctgf, Fezf2, Foxp2, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Htr1f(spec=0.14, log2=7.55, pct=97%, status=keep); Htr1b(spec=0.03, log2=2.33, pct=44%, status=keep); Mc4r(spec=1.84, log2=2.16, pct=41%, status=keep)</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>Htr1f[allen_only_keep, spec=+0.14, log2=7.55, pct=97%; drugs: Lasmiditan (Reyvow; FDA 2019)]; Htr1b[allen_only_keep, spec=+0.03, log2=2.33, pct=44%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Mc4r[allen_only_keep, spec=+1.84, log2=2.16, pct=41%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Cckbr[allen_only_broadly_detectable, spec=-0.20, log2=5.36, pct=84%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.32, log2=8.96, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.58, log2=7.99, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-0.24, log2=10.56, pct=100%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Htr1f, Htr1b, Mc4r | allen_only_broadly_detectable: Cckbr, Gabbr1, Gabbr2, Grm5</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Htr1f | FDA: Lasmiditan (Reyvow; FDA 2019) | indication: migraine (acute attack) || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="110" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Deep-layer output neurons</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>032 L5 NP CTX Glut</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>3409</v>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Bcl11b, Ctgf, Fezf2, Foxp2, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Grm5(spec=0.24, log2=10.80, pct=100%, status=keep); Avpr1a(spec=0.59, log2=0.63, pct=10%, status=keep_validate_spatially)</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Grm5[allen_only_keep, spec=+0.24, log2=10.80, pct=100%; drugs: research_only_or_none]; Avpr1a[allen_only_keep, spec=+0.59, log2=0.63, pct=10%; drugs: research_only_or_none]; Chrm2[allen_only_broadly_detectable, spec=-0.44, log2=7.82, pct=89%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Gabbr1[allen_only_broadly_detectable, spec=-1.47, log2=7.82, pct=95%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Htr2c[allen_only_broadly_detectable, spec=-0.14, log2=7.39, pct=83%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Grm5, Avpr1a | allen_only_broadly_detectable: Chrm2, Gabbr1, Htr2c</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="110" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Deep-layer output neurons</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>029 L6b CTX Glut</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>439</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Bcl11b, Ctgf, Fezf2, Foxp2, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>Cckbr[allen_only_broadly_detectable, spec=-0.41, log2=5.15, pct=78%; drugs: research_only_or_none]; Drd1[allen_only_broadly_detectable, spec=-0.56, log2=4.70, pct=74%; drugs: Apomorphine (mixed); Pergolide (partial)]; Gabbr1[allen_only_broadly_detectable, spec=-0.55, log2=8.74, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.39, log2=8.18, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-1.55, log2=9.25, pct=99%; drugs: research_only_or_none]; Oprm1[allen_only_broadly_detectable, spec=-1.78, log2=5.11, pct=76%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Cckbr, Drd1, Gabbr1, Gabbr2, Grm5, Oprm1</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 6 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="110" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>053 Sst Gaba</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>5983</v>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1[allen_only_broadly_detectable, spec=-0.00, log2=6.18, pct=84%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.84, log2=8.44, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.15, log2=8.42, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[allen_only_broadly_detectable, spec=-0.21, log2=8.47, pct=94%; drugs: research_only_or_none]; Grm5[allen_only_broadly_detectable, spec=-0.93, log2=9.87, pct=99%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 5 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="110" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>052 Pvalb Gaba</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>3617</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1[allen_only_broadly_detectable, spec=-0.74, log2=5.44, pct=77%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-1.33, log2=7.95, pct=97%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.74, log2=8.83, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-0.57, log2=10.24, pct=100%; drugs: research_only_or_none]; Oprd1[allen_only_broadly_detectable, spec=-0.24, log2=4.10, pct=61%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Gabbr2, Grm5, Oprd1</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical)</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 5 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="110" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>046 Vip Gaba</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>3706</v>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Gpr101(spec=0.07, log2=0.31, pct=5%, status=candidate_to_validate)</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>Gpr101[allen_only_keep, spec=+0.07, log2=0.31, pct=5%; drugs: research_only_or_none]; Adcyap1r1[allen_only_broadly_detectable, spec=-1.85, log2=4.34, pct=60%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-1.43, log2=7.85, pct=94%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-1.72, log2=9.08, pct=97%; drugs: research_only_or_none]; Npy1r[allen_only_broadly_detectable, spec=-0.99, log2=4.80, pct=65%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Gpr101 | allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Grm5, Npy1r</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Gpr101 | clinical/research: research only (orphan) | indication: X-LAG / X-linked acrogigantism research || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical)</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="110" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>049 Lamp5 Gaba</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>3704</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Gad1, Gad2, Lamp5, Pvalb, Slc32a1, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr2(spec=0.08, log2=9.57, pct=99%, status=keep); Gpr6(spec=0.20, log2=0.51, pct=9%, status=candidate_to_validate)</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr2[allen_only_keep, spec=+0.08, log2=9.57, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Gpr6[allen_only_keep, spec=+0.20, log2=0.51, pct=9%; drugs: research_only_or_none]; Adcyap1r1[allen_only_broadly_detectable, spec=-1.69, log2=4.49, pct=67%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.96, log2=8.33, pct=98%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-0.63, log2=10.17, pct=99%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Gabbr2, Gpr6 | allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Grm5</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Gpr6 | clinical/research: research antagonists for Parkinson disease | indication: Parkinson research (preclinical) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="110" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>CA1 pyramidal</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>016 CA1-ProS Glut</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>24868</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Fibcd1, Mpped1, Pou3f1, Slc17a7, Spink8, Wfs1</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Calb1, Cnih3, Prox1, Rgs14</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Cnr1, Drd1, Drd2, Gabbr1, Gabbr2, Grm1, Grm5, Htr1a, Htr1b, Htr2c, Oprm1, Sstr2</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Htr1a(spec=0.96, log2=3.33, pct=55%, status=keep); Mc4r(spec=0.08, log2=1.12, pct=21%, status=keep)</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>Htr1a[paper+allen_keep, spec=+0.96, log2=3.33, pct=55%; drugs: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone]; Mc4r[allen_only_keep, spec=+0.08, log2=1.12, pct=21%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Gabbr1[paper+allen_broadly_detectable, spec=-0.45, log2=8.70, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.96, log2=7.93, pct=96%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-1.93, log2=6.56, pct=85%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-0.36, log2=10.79, pct=100%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-4.69, log2=1.63, pct=29%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-7.05, log2=5.38, pct=80%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Drd1[paper_only_allen_downgrade, spec=-1.77, log2=0.02, pct=0%; drugs: Apomorphine (mixed); Pergolide (partial)]; Drd2[paper_only_allen_downgrade, spec=-1.50, log2=0.01, pct=0%; drugs: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect)]; Htr1b[paper_only_allen_downgrade, spec=-1.27, log2=2.14, pct=38%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Htr2c[paper_only_allen_downgrade, spec=-10.14, log2=1.80, pct=29%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Oprm1[paper_only_allen_downgrade, spec=-6.78, log2=0.18, pct=3%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-3.27, log2=0.51, pct=10%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>both_keep: Htr1a | allen_only_keep: Mc4r | paper+broadly_detectable: Gabbr1, Gabbr2, Grm1, Grm5 | paper_only: Adcyap1r1(downgrade,spec=-4.69,log2=1.63); Cnr1(downgrade,spec=-7.05,log2=5.38); Drd1(downgrade,spec=-1.77,log2=0.02); Drd2(downgrade,spec=-1.50,log2=0.01); Htr1b(downgrade,spec=-1.27,log2=2.14); Htr2c(downgrade,spec=-10.14,log2=1.80); Oprm1(downgrade,spec=-6.78,log2=0.18); Sstr2(downgrade,spec=-3.27,log2=0.51)</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Htr1a | FDA: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone | clinical/research: NLX-101 (depression) | indication: generalized anxiety; major depression || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Drd2 | FDA: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect) | clinical/research: many | indication: schizophrenia; bipolar; Parkinson disease; hyperprolactinemia || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr"/>
+      <c r="P51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52" ht="110" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>CA2 pyramidal</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>025 CA2-FC-IG Glut</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>327</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Amigo2, Avpr1b, Cacng5, Map3k15, Pcp4, Rgs14, Slc17a7</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Cnih3, Prox1, Wfs1</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Avpr1a, Avpr1b, Cnr1, Drd1, Gabbr1, Gabbr2, Grm1, Grm5, Htr1a, Oxtr</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Avpr1b(spec=0.77, log2=0.81, pct=17%, status=keep_validate_spatially)</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>Avpr1b[paper+allen_keep, spec=+0.77, log2=0.81, pct=17%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.99, log2=8.16, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.64, log2=8.25, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-0.81, log2=10.35, pct=100%; drugs: research_only_or_none]; Avpr1a[paper_only_allen_downgrade, spec=-0.08, log2=0.03, pct=1%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-6.66, log2=5.77, pct=87%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Drd1[paper_only_allen_downgrade, spec=-0.64, log2=1.15, pct=21%; drugs: Apomorphine (mixed); Pergolide (partial)]; Grm1[paper_only_allen_downgrade, spec=-2.06, log2=6.43, pct=89%; drugs: research_only_or_none]; Htr1a[paper_only_allen_downgrade, spec=-3.00, log2=0.33, pct=7%; drugs: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone]; Oxtr[paper_only_allen_downgrade, spec=-0.07, log2=1.27, pct=24%; drugs: research_only_or_none]</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>both_keep: Avpr1b | paper+broadly_detectable: Gabbr1, Gabbr2, Grm5 | paper_only: Avpr1a(downgrade,spec=-0.08,log2=0.03); Cnr1(downgrade,spec=-6.66,log2=5.77); Drd1(downgrade,spec=-0.64,log2=1.15); Grm1(downgrade,spec=-2.06,log2=6.43); Htr1a(downgrade,spec=-3.00,log2=0.33); Oxtr(downgrade,spec=-0.07,log2=1.27)</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Avpr1b | clinical/research: Nelivaptan / SSR149415 (depression trials failed); ABT-558 | indication: major depression; PTSD; anxiety (failed/discontinued) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Htr1a | FDA: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone | clinical/research: NLX-101 (depression) | indication: generalized anxiety; major depression || Oxtr | clinical/research: Intranasal oxytocin (autism/social trials; mostly failed); Carbetocin (Pabal - postpartum hemorrhage outside USA) | indication: autism research; social cognition; postpartum hemorrhage (Carbetocin EU)</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr"/>
+      <c r="P52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="110" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>CA3 pyramidal</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>017 CA3 Glut</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>4799</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Calb2, Cnih3, Coch, Lct, Slc17a7</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Prox1, Rgs14, Wfs1</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Cnr1, Drd2, Gabbr1, Gabbr2, Grm1, Grm5, Htr1a, Htr1b, Oprm1</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Npy2r(spec=2.24, log2=5.61, pct=85%, status=keep); Hcrtr1(spec=0.01, log2=0.28, pct=6%, status=candidate_to_validate)</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>Npy2r[allen_only_keep, spec=+2.24, log2=5.61, pct=85%; drugs: research_only_or_none]; Hcrtr1[allen_only_keep, spec=+0.01, log2=0.28, pct=6%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.90, log2=8.25, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.87, log2=9.02, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-1.10, log2=7.39, pct=93%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-0.96, log2=10.19, pct=100%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-5.28, log2=1.04, pct=20%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-5.87, log2=6.56, pct=94%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Drd2[paper_only_allen_downgrade, spec=-1.32, log2=0.19, pct=3%; drugs: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect)]; Htr1a[paper_only_allen_downgrade, spec=-1.93, log2=1.39, pct=28%; drugs: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone]; Htr1b[paper_only_allen_downgrade, spec=-3.36, log2=0.05, pct=1%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Oprm1[paper_only_allen_downgrade, spec=-6.77, log2=0.19, pct=4%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Npy2r, Hcrtr1 | paper+broadly_detectable: Gabbr1, Gabbr2, Grm1, Grm5 | paper_only: Adcyap1r1(downgrade,spec=-5.28,log2=1.04); Cnr1(downgrade,spec=-5.87,log2=6.56); Drd2(downgrade,spec=-1.32,log2=0.19); Htr1a(downgrade,spec=-1.93,log2=1.39); Htr1b(downgrade,spec=-3.36,log2=0.05); Oprm1(downgrade,spec=-6.77,log2=0.19)</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Npy2r | clinical/research: BIIE-0246 (research antagonist) | indication: food intake; anxiety (preclinical) || Hcrtr1 | clinical/research: SB-334867 (research selective antagonist) | indication: addiction; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Drd2 | FDA: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect) | clinical/research: many | indication: schizophrenia; bipolar; Parkinson disease; hyperprolactinemia || Htr1a | FDA: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone | clinical/research: NLX-101 (depression) | indication: generalized anxiety; major depression || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr"/>
+      <c r="P53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="110" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>DG granule cell</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>037 DG Glut</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
         <v>80255</v>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>C1ql2, Calb1, Dock10, Dsp, Prox1, Slc17a7</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>Cnih3, Rgs14, Wfs1</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>Adcyap1r1, Cnr1, Drd2, Gabbr1, Gabbr2, Grm1, Grm5, Htr1a, Htr2c</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>Grm1[paper+allen_broadly_detectable, spec=-0.06, log2=8.43, pct=93%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-0.98, log2=10.17, pct=99%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-2.92, log2=3.40, pct=47%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-11.77, log2=0.65, pct=10%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Drd2[paper_only_allen_downgrade, spec=-1.50, log2=0.00, pct=0%; drugs: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect)]; Gabbr1[paper_only_allen_downgrade, spec=-2.51, log2=6.64, pct=82%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper_only_allen_downgrade, spec=-2.13, log2=7.76, pct=89%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Htr1a[paper_only_allen_downgrade, spec=-2.62, log2=0.71, pct=11%; drugs: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone]; Htr2c[paper_only_allen_downgrade, spec=-11.79, log2=0.14, pct=2%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="K54" s="3" t="inlineStr">
         <is>
           <t>paper+broadly_detectable: Grm1, Grm5 | paper_only: Adcyap1r1(downgrade,spec=-2.92,log2=3.40); Cnr1(downgrade,spec=-11.77,log2=0.65); Drd2(downgrade,spec=-1.50,log2=0.00); Gabbr1(downgrade,spec=-2.51,log2=6.64); Gabbr2(downgrade,spec=-2.13,log2=7.76); Htr1a(downgrade,spec=-2.62,log2=0.71); Htr2c(downgrade,spec=-11.79,log2=0.14)</t>
         </is>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="L54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="M54" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="N54" s="3" t="inlineStr">
         <is>
           <t>Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Drd2 | FDA: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect) | clinical/research: many | indication: schizophrenia; bipolar; Parkinson disease; hyperprolactinemia || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Htr1a | FDA: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone | clinical/research: NLX-101 (depression) | indication: generalized anxiety; major depression || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O54" s="3" t="inlineStr"/>
+      <c r="P54" s="3" t="inlineStr">
         <is>
           <t>no cell-type-specific GPCR; relying on 2 broadly_expressed_detectable candidates</t>
         </is>

--- a/v3/outputs/FINAL_decision.xlsx
+++ b/v3/outputs/FINAL_decision.xlsx
@@ -36,7 +36,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -80,11 +80,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
@@ -112,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -141,13 +136,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1664,176 +1656,176 @@
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>BMAp</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Amygdala GABA / striatal-like inhibitory neighbors</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>073 MEA-BST Sox6 Gaba</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>exclusion_counterstain</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="n">
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
         <v>8705</v>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>Ebf1, Gad1, Gad2, Lhx6, Slc32a1, Sox6, Sp9</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Meis2, Slc17a6, Slc17a7</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>Adcyap1r1, Gabbr1, Gabbr2, Grm5</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>(counter-stain only; drugs not recommended)</t>
-        </is>
-      </c>
-      <c r="J17" s="10" t="n">
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="K17" s="10" t="inlineStr">
+      <c r="K17" s="9" t="inlineStr">
         <is>
           <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="L17" s="10" t="inlineStr">
-        <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>BMAp</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Amygdala GABA / striatal-like inhibitory neighbors</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>074 MEA-BST Lhx6 Sp9 Gaba</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>exclusion_counterstain</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="n">
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
         <v>6461</v>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>Ebf1, Gad1, Gad2, Lhx6, Slc32a1, Sox6, Sp9</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>Meis2, Slc17a6, Slc17a7</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>Gabbr1, Grm5, Oprm1</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>(counter-stain only; drugs not recommended)</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="n">
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Oprm1: Morphine (FDA)</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="K18" s="10" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="L18" s="10" t="inlineStr">
-        <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>BMAp</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Amygdala GABA / striatal-like inhibitory neighbors</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>082 CEA-BST Ebf1 Pdyn Gaba</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>exclusion_counterstain</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="n">
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
         <v>6966</v>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>Ebf1, Gad1, Gad2, Lhx6, Slc32a1, Sox6, Sp9</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>Meis2, Slc17a6, Slc17a7</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>Gabbr1, Gpr101, Grm5</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>(counter-stain only; drugs not recommended)</t>
-        </is>
-      </c>
-      <c r="J19" s="10" t="n">
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gpr101: (no clinical drugs) (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="K19" s="10" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>Gabbr1=allen_only_broadly_detectable; Gpr101=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="L19" s="10" t="inlineStr">
-        <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
@@ -2012,118 +2004,118 @@
       </c>
     </row>
     <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>RE</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Reticular/inhibitory thalamic exclusion</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Reticular/inhibitory thalamic neighbors</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>093 RT-ZI Gnb3 Gaba</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>exclusion_counterstain</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="n">
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n">
         <v>7452</v>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>Gad1, Gad2, Gnb3, Otx2, Pvalb, Slc32a1</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>Slc17a6, Slc17a7, Tcf7l2</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>Chrm2</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>(counter-stain only; drugs not recommended)</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="n">
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Chrm2: Donepezil (Aricept) (FDA 1996)</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>Chrm2=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>RE</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Reticular/inhibitory thalamic exclusion</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Reticular/inhibitory thalamic neighbors</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>109 LGv-ZI Otx2 Gaba</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>exclusion_counterstain</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="n">
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
         <v>4380</v>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>Gad1, Gad2, Gnb3, Otx2, Pvalb, Slc32a1</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>Slc17a6, Slc17a7, Tcf7l2</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>Grm5</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>(counter-stain only; drugs not recommended)</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="n">
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="K24" s="10" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="L24" s="10" t="inlineStr">
-        <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
@@ -2244,176 +2236,176 @@
       </c>
     </row>
     <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>LM</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Nearby hypothalamic exclusion populations</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic neighbors</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>132 AHN-RCH-LHA Otp Fezf1 Glut</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>exclusion_counterstain</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="n">
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n">
         <v>4156</v>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>Fezf1, Gad1, Gsx1, Otp, Pdrm12, Slc32a1</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>Foxb1, Lhx5, Pou4f1</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>Gabbr1, Grm5</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>(counter-stain only; drugs not recommended)</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="n">
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K27" s="10" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="L27" s="10" t="inlineStr">
-        <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>LM</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Nearby hypothalamic exclusion populations</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic neighbors</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>098 AHN-SBPV-PVHd Pdrm12 Gaba</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>exclusion_counterstain</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="n">
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n">
         <v>7028</v>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>Fezf1, Gad1, Gsx1, Otp, Pdrm12, Slc32a1</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>Foxb1, Lhx5, Pou4f1</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>Gabbr1, Grm5</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>(counter-stain only; drugs not recommended)</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="n">
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K28" s="10" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="L28" s="10" t="inlineStr">
-        <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>LM</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Nearby hypothalamic exclusion populations</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic neighbors</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>102 DMH-LHA Gsx1 Gaba</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>exclusion_counterstain</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="n">
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
         <v>6768</v>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>Fezf1, Gad1, Gsx1, Otp, Pdrm12, Slc32a1</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>Foxb1, Lhx5, Pou4f1</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>Gabbr1</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>(counter-stain only; drugs not recommended)</t>
-        </is>
-      </c>
-      <c r="J29" s="10" t="n">
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977)</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="K29" s="10" t="inlineStr">
+      <c r="K29" s="9" t="inlineStr">
         <is>
           <t>Gabbr1=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="L29" s="10" t="inlineStr">
-        <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3927,7 @@
           <t>exclusion_markers</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>paper_suggested_gpcrs</t>
         </is>
@@ -3970,7 +3962,7 @@
           <t>existing_drugs_for_picks</t>
         </is>
       </c>
-      <c r="O1" s="12" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>drugs_with_sources_per_picks</t>
         </is>
@@ -4983,7 +4975,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>target</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
@@ -5047,7 +5039,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>target</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
@@ -5111,7 +5103,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>target</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
@@ -5369,7 +5361,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Reticular/inhibitory thalamic exclusion</t>
+          <t>Reticular/inhibitory thalamic neighbors</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -5379,7 +5371,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>target</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
@@ -5433,7 +5425,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Reticular/inhibitory thalamic exclusion</t>
+          <t>Reticular/inhibitory thalamic neighbors</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -5443,7 +5435,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>target</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
@@ -5633,7 +5625,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Nearby hypothalamic exclusion populations</t>
+          <t>Nearby hypothalamic neighbors</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -5643,7 +5635,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>target</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
@@ -5697,7 +5689,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Nearby hypothalamic exclusion populations</t>
+          <t>Nearby hypothalamic neighbors</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5707,7 +5699,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>target</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
@@ -5761,7 +5753,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Nearby hypothalamic exclusion populations</t>
+          <t>Nearby hypothalamic neighbors</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -5771,7 +5763,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>target</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">

--- a/v3/outputs/FINAL_decision.xlsx
+++ b/v3/outputs/FINAL_decision.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINAL_Recommendations" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Table_full" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GPCR_Drug_References" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MarkerBased_Cluster_Recall" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -93,6 +94,11 @@
         <fgColor rgb="00B5A0DC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -112,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -149,6 +155,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -515,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -691,7 +700,7 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>All sheets</t>
+          <t>MarkerBased_Cluster_Recall</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -699,7 +708,44 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Generated from v3/outputs/Final_Probe_Panel_v7_modular.xlsx by D05_make_recommendations_workbook.py.</t>
+          <t>NEW: Paper-marker-based recall of Allen WMB clusters for LM, RE, BMAp (the 3 regions with broad ROI dissection). For each cell type, the top 5 Allen clusters that best match the paper marker signature are listed with net_score, pct_pos_avg, n_pos_markers_above_30pct, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>MarkerBased_Cluster_Recall</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Compare against the subclass anchor in CellType_Subclass_Anchors. If the recall returns a cluster from a DIFFERENT subclass than the v6 anchor, the paper marker set may be either (a) imprecise for the intended anatomical target, or (b) actually identifying a transcriptomically-related neighboring population. Inspect manually.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>All sheets</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Generated from v3/outputs/Final_Probe_Panel_v8_modular.xlsx by D05_make_recommendations_workbook.py. Cluster recall computed by A05_marker_based_cluster_recall.py.</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1808,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E17" s="10" t="n">
@@ -1790,7 +1836,7 @@
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>(counter-stain only; drugs not recommended)</t>
+          <t>(neighbor control / counter-stain; drugs not recommended)</t>
         </is>
       </c>
       <c r="K17" s="10" t="n">
@@ -1803,7 +1849,7 @@
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1871,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E18" s="10" t="n">
@@ -1853,7 +1899,7 @@
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>(counter-stain only; drugs not recommended)</t>
+          <t>(neighbor control / counter-stain; drugs not recommended)</t>
         </is>
       </c>
       <c r="K18" s="10" t="n">
@@ -1866,7 +1912,7 @@
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1934,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E19" s="10" t="n">
@@ -1916,7 +1962,7 @@
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>(counter-stain only; drugs not recommended)</t>
+          <t>(neighbor control / counter-stain; drugs not recommended)</t>
         </is>
       </c>
       <c r="K19" s="10" t="n">
@@ -1929,7 +1975,7 @@
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2186,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E23" s="10" t="n">
@@ -2168,7 +2214,7 @@
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>(counter-stain only; drugs not recommended)</t>
+          <t>(neighbor control / counter-stain; drugs not recommended)</t>
         </is>
       </c>
       <c r="K23" s="10" t="n">
@@ -2181,7 +2227,7 @@
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2249,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E24" s="10" t="n">
@@ -2231,7 +2277,7 @@
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>(counter-stain only; drugs not recommended)</t>
+          <t>(neighbor control / counter-stain; drugs not recommended)</t>
         </is>
       </c>
       <c r="K24" s="10" t="n">
@@ -2244,7 +2290,7 @@
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2438,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E27" s="10" t="n">
@@ -2420,7 +2466,7 @@
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>(counter-stain only; drugs not recommended)</t>
+          <t>(neighbor control / counter-stain; drugs not recommended)</t>
         </is>
       </c>
       <c r="K27" s="10" t="n">
@@ -2433,7 +2479,7 @@
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2501,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E28" s="10" t="n">
@@ -2483,7 +2529,7 @@
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
-          <t>(counter-stain only; drugs not recommended)</t>
+          <t>(neighbor control / counter-stain; drugs not recommended)</t>
         </is>
       </c>
       <c r="K28" s="10" t="n">
@@ -2496,7 +2542,7 @@
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2564,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E29" s="10" t="n">
@@ -2546,7 +2592,7 @@
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>(counter-stain only; drugs not recommended)</t>
+          <t>(neighbor control / counter-stain; drugs not recommended)</t>
         </is>
       </c>
       <c r="K29" s="10" t="n">
@@ -2559,7 +2605,7 @@
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
-          <t>EXCLUSION COUNTER-STAIN (not a probe target; use markers to confirm NOT this cell)</t>
+          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
         </is>
       </c>
     </row>
@@ -5327,7 +5373,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
@@ -5396,7 +5442,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
@@ -5465,7 +5511,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
@@ -5753,7 +5799,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
@@ -5822,7 +5868,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
@@ -6037,7 +6083,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
@@ -6106,7 +6152,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
@@ -6175,7 +6221,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>exclusion_counterstain</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
@@ -13268,4 +13314,2621 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>region_user</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>cell_type_label</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>subclass</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>supertype</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>n_cells_in_cluster</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>n_pos_markers_total</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>n_pos_markers_in_data</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>n_neg_markers_in_data</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>mean_pos_log2</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>mean_neg_log2</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>pct_pos_avg</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>pct_neg_avg</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>n_pos_above_30pct</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>frac_pos_above_30pct</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>net_score</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>specificity</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>rank_within_celltype</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Amygdala GABA / striatal-like inhibitory neighbors</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>0859 Sst Chodl Gaba_4</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>056 Sst Chodl Gaba</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>0241 Sst Chodl Gaba_4</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I2" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" s="10" t="n">
+        <v>5.0184</v>
+      </c>
+      <c r="L2" s="10" t="n">
+        <v>0.5298</v>
+      </c>
+      <c r="M2" s="10" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="N2" s="10" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="O2" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P2" s="10" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="Q2" s="10" t="n">
+        <v>4.8347</v>
+      </c>
+      <c r="R2" s="10" t="n">
+        <v>7.9677</v>
+      </c>
+      <c r="S2" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Amygdala GABA / striatal-like inhibitory neighbors</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>1258 MEA-BST Lhx6 Sp9 Gaba_5</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>074 MEA-BST Lhx6 Sp9 Gaba</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>0351 MEA-BST Lhx6 Sp9 Gaba_5</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>127</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>4.7215</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>0.5343</v>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>60.15</v>
+      </c>
+      <c r="N3" s="10" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="O3" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P3" s="10" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="Q3" s="10" t="n">
+        <v>4.5334</v>
+      </c>
+      <c r="R3" s="10" t="n">
+        <v>7.444</v>
+      </c>
+      <c r="S3" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Amygdala GABA / striatal-like inhibitory neighbors</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>0850 Sst Chodl Gaba_2</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>056 Sst Chodl Gaba</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>0239 Sst Chodl Gaba_2</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>4.571</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>0.6092</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="N4" s="10" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="O4" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" s="10" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="Q4" s="10" t="n">
+        <v>4.2695</v>
+      </c>
+      <c r="R4" s="10" t="n">
+        <v>6.4455</v>
+      </c>
+      <c r="S4" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Amygdala GABA / striatal-like inhibitory neighbors</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>0861 Sst Chodl Gaba_5</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>056 Sst Chodl Gaba</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>0242 Sst Chodl Gaba_5</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>4.2796</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="N5" s="10" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P5" s="10" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="Q5" s="10" t="n">
+        <v>4.2292</v>
+      </c>
+      <c r="R5" s="10" t="n">
+        <v>11.2291</v>
+      </c>
+      <c r="S5" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Amygdala GABA / striatal-like inhibitory neighbors</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>0852 Sst Chodl Gaba_2</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>056 Sst Chodl Gaba</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>0239 Sst Chodl Gaba_2</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>4.2963</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>0.5489000000000001</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>52.62</v>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="P6" s="10" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="Q6" s="10" t="n">
+        <v>4.0551</v>
+      </c>
+      <c r="R6" s="10" t="n">
+        <v>6.6211</v>
+      </c>
+      <c r="S6" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>BMA/MEA VGLUT2-like excitatory</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>2009 MEA-COA-BMA Ccdc42 Glut_3</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>113 MEA-COA-BMA Ccdc42 Glut</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>0507 MEA-COA-BMA Ccdc42 Glut_3</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>41</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>4.8852</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>0.5103</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>60.24</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="O7" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="P7" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q7" s="13" t="n">
+        <v>4.7249</v>
+      </c>
+      <c r="R7" s="13" t="n">
+        <v>8.0047</v>
+      </c>
+      <c r="S7" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>BMA/MEA VGLUT2-like excitatory</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>2008 MEA-COA-BMA Ccdc42 Glut_3</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>113 MEA-COA-BMA Ccdc42 Glut</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>0507 MEA-COA-BMA Ccdc42 Glut_3</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>1043</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>4.6242</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>0.6246</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>60.81</v>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="O8" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="P8" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q8" s="13" t="n">
+        <v>4.3997</v>
+      </c>
+      <c r="R8" s="13" t="n">
+        <v>6.3819</v>
+      </c>
+      <c r="S8" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>BMA/MEA VGLUT2-like excitatory</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>2207 MEA Otp Foxp2 Glut_1</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>120 MEA Otp Foxp2 Glut</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>0538 MEA Otp Foxp2 Glut_1</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>4.3625</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>0.5911999999999999</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>61.34</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="O9" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="P9" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q9" s="13" t="n">
+        <v>4.1213</v>
+      </c>
+      <c r="R9" s="13" t="n">
+        <v>6.3112</v>
+      </c>
+      <c r="S9" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>BMA/MEA VGLUT2-like excitatory</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>2204 MEA Otp Foxp2 Glut_1</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>120 MEA Otp Foxp2 Glut</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>0538 MEA Otp Foxp2 Glut_1</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>1215</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>4.4303</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>0.6271</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q10" s="13" t="n">
+        <v>4.1032</v>
+      </c>
+      <c r="R10" s="13" t="n">
+        <v>6.0932</v>
+      </c>
+      <c r="S10" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>BMA/MEA VGLUT2-like excitatory</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>2011 MEA-COA-BMA Ccdc42 Glut_4</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>113 MEA-COA-BMA Ccdc42 Glut</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>0508 MEA-COA-BMA Ccdc42 Glut_4</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>53</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>4.2159</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>0.5905</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="P11" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q11" s="13" t="n">
+        <v>4.0254</v>
+      </c>
+      <c r="R11" s="13" t="n">
+        <v>6.1052</v>
+      </c>
+      <c r="S11" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Posterior BMA glutamatergic / pallial amygdala VGLUT1</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>0192 MEA Slc17a7 Glut_1</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>012 MEA Slc17a7 Glut</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>0055 MEA Slc17a7 Glut_1</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>4.1162</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>0.6978</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="P12" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q12" s="13" t="n">
+        <v>3.7684</v>
+      </c>
+      <c r="R12" s="13" t="n">
+        <v>5.1593</v>
+      </c>
+      <c r="S12" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Posterior BMA glutamatergic / pallial amygdala VGLUT1</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>0200 MEA Slc17a7 Glut_1</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>012 MEA Slc17a7 Glut</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>0055 MEA Slc17a7 Glut_1</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>4.2872</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>1.1325</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q13" s="13" t="n">
+        <v>3.5048</v>
+      </c>
+      <c r="R13" s="13" t="n">
+        <v>3.4786</v>
+      </c>
+      <c r="S13" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Posterior BMA glutamatergic / pallial amygdala VGLUT1</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>0194 MEA Slc17a7 Glut_1</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>012 MEA Slc17a7 Glut</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>0055 MEA Slc17a7 Glut_1</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>3.885</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>1.1766</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="P14" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q14" s="13" t="n">
+        <v>3.0084</v>
+      </c>
+      <c r="R14" s="13" t="n">
+        <v>3.0432</v>
+      </c>
+      <c r="S14" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Posterior BMA glutamatergic / pallial amygdala VGLUT1</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>0227 LA-BLA-BMA-PA Glut_1</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>014 LA-BLA-BMA-PA Glut</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>0060 LA-BLA-BMA-PA Glut_1</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>3.1042</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q15" s="13" t="n">
+        <v>3.0042</v>
+      </c>
+      <c r="R15" s="13" t="n">
+        <v>7.7617</v>
+      </c>
+      <c r="S15" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>BMAp</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Posterior BMA glutamatergic / pallial amygdala VGLUT1</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>0212 MEA Slc17a7 Glut_2</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>012 MEA Slc17a7 Glut</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>0056 MEA Slc17a7 Glut_2</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>68</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>4.3103</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>1.6718</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="P16" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q16" s="13" t="n">
+        <v>2.9885</v>
+      </c>
+      <c r="R16" s="13" t="n">
+        <v>2.4328</v>
+      </c>
+      <c r="S16" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Lateral mammillary excitatory</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>2282 ARH-PVp Tbx3 Glut_3</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>126 ARH-PVp Tbx3 Glut</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>0556 ARH-PVp Tbx3 Glut_3</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>663</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>8.527699999999999</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>1.1941</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>96.61</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="P17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="13" t="n">
+        <v>7.8335</v>
+      </c>
+      <c r="R17" s="13" t="n">
+        <v>6.5895</v>
+      </c>
+      <c r="S17" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Lateral mammillary excitatory</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>2281 ARH-PVp Tbx3 Glut_3</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>126 ARH-PVp Tbx3 Glut</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>0556 ARH-PVp Tbx3 Glut_3</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>698</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>7.6839</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>1.493</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="P18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="13" t="n">
+        <v>6.6909</v>
+      </c>
+      <c r="R18" s="13" t="n">
+        <v>4.8236</v>
+      </c>
+      <c r="S18" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Lateral mammillary excitatory</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>2487 PH Pitx2 Glut_2</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>138 PH Pitx2 Glut</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>0611 PH Pitx2 Glut_2</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>5.5814</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>0.1934</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>68.13</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="P19" s="13" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="Q19" s="13" t="n">
+        <v>5.7769</v>
+      </c>
+      <c r="R19" s="13" t="n">
+        <v>19.0244</v>
+      </c>
+      <c r="S19" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Lateral mammillary excitatory</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>2562 PH-SUM Foxa1 Glut_6</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>141 PH-SUM Foxa1 Glut</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>0627 PH-SUM Foxa1 Glut_6</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>5.6269</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="P20" s="13" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>5.7111</v>
+      </c>
+      <c r="R20" s="13" t="n">
+        <v>13.9043</v>
+      </c>
+      <c r="S20" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Lateral mammillary excitatory</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>2489 PH Pitx2 Glut_2</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>138 PH Pitx2 Glut</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>0611 PH Pitx2 Glut_2</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>142</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>5.6068</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>0.4301</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>66.51000000000001</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="P21" s="13" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="R21" s="13" t="n">
+        <v>10.5766</v>
+      </c>
+      <c r="S21" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic exclusion populations</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>2568 MM-ant Foxb1 Glut_1</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>143 MM-ant Foxb1 Glut</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>0629 MM-ant Foxb1 Glut_1</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>2271</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>4.8759</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>2.2519</v>
+      </c>
+      <c r="M22" s="10" t="n">
+        <v>58.42</v>
+      </c>
+      <c r="N22" s="10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="O22" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P22" s="10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Q22" s="10" t="n">
+        <v>2.9365</v>
+      </c>
+      <c r="R22" s="10" t="n">
+        <v>2.0732</v>
+      </c>
+      <c r="S22" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic exclusion populations</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>2574 MM Foxb1 Glut_2</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>144 MM Foxb1 Glut</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>0631 MM Foxb1 Glut_2</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>3759</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>4.9588</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>2.3859</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="N23" s="10" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="O23" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P23" s="10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>2.8853</v>
+      </c>
+      <c r="R23" s="10" t="n">
+        <v>1.9947</v>
+      </c>
+      <c r="S23" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic exclusion populations</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>2569 MM-ant Foxb1 Glut_1</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>143 MM-ant Foxb1 Glut</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>0629 MM-ant Foxb1 Glut_1</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>139</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>4.928</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>2.3717</v>
+      </c>
+      <c r="M24" s="10" t="n">
+        <v>59.44</v>
+      </c>
+      <c r="N24" s="10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="O24" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P24" s="10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>2.8687</v>
+      </c>
+      <c r="R24" s="10" t="n">
+        <v>1.9937</v>
+      </c>
+      <c r="S24" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic exclusion populations</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>2565 MM-ant Foxb1 Glut_1</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>143 MM-ant Foxb1 Glut</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>0629 MM-ant Foxb1 Glut_1</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>846</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>4.8032</v>
+      </c>
+      <c r="L25" s="10" t="n">
+        <v>2.2876</v>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>59.06</v>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="O25" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P25" s="10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>2.8281</v>
+      </c>
+      <c r="R25" s="10" t="n">
+        <v>2.0117</v>
+      </c>
+      <c r="S25" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic exclusion populations</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>2572 MM Foxb1 Glut_1</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>144 MM Foxb1 Glut</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>0630 MM Foxb1 Glut_1</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>547</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>4.9711</v>
+      </c>
+      <c r="L26" s="10" t="n">
+        <v>2.4648</v>
+      </c>
+      <c r="M26" s="10" t="n">
+        <v>60.47</v>
+      </c>
+      <c r="N26" s="10" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="O26" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P26" s="10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Q26" s="10" t="n">
+        <v>2.8188</v>
+      </c>
+      <c r="R26" s="10" t="n">
+        <v>1.9382</v>
+      </c>
+      <c r="S26" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>Midline thalamic glutamatergic / reuniens</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>2660 TH Prkcd Grin2c Glut_6</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>151 TH Prkcd Grin2c Glut</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>0659 TH Prkcd Grin2c Glut_6</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>2407</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>9.663500000000001</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>0.1871</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="13" t="n">
+        <v>9.9764</v>
+      </c>
+      <c r="R27" s="13" t="n">
+        <v>33.6548</v>
+      </c>
+      <c r="S27" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Midline thalamic glutamatergic / reuniens</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>2654 TH Prkcd Grin2c Glut_4</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>151 TH Prkcd Grin2c Glut</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>0657 TH Prkcd Grin2c Glut_4</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>724</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I28" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>9.7659</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>98.06999999999999</v>
+      </c>
+      <c r="N28" s="13" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="13" t="n">
+        <v>9.9413</v>
+      </c>
+      <c r="R28" s="13" t="n">
+        <v>23.0002</v>
+      </c>
+      <c r="S28" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Midline thalamic glutamatergic / reuniens</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>2707 MG-POL-SGN Nts Glut_2</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>153 MG-POL-SGN Nts Glut</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>0673 MG-POL-SGN Nts Glut_2</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>9.507899999999999</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>0.1914</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>97.92</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="13" t="n">
+        <v>9.8164</v>
+      </c>
+      <c r="R29" s="13" t="n">
+        <v>32.6244</v>
+      </c>
+      <c r="S29" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Midline thalamic glutamatergic / reuniens</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>2667 TH Prkcd Grin2c Glut_7</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>151 TH Prkcd Grin2c Glut</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>0660 TH Prkcd Grin2c Glut_7</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>767</v>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I30" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>9.4495</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>96.77</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="13" t="n">
+        <v>9.7834</v>
+      </c>
+      <c r="R30" s="13" t="n">
+        <v>35.5195</v>
+      </c>
+      <c r="S30" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Midline thalamic glutamatergic / reuniens</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>2705 MG-POL-SGN Nts Glut_1</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>153 MG-POL-SGN Nts Glut</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>0672 MG-POL-SGN Nts Glut_1</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>815</v>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I31" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>9.5785</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="N31" s="13" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="O31" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="13" t="n">
+        <v>9.7783</v>
+      </c>
+      <c r="R31" s="13" t="n">
+        <v>23.9346</v>
+      </c>
+      <c r="S31" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Reticular/inhibitory thalamic exclusion</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>1592 RT-ZI Gnb3 Gaba_3</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>093 RT-ZI Gnb3 Gaba</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>0433 RT-ZI Gnb3 Gaba_3</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>496</v>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I32" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" s="10" t="n">
+        <v>6.6825</v>
+      </c>
+      <c r="L32" s="10" t="n">
+        <v>1.5571</v>
+      </c>
+      <c r="M32" s="10" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="N32" s="10" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="O32" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P32" s="10" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="Q32" s="10" t="n">
+        <v>5.554</v>
+      </c>
+      <c r="R32" s="10" t="n">
+        <v>4.0328</v>
+      </c>
+      <c r="S32" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Reticular/inhibitory thalamic exclusion</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>1604 RT-ZI Gnb3 Gaba_5</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>093 RT-ZI Gnb3 Gaba</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>0435 RT-ZI Gnb3 Gaba_5</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>159</v>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I33" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="10" t="n">
+        <v>6.7576</v>
+      </c>
+      <c r="L33" s="10" t="n">
+        <v>1.6887</v>
+      </c>
+      <c r="M33" s="10" t="n">
+        <v>67.92</v>
+      </c>
+      <c r="N33" s="10" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="O33" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P33" s="10" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="Q33" s="10" t="n">
+        <v>5.4974</v>
+      </c>
+      <c r="R33" s="10" t="n">
+        <v>3.7779</v>
+      </c>
+      <c r="S33" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Reticular/inhibitory thalamic exclusion</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>1594 RT-ZI Gnb3 Gaba_3</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>093 RT-ZI Gnb3 Gaba</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>0433 RT-ZI Gnb3 Gaba_3</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I34" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" s="10" t="n">
+        <v>6.4464</v>
+      </c>
+      <c r="L34" s="10" t="n">
+        <v>1.3998</v>
+      </c>
+      <c r="M34" s="10" t="n">
+        <v>70.73999999999999</v>
+      </c>
+      <c r="N34" s="10" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="O34" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P34" s="10" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="Q34" s="10" t="n">
+        <v>5.4752</v>
+      </c>
+      <c r="R34" s="10" t="n">
+        <v>4.2983</v>
+      </c>
+      <c r="S34" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Reticular/inhibitory thalamic exclusion</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>1593 RT-ZI Gnb3 Gaba_3</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>093 RT-ZI Gnb3 Gaba</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>0433 RT-ZI Gnb3 Gaba_3</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>1284</v>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I35" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" s="10" t="n">
+        <v>6.5799</v>
+      </c>
+      <c r="L35" s="10" t="n">
+        <v>1.5941</v>
+      </c>
+      <c r="M35" s="10" t="n">
+        <v>70.31999999999999</v>
+      </c>
+      <c r="N35" s="10" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="O35" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P35" s="10" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="Q35" s="10" t="n">
+        <v>5.4144</v>
+      </c>
+      <c r="R35" s="10" t="n">
+        <v>3.8841</v>
+      </c>
+      <c r="S35" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Reticular/inhibitory thalamic exclusion</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>1601 RT-ZI Gnb3 Gaba_5</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>093 RT-ZI Gnb3 Gaba</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>0435 RT-ZI Gnb3 Gaba_5</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>938</v>
+      </c>
+      <c r="H36" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I36" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" s="10" t="n">
+        <v>6.5652</v>
+      </c>
+      <c r="L36" s="10" t="n">
+        <v>1.6852</v>
+      </c>
+      <c r="M36" s="10" t="n">
+        <v>69.08</v>
+      </c>
+      <c r="N36" s="10" t="n">
+        <v>26.61</v>
+      </c>
+      <c r="O36" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P36" s="10" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="Q36" s="10" t="n">
+        <v>5.3086</v>
+      </c>
+      <c r="R36" s="10" t="n">
+        <v>3.6776</v>
+      </c>
+      <c r="S36" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/v3/outputs/FINAL_decision.xlsx
+++ b/v3/outputs/FINAL_decision.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
+          <t>Calb2, Nox4, Slc17a6, Spon1</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Gad1, Gad2, Pvalb, Slc32a1</t>
+          <t>Adcyap1, Gad1, Gad2, Grin2c, Necab1, Nts, Pou4f1, Prkcd, Pvalb, Slc32a1, Sox1, Sp9, Tnnt1</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
@@ -1816,35 +1816,35 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>149 PVT-PT Ntrk1 Glut</t>
+          <t>151 TH Prkcd Grin2c Glut</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
+          <t>Calb2, Nox4, Slc17a6, Spon1</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Gad1, Gad2, Pvalb, Slc32a1</t>
+          <t>Adcyap1, Gad1, Gad2, Grin2c, Necab1, Nts, Pou4f1, Prkcd, Pvalb, Slc32a1, Sox1, Sp9, Tnnt1</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Oprk1, Galr1, Oxtr, Cnr1, Oprm1</t>
+          <t>Grm1, Gabbr1, Gabbr2</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>Oprk1: Difelikefalin (Korsuva) (FDA 2021) | Galr1: M40 (galanin antagonist) (research) | Oxtr: Carbetocin (Pabal/Lonactene) (EU-only) | Cnr1: Dronabinol (Marinol; THC) (FDA 1985) | Oprm1: Morphine (FDA)</t>
+          <t>Grm1: JNJ-16259685 (research) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977)</t>
         </is>
       </c>
       <c r="H21" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>Oprk1=allen_only_keep; Galr1=allen_only_keep; Oxtr=allen_only_keep; Cnr1=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
+          <t>Grm1=paper+allen_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
@@ -1854,52 +1854,52 @@
       </c>
     </row>
     <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>RE</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Midline thalamic glutamatergic / reuniens</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>145 MH Tac2 Glut</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Gad1, Gad2, Pvalb, Slc32a1</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1, Gabbr2, Sstr2, Tacr1</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Sstr2: Octreotide (FDA 1988) | Tacr1: Aprepitant (Emend) (FDA 2003)</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1=paper+allen_keep; Gabbr2=paper+allen_keep; Sstr2=paper+allen_keep; Tacr1=allen_only_keep</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t>ORDER (cell-type-specific picks available)</t>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Reticular/inhibitory thalamic exclusion</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>093 RT-ZI Gnb3 Gaba</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Dlx1, Dlx2, Gad1, Gad2, Pvalb, Slc32a1, Sox14</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Calb2, Pcp4, Slc17a6, Slc17a7, Tcf7l2</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Chrm2</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>(neighbor control / counter-stain; drugs not recommended)</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>Chrm2=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>093 RT-ZI Gnb3 Gaba</t>
+          <t>109 LGv-ZI Otx2 Gaba</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>Chrm2</t>
+          <t>Grm5</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>Chrm2=allen_only_broadly_detectable</t>
+          <t>Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
@@ -1954,52 +1954,52 @@
       </c>
     </row>
     <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>RE</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Reticular/inhibitory thalamic exclusion</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>109 LGv-ZI Otx2 Gaba</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>Dlx1, Dlx2, Gad1, Gad2, Pvalb, Slc32a1, Sox14</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>Calb2, Pcp4, Slc17a6, Slc17a7, Tcf7l2</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>Grm5</t>
-        </is>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>(neighbor control / counter-stain; drugs not recommended)</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>Grm5=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Lateral mammillary excitatory</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>138 PH Pitx2 Glut</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Foxa1, Lmx1a, Nr4a2, Pdyn, Pitx2, Slc17a6, Snap25, Tac2</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Avp, Cartpt, Foxb1, Gad1, Gad2, Lhx1, Lhx5, Nhlh2, Nkx2-4, Npy, Nts, Otp, Pnoc, Pomc, Slc32a1, Tbx3, Uncx</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1, Grm5</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1=paper+allen_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
@@ -2016,90 +2016,90 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
+          <t>141 PH-SUM Foxa1 Glut</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Foxa1, Lmx1a, Nr4a2, Pdyn, Pitx2, Slc17a6, Snap25, Tac2</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Avp, Cartpt, Foxb1, Gad1, Gad2, Lhx1, Lhx5, Nhlh2, Nkx2-4, Npy, Nts, Otp, Pnoc, Pomc, Slc32a1, Tbx3, Uncx</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977)</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1=paper+allen_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic exclusion populations</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
           <t>144 MM Foxb1 Glut</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Esr1, Kcnc2, Nr4a2, Pdyn, Prlr, Slc17a6, Snap25, Syt4, Tac2</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>Foxb1, Gad1, Gad2, Slc32a1</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Avp, Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1, Lhx5, Nhlh2, Npy, Nts, Otp, Pnoc, Pomc, Uncx</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Foxa1, Lmx1a, Nr4a2, Pitx2, Slc17a6</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Gabbr1, Gabbr2, Grm1</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research)</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="n">
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>(neighbor control / counter-stain; drugs not recommended)</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>LM</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Lateral mammillary excitatory</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>143 MM-ant Foxb1 Glut</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>Esr1, Kcnc2, Nr4a2, Pdyn, Prlr, Slc17a6, Snap25, Syt4, Tac2</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>Foxb1, Gad1, Gad2, Slc32a1</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>Htr2a, Gabbr1, Gabbr2, Grm1</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>Htr2a: Pimavanserin (Nuplazid) (FDA 2016) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research)</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Htr2a=allen_only_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>ORDER (cell-type-specific picks available)</t>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
         </is>
       </c>
     </row>
@@ -2116,22 +2116,22 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>132 AHN-RCH-LHA Otp Fezf1 Glut</t>
+          <t>143 MM-ant Foxb1 Glut</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1os, Otp, Pdrm12, Rprm</t>
+          <t>Avp, Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1, Lhx5, Nhlh2, Npy, Nts, Otp, Pnoc, Pomc, Uncx</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Nr4a2, Prlr, Slc17a6, Tac2</t>
+          <t>Foxa1, Lmx1a, Nr4a2, Pitx2, Slc17a6</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>Gabbr1, Grm5</t>
+          <t>Htr2a, Gabbr1, Gabbr2, Grm1</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -2140,11 +2140,11 @@
         </is>
       </c>
       <c r="H27" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+          <t>Htr2a=allen_only_keep; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
@@ -2166,22 +2166,22 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>098 AHN-SBPV-PVHd Pdrm12 Gaba</t>
+          <t>126 ARH-PVp Tbx3 Glut</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1os, Otp, Pdrm12, Rprm</t>
+          <t>Avp, Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1, Lhx5, Nhlh2, Npy, Nts, Otp, Pnoc, Pomc, Uncx</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Nr4a2, Prlr, Slc17a6, Tac2</t>
+          <t>Foxa1, Lmx1a, Nr4a2, Pitx2, Slc17a6</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>Gabbr1, Grm5</t>
+          <t>Gabbr1</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -2190,11 +2190,11 @@
         </is>
       </c>
       <c r="H28" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+          <t>Gabbr1=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr">
@@ -2216,190 +2216,190 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
+          <t>132 AHN-RCH-LHA Otp Fezf1 Glut</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Avp, Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1, Lhx5, Nhlh2, Npy, Nts, Otp, Pnoc, Pomc, Uncx</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Foxa1, Lmx1a, Nr4a2, Pitx2, Slc17a6</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Gabbr1, Grm5</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>(neighbor control / counter-stain; drugs not recommended)</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic exclusion populations</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
           <t>102 DMH-LHA Gsx1 Gaba</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1os, Otp, Pdrm12, Rprm</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>Nr4a2, Prlr, Slc17a6, Tac2</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Avp, Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1, Lhx5, Nhlh2, Npy, Nts, Otp, Pnoc, Pomc, Uncx</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>Foxa1, Lmx1a, Nr4a2, Pitx2, Slc17a6</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Gabbr1</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>(neighbor control / counter-stain; drugs not recommended)</t>
         </is>
       </c>
-      <c r="H29" s="11" t="n">
+      <c r="H30" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I30" s="11" t="inlineStr">
         <is>
           <t>Gabbr1=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J30" s="11" t="inlineStr">
         <is>
           <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>ORBm</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>L2/3 IT excitatory</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>007 L2/3 IT CTX Glut</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>Calb1, Cdh13, Cux1, Cux2, Fst, Rorb, Satb2, Slc17a6, Slc17a7</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>Bcl11b, Foxp2, Gad1, Gad2, Slc32a1</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>Cckbr, Gabbr1, Gabbr2, Grm1, Grm5</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
-      <c r="H30" s="9" t="n">
+      <c r="H31" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>Cckbr=paper+allen_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>ORBm</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>L5 IT / L5 ET/PT output neurons</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>005 L5 IT CTX Glut</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>Bcl11b, Crym, Deptor, Etv1, Fam84b, Fezf2, Pde1c, Satb2, Slc17a7</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>Cux1, Cux2, Gad1, Rorb</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>Gabbr1, Gabbr2, Grm5</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
-      <c r="H31" s="10" t="n">
+      <c r="H32" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>ORBm</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>L5 IT / L5 ET/PT output neurons</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>022 L5 ET CTX Glut</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>Bcl11b, Crym, Deptor, Etv1, Fam84b, Fezf2, Pde1c, Satb2, Slc17a7</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>Cux1, Cux2, Gad1, Rorb</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1, Mc4r, Cckbr, Gabbr2, Grm5</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Mc4r: Setmelanotide (Imcivree) (FDA 2020) | Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1=allen_only_keep; Mc4r=allen_only_keep; Cckbr=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="J32" s="9" t="inlineStr">
-        <is>
-          <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>032 L5 NP CTX Glut</t>
+          <t>022 L5 ET CTX Glut</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -2431,12 +2431,12 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Htr2c, Avpr1a, Chrm2, Gabbr1, Grm5</t>
+          <t>Gabbr1, Mc4r, Cckbr, Gabbr2, Grm5</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>Htr2c: Lorcaserin (Belviq) (FDA) | Avpr1a: Balovaptan (RG7314) (clinical-trial) | Chrm2: Donepezil (Aricept) (FDA 1996) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Mc4r: Setmelanotide (Imcivree) (FDA 2020) | Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
       <c r="H33" s="9" t="n">
@@ -2444,62 +2444,62 @@
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
+          <t>Gabbr1=allen_only_keep; Mc4r=allen_only_keep; Cckbr=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>L5 IT / L5 ET/PT output neurons</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>032 L5 NP CTX Glut</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Bcl11b, Crym, Deptor, Etv1, Fam84b, Fezf2, Pde1c, Satb2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Htr2c, Avpr1a, Chrm2, Gabbr1, Grm5</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Htr2c: Lorcaserin (Belviq) (FDA) | Avpr1a: Balovaptan (RG7314) (clinical-trial) | Chrm2: Donepezil (Aricept) (FDA 1996) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
           <t>Htr2c=allen_only_keep; Avpr1a=allen_only_keep; Chrm2=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>ORBm</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>L6 CT / L6b</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>030 L6 CT CTX Glut</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>Ccn2, Cplx3, Ctgf, Foxp2, Ntsr1, Nxph4, Slc17a7, Tle4</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>Cux1, Cux2, Gad1, Rorb</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>Gabbr1, Gabbr2, Grm5, Htr1f, Oprm1</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Htr1f: Lasmiditan (Reyvow) (FDA 2019) | Oprm1: Morphine (FDA)</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Htr1f=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>029 L6b CTX Glut</t>
+          <t>030 L6 CT CTX Glut</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -2531,20 +2531,20 @@
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>Cckbr, Gabbr1, Gabbr2, Oprm1</t>
+          <t>Gabbr1, Gabbr2, Grm5, Htr1f, Oprm1</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Oprm1: Morphine (FDA)</t>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Htr1f: Lasmiditan (Reyvow) (FDA 2019) | Oprm1: Morphine (FDA)</t>
         </is>
       </c>
       <c r="H35" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>Cckbr=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
+          <t>Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Htr1f=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
@@ -2566,140 +2566,140 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
+          <t>029 L6b CTX Glut</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Ccn2, Cplx3, Ctgf, Foxp2, Ntsr1, Nxph4, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>Cckbr, Gabbr1, Gabbr2, Oprm1</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Oprm1: Morphine (FDA)</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Cckbr=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>L6 CT / L6b</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
           <t>004 L6 IT CTX Glut</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>Ccn2, Cplx3, Ctgf, Foxp2, Ntsr1, Nxph4, Slc17a7, Tle4</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>Cux1, Cux2, Gad1, Rorb</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>Cckbr, Gabbr1, Gabbr2, Grm1, Grm5</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
-      <c r="H36" s="10" t="n">
+      <c r="H37" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Cckbr=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="J36" s="10" t="inlineStr">
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>ORBm</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>Cortical interneurons</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>052 Pvalb Gaba</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>Cux1, Foxp2, Slc17a7</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>Oprd1, Adcyap1r1, Gabbr1, Gabbr2, Grm5</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>Oprd1: SNC80 (research) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
-      <c r="H37" s="9" t="n">
+      <c r="H38" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>Oprd1=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>ORBm</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Cortical interneurons</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>053 Sst Gaba</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>Cux1, Foxp2, Slc17a7</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
-        <is>
-          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
@@ -2716,127 +2716,127 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
+          <t>053 Sst Gaba</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
           <t>046 Vip Gaba</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>Cux1, Foxp2, Slc17a7</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>Adcyap1r1, Gabbr1, Npy1r</t>
         </is>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Npy1r: BIBP3226 (research)</t>
         </is>
       </c>
-      <c r="H39" s="10" t="n">
+      <c r="H40" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Npy1r=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="J39" s="10" t="inlineStr">
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>ORBm</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>Cortical interneurons</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>049 Lamp5 Gaba</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>Cux1, Foxp2, Slc17a7</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr2, Adcyap1r1, Gabbr1, Grm5, Hcrtr2</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr2: Baclofen (FDA 1977) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Hcrtr2: Suvorexant (Belsomra) (FDA 2014)</t>
-        </is>
-      </c>
-      <c r="H40" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr2=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Hcrtr2=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="60" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>AId</t>
+          <t>ORBm</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Upper-layer IT excitatory</t>
+          <t>Cortical interneurons</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>007 L2/3 IT CTX Glut</t>
+          <t>049 Lamp5 Gaba</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Calb1, Cux1, Cux2, Rorb, Satb2, Slc17a6, Slc17a7</t>
+          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>Bcl11b, Foxp2, Gad1, Gad2, Slc32a1</t>
+          <t>Cux1, Foxp2, Slc17a7</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Gpr88, Cckbr, Gabbr1, Gabbr2, Grm5</t>
+          <t>Gabbr2, Adcyap1r1, Gabbr1, Grm5, Hcrtr2</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>Gpr88: RTI-13951-33 (research) | Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+          <t>Gabbr2: Baclofen (FDA 1977) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Hcrtr2: Suvorexant (Belsomra) (FDA 2014)</t>
         </is>
       </c>
       <c r="H41" s="9" t="n">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>Gpr88=allen_only_keep; Cckbr=paper+allen_broadly_detectable; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
+          <t>Gabbr2=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Hcrtr2=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>006 L4/5 IT CTX Glut</t>
+          <t>007 L2/3 IT CTX Glut</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>Crhr1, Gabbr1, Gabbr2, Grm5, Htr2a</t>
+          <t>Gpr88, Cckbr, Gabbr1, Gabbr2, Grm5</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>Crhr1: Verucerfont (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Htr2a: Pimavanserin (Nuplazid) (FDA 2016)</t>
+          <t>Gpr88: RTI-13951-33 (research) | Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
       <c r="H42" s="9" t="n">
@@ -2894,112 +2894,112 @@
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
+          <t>Gpr88=allen_only_keep; Cckbr=paper+allen_broadly_detectable; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Upper-layer IT excitatory</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>006 L4/5 IT CTX Glut</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>Calb1, Cux1, Cux2, Rorb, Satb2, Slc17a6, Slc17a7</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>Bcl11b, Foxp2, Gad1, Gad2, Slc32a1</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Crhr1, Gabbr1, Gabbr2, Grm5, Htr2a</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>Crhr1: Verucerfont (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Htr2a: Pimavanserin (Nuplazid) (FDA 2016)</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
           <t>Crhr1=allen_only_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable; Htr2a=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="J42" s="9" t="inlineStr">
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>AId</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>Deep-layer output neurons</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>030 L6 CT CTX Glut</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>Bcl11b, Crym, Etv1, Fezf2, Foxp2, Ntsr1, Slc17a7, Tle4</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>Cux1, Cux2, Gad1, Rorb</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>Gabbr1, Gabbr2, Grm5, Htr1f</t>
         </is>
       </c>
-      <c r="G43" s="10" t="inlineStr">
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Htr1f: Lasmiditan (Reyvow) (FDA 2019)</t>
         </is>
       </c>
-      <c r="H43" s="10" t="n">
+      <c r="H44" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Htr1f=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr">
+      <c r="J44" s="10" t="inlineStr">
         <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>AId</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>Deep-layer output neurons</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>022 L5 ET CTX Glut</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>Bcl11b, Crym, Etv1, Fezf2, Foxp2, Ntsr1, Slc17a7, Tle4</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>Cux1, Cux2, Gad1, Rorb</t>
-        </is>
-      </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>Htr1f, Htr1b, Mc4r, Cckbr, Gabbr1</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>Htr1f: Lasmiditan (Reyvow) (FDA 2019) | Htr1b: Sumatriptan (FDA 1992) | Mc4r: Setmelanotide (Imcivree) (FDA 2020) | Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977)</t>
-        </is>
-      </c>
-      <c r="H44" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>Htr1f=allen_only_keep; Htr1b=allen_only_keep; Mc4r=allen_only_keep; Cckbr=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="J44" s="9" t="inlineStr">
-        <is>
-          <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>032 L5 NP CTX Glut</t>
+          <t>022 L5 ET CTX Glut</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -3031,12 +3031,12 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>Grm5, Avpr1a, Chrm2, Gabbr1, Htr2c</t>
+          <t>Htr1f, Htr1b, Mc4r, Cckbr, Gabbr1</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>Grm5: Mavoglurant (AFQ056) (clinical-trial) | Avpr1a: Balovaptan (RG7314) (clinical-trial) | Chrm2: Donepezil (Aricept) (FDA 1996) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Htr2c: Lorcaserin (Belviq) (FDA)</t>
+          <t>Htr1f: Lasmiditan (Reyvow) (FDA 2019) | Htr1b: Sumatriptan (FDA 1992) | Mc4r: Setmelanotide (Imcivree) (FDA 2020) | Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977)</t>
         </is>
       </c>
       <c r="H45" s="9" t="n">
@@ -3044,62 +3044,62 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
+          <t>Htr1f=allen_only_keep; Htr1b=allen_only_keep; Mc4r=allen_only_keep; Cckbr=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>Deep-layer output neurons</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>032 L5 NP CTX Glut</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>Bcl11b, Crym, Etv1, Fezf2, Foxp2, Ntsr1, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>Grm5, Avpr1a, Chrm2, Gabbr1, Htr2c</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>Grm5: Mavoglurant (AFQ056) (clinical-trial) | Avpr1a: Balovaptan (RG7314) (clinical-trial) | Chrm2: Donepezil (Aricept) (FDA 1996) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Htr2c: Lorcaserin (Belviq) (FDA)</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
           <t>Grm5=allen_only_keep; Avpr1a=allen_only_keep; Chrm2=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Htr2c=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="J45" s="9" t="inlineStr">
+      <c r="J46" s="9" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>AId</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>Deep-layer output neurons</t>
-        </is>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t>029 L6b CTX Glut</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>Bcl11b, Crym, Etv1, Fezf2, Foxp2, Ntsr1, Slc17a7, Tle4</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>Cux1, Cux2, Gad1, Rorb</t>
-        </is>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>Cckbr, Drd1, Gabbr1, Gabbr2, Grm5</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>Cckbr: Netazepide (YF476) (clinical-trial) | Drd1: Apomorphine (FDA) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>Cckbr=allen_only_broadly_detectable; Drd1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="J46" s="10" t="inlineStr">
-        <is>
-          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
@@ -3111,32 +3111,32 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Cortical interneurons</t>
+          <t>Deep-layer output neurons</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>053 Sst Gaba</t>
+          <t>029 L6b CTX Glut</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
+          <t>Bcl11b, Crym, Etv1, Fezf2, Foxp2, Ntsr1, Slc17a7, Tle4</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>Cux1, Foxp2, Slc17a7</t>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5</t>
+          <t>Cckbr, Drd1, Gabbr1, Gabbr2, Grm5</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+          <t>Cckbr: Netazepide (YF476) (clinical-trial) | Drd1: Apomorphine (FDA) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
       <c r="H47" s="10" t="n">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+          <t>Cckbr=allen_only_broadly_detectable; Drd1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>052 Pvalb Gaba</t>
+          <t>053 Sst Gaba</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm5, Oprd1</t>
+          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Oprd1: SNC80 (research)</t>
+          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
       <c r="H48" s="10" t="n">
@@ -3194,62 +3194,62 @@
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
+          <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>052 Pvalb Gaba</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm5, Oprd1</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Oprd1: SNC80 (research)</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
           <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Oprd1=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="J48" s="10" t="inlineStr">
+      <c r="J49" s="10" t="inlineStr">
         <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>AId</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>Cortical interneurons</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>046 Vip Gaba</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
-        </is>
-      </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>Cux1, Foxp2, Slc17a7</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>Gpr101, Adcyap1r1, Gabbr1, Grm5, Npy1r</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>Gpr101: (no clinical drugs) (research) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Npy1r: BIBP3226 (research)</t>
-        </is>
-      </c>
-      <c r="H49" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Gpr101=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Npy1r=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="J49" s="9" t="inlineStr">
-        <is>
-          <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>049 Lamp5 Gaba</t>
+          <t>046 Vip Gaba</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>Gabbr2, Gpr6, Adcyap1r1, Gabbr1, Grm5</t>
+          <t>Gpr101, Adcyap1r1, Gabbr1, Grm5, Npy1r</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>Gabbr2: Baclofen (FDA 1977) | Gpr6: CVN424 (Cerevance) (clinical-trial) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+          <t>Gpr101: (no clinical drugs) (research) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Npy1r: BIBP3226 (research)</t>
         </is>
       </c>
       <c r="H50" s="9" t="n">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>Gabbr2=allen_only_keep; Gpr6=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+          <t>Gpr101=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Npy1r=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="J50" s="9" t="inlineStr">
@@ -3306,37 +3306,37 @@
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>AId</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>CA1 pyramidal</t>
+          <t>Cortical interneurons</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>016 CA1-ProS Glut</t>
+          <t>049 Lamp5 Gaba</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Fibcd1, Mpped1, Pou3f1, Slc17a7, Spink8, Wfs1</t>
+          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Calb1, Cnih3, Prox1, Rgs14</t>
+          <t>Cux1, Foxp2, Slc17a7</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Htr1a, Mc4r, Gabbr1, Gabbr2, Grm1</t>
+          <t>Gabbr2, Gpr6, Adcyap1r1, Gabbr1, Grm5</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>Htr1a: Buspirone (FDA 1986) | Mc4r: Setmelanotide (Imcivree) (FDA 2020) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research)</t>
+          <t>Gabbr2: Baclofen (FDA 1977) | Gpr6: CVN424 (Cerevance) (clinical-trial) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
       <c r="H51" s="9" t="n">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>Htr1a=paper+allen_keep; Mc4r=allen_only_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable</t>
+          <t>Gabbr2=allen_only_keep; Gpr6=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="J51" s="9" t="inlineStr">
@@ -3361,40 +3361,40 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>CA2 pyramidal</t>
+          <t>CA1 pyramidal</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>025 CA2-FC-IG Glut</t>
+          <t>016 CA1-ProS Glut</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Amigo2, Avpr1b, Cacng5, Map3k15, Pcp4, Rgs14, Slc17a7</t>
+          <t>Fibcd1, Mpped1, Pou3f1, Slc17a7, Spink8, Wfs1</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Cnih3, Prox1, Wfs1</t>
+          <t>Calb1, Cnih3, Prox1, Rgs14</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>Avpr1b, Gabbr1, Gabbr2, Grm5</t>
+          <t>Htr1a, Mc4r, Gabbr1, Gabbr2, Grm1</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>Avpr1b: Nelivaptan (SSR149415) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+          <t>Htr1a: Buspirone (FDA 1986) | Mc4r: Setmelanotide (Imcivree) (FDA 2020) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research)</t>
         </is>
       </c>
       <c r="H52" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>Avpr1b=paper+allen_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
+          <t>Htr1a=paper+allen_keep; Mc4r=allen_only_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable</t>
         </is>
       </c>
       <c r="J52" s="9" t="inlineStr">
@@ -3411,93 +3411,143 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
+          <t>CA2 pyramidal</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>025 CA2-FC-IG Glut</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>Amigo2, Avpr1b, Cacng5, Map3k15, Pcp4, Rgs14, Slc17a7</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>Cnih3, Prox1, Wfs1</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>Avpr1b, Gabbr1, Gabbr2, Grm5</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>Avpr1b: Nelivaptan (SSR149415) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>Avpr1b=paper+allen_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
           <t>CA3 pyramidal</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>017 CA3 Glut</t>
         </is>
       </c>
-      <c r="D53" s="9" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>Calb2, Cnih3, Coch, Lct, Slc17a7</t>
         </is>
       </c>
-      <c r="E53" s="9" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
         <is>
           <t>Prox1, Rgs14, Wfs1</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
+      <c r="F54" s="9" t="inlineStr">
         <is>
           <t>Npy2r, Hcrtr1, Gabbr1, Gabbr2, Grm1</t>
         </is>
       </c>
-      <c r="G53" s="9" t="inlineStr">
+      <c r="G54" s="9" t="inlineStr">
         <is>
           <t>Npy2r: BIIE0246 (research) | Hcrtr1: SB-334867 (research) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research)</t>
         </is>
       </c>
-      <c r="H53" s="9" t="n">
+      <c r="H54" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="I53" s="9" t="inlineStr">
+      <c r="I54" s="9" t="inlineStr">
         <is>
           <t>Npy2r=allen_only_keep; Hcrtr1=allen_only_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="J53" s="9" t="inlineStr">
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>DG granule cell</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>037 DG Glut</t>
         </is>
       </c>
-      <c r="D54" s="10" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>C1ql2, Calb1, Dock10, Dsp, Prox1, Slc17a7</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>Cnih3, Rgs14, Wfs1</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>Grm1, Grm5</t>
         </is>
       </c>
-      <c r="G54" s="10" t="inlineStr">
+      <c r="G55" s="10" t="inlineStr">
         <is>
           <t>Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
-      <c r="H54" s="10" t="n">
+      <c r="H55" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>Grm1=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="J54" s="10" t="inlineStr">
+      <c r="J55" s="10" t="inlineStr">
         <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
@@ -3514,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4764,12 +4814,12 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
+          <t>Calb2, Nox4, Slc17a6, Spon1</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Gad1, Gad2, Pvalb, Slc32a1</t>
+          <t>Adcyap1, Gad1, Gad2, Grin2c, Necab1, Nts, Pou4f1, Prkcd, Pvalb, Slc32a1, Sox1, Sp9, Tnnt1</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -4809,7 +4859,7 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>149 PVT-PT Ntrk1 Glut</t>
+          <t>151 TH Prkcd Grin2c Glut</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -4818,7 +4868,7 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>9854</v>
+        <v>68125</v>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
@@ -4827,30 +4877,30 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
+          <t>Calb2, Nox4, Slc17a6, Spon1</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>Gad1, Gad2, Pvalb, Slc32a1</t>
+          <t>Adcyap1, Gad1, Gad2, Grin2c, Necab1, Nts, Pou4f1, Prkcd, Pvalb, Slc32a1, Sox1, Sp9, Tnnt1</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>Oprk1, Galr1, Oxtr, Cnr1, Oprm1</t>
+          <t>Grm1, Gabbr1, Gabbr2</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Oprk1: Difelikefalin (Korsuva) (FDA 2021) | Galr1: M40 (galanin antagonist) (research) | Oxtr: Carbetocin (Pabal/Lonactene) (EU-only) | Cnr1: Dronabinol (Marinol; THC) (FDA 1985) | Oprm1: Morphine (FDA)</t>
+          <t>Grm1: JNJ-16259685 (research) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977)</t>
         </is>
       </c>
       <c r="K21" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>Oprk1=allen_only_keep; Galr1=allen_only_keep; Oxtr=allen_only_keep; Cnr1=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
+          <t>Grm1=paper+allen_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable</t>
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
@@ -4860,65 +4910,65 @@
       </c>
     </row>
     <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>RE</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Midline thalamic glutamatergic / reuniens</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>145 MH Tac2 Glut</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>7972</v>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Reticular/inhibitory thalamic exclusion</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>093 RT-ZI Gnb3 Gaba</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>7452</v>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>PARTIAL: Allen ROI = TH (entire thalamus); subclass `152 RE-Xi Nox4 Glut` is the most RE-specific transcriptomic class but it covers both nucleus reuniens AND xiphoid nucleus.</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>Gad1, Gad2, Pvalb, Slc32a1</t>
-        </is>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1, Gabbr2, Sstr2, Tacr1</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Sstr2: Octreotide (FDA 1988) | Tacr1: Aprepitant (Emend) (FDA 2003)</t>
-        </is>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L22" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1=paper+allen_keep; Gabbr2=paper+allen_keep; Sstr2=paper+allen_keep; Tacr1=allen_only_keep</t>
-        </is>
-      </c>
-      <c r="M22" s="9" t="inlineStr">
-        <is>
-          <t>ORDER (cell-type-specific picks available)</t>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>Dlx1, Dlx2, Gad1, Gad2, Pvalb, Slc32a1, Sox14</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Calb2, Pcp4, Slc17a6, Slc17a7, Tcf7l2</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>Chrm2</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>(neighbor control / counter-stain; drugs not recommended)</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>Chrm2=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4985,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>093 RT-ZI Gnb3 Gaba</t>
+          <t>109 LGv-ZI Otx2 Gaba</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -4944,7 +4994,7 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>7452</v>
+        <v>4380</v>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
@@ -4963,7 +5013,7 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>Chrm2</t>
+          <t>Grm5</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
@@ -4976,7 +5026,7 @@
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>Chrm2=allen_only_broadly_detectable</t>
+          <t>Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
@@ -4986,65 +5036,65 @@
       </c>
     </row>
     <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>RE</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Reticular/inhibitory thalamic exclusion</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>109 LGv-ZI Otx2 Gaba</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>neighbor_control</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="n">
-        <v>4380</v>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>PARTIAL: Allen ROI = TH (entire thalamus); subclass `152 RE-Xi Nox4 Glut` is the most RE-specific transcriptomic class but it covers both nucleus reuniens AND xiphoid nucleus.</t>
-        </is>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>Dlx1, Dlx2, Gad1, Gad2, Pvalb, Slc32a1, Sox14</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>Calb2, Pcp4, Slc17a6, Slc17a7, Tcf7l2</t>
-        </is>
-      </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>Grm5</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>(neighbor control / counter-stain; drugs not recommended)</t>
-        </is>
-      </c>
-      <c r="K24" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>Grm5=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="M24" s="11" t="inlineStr">
-        <is>
-          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Lateral mammillary excitatory</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>138 PH Pitx2 Glut</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>1795</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>BROAD: Allen ROI = HY (entire hypothalamus). Subclass `144 MM Foxb1 Glut` and `143 MM-ant Foxb1 Glut` cover the WHOLE mammillary body (lateral + medial + supramammillary) - NOT lateral-specific. To restrict to LM, dissect lateral mammillary nucleus directly OR co-stain with LM-discriminating markers (Lhx5, Cck, Calb2 vs medial-mammillary markers).</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Foxa1, Lmx1a, Nr4a2, Pdyn, Pitx2, Slc17a6, Snap25, Tac2</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Avp, Cartpt, Foxb1, Gad1, Gad2, Lhx1, Lhx5, Nhlh2, Nkx2-4, Npy, Nts, Otp, Pnoc, Pomc, Slc32a1, Tbx3, Uncx</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1, Grm5</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1=paper+allen_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
@@ -5061,116 +5111,116 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
+          <t>141 PH-SUM Foxa1 Glut</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>2921</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>BROAD: Allen ROI = HY (entire hypothalamus). Subclass `144 MM Foxb1 Glut` and `143 MM-ant Foxb1 Glut` cover the WHOLE mammillary body (lateral + medial + supramammillary) - NOT lateral-specific. To restrict to LM, dissect lateral mammillary nucleus directly OR co-stain with LM-discriminating markers (Lhx5, Cck, Calb2 vs medial-mammillary markers).</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Foxa1, Lmx1a, Nr4a2, Pdyn, Pitx2, Slc17a6, Snap25, Tac2</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Avp, Cartpt, Foxb1, Gad1, Gad2, Lhx1, Lhx5, Nhlh2, Nkx2-4, Npy, Nts, Otp, Pnoc, Pomc, Slc32a1, Tbx3, Uncx</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977)</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>Gabbr1=paper+allen_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic exclusion populations</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
           <t>144 MM Foxb1 Glut</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="n">
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="n">
         <v>8270</v>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>BROAD: Allen ROI = HY (entire hypothalamus). Subclass `144 MM Foxb1 Glut` and `143 MM-ant Foxb1 Glut` cover the WHOLE mammillary body (lateral + medial + supramammillary) - NOT lateral-specific. To restrict to LM, dissect lateral mammillary nucleus directly OR co-stain with LM-discriminating markers (Lhx5, Cck, Calb2 vs medial-mammillary markers).</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>Esr1, Kcnc2, Nr4a2, Pdyn, Prlr, Slc17a6, Snap25, Syt4, Tac2</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>Foxb1, Gad1, Gad2, Slc32a1</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Avp, Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1, Lhx5, Nhlh2, Npy, Nts, Otp, Pnoc, Pomc, Uncx</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>Foxa1, Lmx1a, Nr4a2, Pitx2, Slc17a6</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>Gabbr1, Gabbr2, Grm1</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research)</t>
-        </is>
-      </c>
-      <c r="K25" s="10" t="n">
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>(neighbor control / counter-stain; drugs not recommended)</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="M25" s="10" t="inlineStr">
-        <is>
-          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>LM</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Lateral mammillary excitatory</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>143 MM-ant Foxb1 Glut</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>5437</v>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>BROAD: Allen ROI = HY (entire hypothalamus). Subclass `144 MM Foxb1 Glut` and `143 MM-ant Foxb1 Glut` cover the WHOLE mammillary body (lateral + medial + supramammillary) - NOT lateral-specific. To restrict to LM, dissect lateral mammillary nucleus directly OR co-stain with LM-discriminating markers (Lhx5, Cck, Calb2 vs medial-mammillary markers).</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>Esr1, Kcnc2, Nr4a2, Pdyn, Prlr, Slc17a6, Snap25, Syt4, Tac2</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>Foxb1, Gad1, Gad2, Slc32a1</t>
-        </is>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Htr2a, Gabbr1, Gabbr2, Grm1</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>Htr2a: Pimavanserin (Nuplazid) (FDA 2016) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research)</t>
-        </is>
-      </c>
-      <c r="K26" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L26" s="9" t="inlineStr">
-        <is>
-          <t>Htr2a=allen_only_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="M26" s="9" t="inlineStr">
-        <is>
-          <t>ORDER (cell-type-specific picks available)</t>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5237,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>132 AHN-RCH-LHA Otp Fezf1 Glut</t>
+          <t>143 MM-ant Foxb1 Glut</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -5196,7 +5246,7 @@
         </is>
       </c>
       <c r="E27" s="11" t="n">
-        <v>4156</v>
+        <v>5437</v>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
@@ -5205,17 +5255,17 @@
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1os, Otp, Pdrm12, Rprm</t>
+          <t>Avp, Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1, Lhx5, Nhlh2, Npy, Nts, Otp, Pnoc, Pomc, Uncx</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Nr4a2, Prlr, Slc17a6, Tac2</t>
+          <t>Foxa1, Lmx1a, Nr4a2, Pitx2, Slc17a6</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>Gabbr1, Grm5</t>
+          <t>Htr2a, Gabbr1, Gabbr2, Grm1</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
@@ -5224,11 +5274,11 @@
         </is>
       </c>
       <c r="K27" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+          <t>Htr2a=allen_only_keep; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
@@ -5250,7 +5300,7 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>098 AHN-SBPV-PVHd Pdrm12 Gaba</t>
+          <t>126 ARH-PVp Tbx3 Glut</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -5259,7 +5309,7 @@
         </is>
       </c>
       <c r="E28" s="11" t="n">
-        <v>7028</v>
+        <v>4103</v>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
@@ -5268,17 +5318,17 @@
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1os, Otp, Pdrm12, Rprm</t>
+          <t>Avp, Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1, Lhx5, Nhlh2, Npy, Nts, Otp, Pnoc, Pomc, Uncx</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Nr4a2, Prlr, Slc17a6, Tac2</t>
+          <t>Foxa1, Lmx1a, Nr4a2, Pitx2, Slc17a6</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>Gabbr1, Grm5</t>
+          <t>Gabbr1</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr">
@@ -5287,11 +5337,11 @@
         </is>
       </c>
       <c r="K28" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+          <t>Gabbr1=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
@@ -5313,242 +5363,242 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
+          <t>132 AHN-RCH-LHA Otp Fezf1 Glut</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>neighbor_control</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>4156</v>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>BROAD: Allen ROI = HY (entire hypothalamus). Subclass `144 MM Foxb1 Glut` and `143 MM-ant Foxb1 Glut` cover the WHOLE mammillary body (lateral + medial + supramammillary) - NOT lateral-specific. To restrict to LM, dissect lateral mammillary nucleus directly OR co-stain with LM-discriminating markers (Lhx5, Cck, Calb2 vs medial-mammillary markers).</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>Avp, Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1, Lhx5, Nhlh2, Npy, Nts, Otp, Pnoc, Pomc, Uncx</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Foxa1, Lmx1a, Nr4a2, Pitx2, Slc17a6</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>Gabbr1, Grm5</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>(neighbor control / counter-stain; drugs not recommended)</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="M29" s="11" t="inlineStr">
+        <is>
+          <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Nearby hypothalamic exclusion populations</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
           <t>102 DMH-LHA Gsx1 Gaba</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>neighbor_control</t>
         </is>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E30" s="11" t="n">
         <v>6768</v>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>BROAD: Allen ROI = HY (entire hypothalamus). Subclass `144 MM Foxb1 Glut` and `143 MM-ant Foxb1 Glut` cover the WHOLE mammillary body (lateral + medial + supramammillary) - NOT lateral-specific. To restrict to LM, dissect lateral mammillary nucleus directly OR co-stain with LM-discriminating markers (Lhx5, Cck, Calb2 vs medial-mammillary markers).</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1os, Otp, Pdrm12, Rprm</t>
-        </is>
-      </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>Nr4a2, Prlr, Slc17a6, Tac2</t>
-        </is>
-      </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>Avp, Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1, Lhx5, Nhlh2, Npy, Nts, Otp, Pnoc, Pomc, Uncx</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Foxa1, Lmx1a, Nr4a2, Pitx2, Slc17a6</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
         <is>
           <t>Gabbr1</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J30" s="11" t="inlineStr">
         <is>
           <t>(neighbor control / counter-stain; drugs not recommended)</t>
         </is>
       </c>
-      <c r="K29" s="11" t="n">
+      <c r="K30" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="L29" s="11" t="inlineStr">
+      <c r="L30" s="11" t="inlineStr">
         <is>
           <t>Gabbr1=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="M29" s="11" t="inlineStr">
+      <c r="M30" s="11" t="inlineStr">
         <is>
           <t>NEIGHBOR CONTROL (validation counter-stain; not a primary probe target)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>ORBm</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>L2/3 IT excitatory</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>007 L2/3 IT CTX Glut</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E31" s="9" t="n">
         <v>8869</v>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>OK: Allen ROI = PL-ILA-ORB (orbital + prelimbic + infralimbic).</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>Calb1, Cdh13, Cux1, Cux2, Fst, Rorb, Satb2, Slc17a6, Slc17a7</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>Bcl11b, Foxp2, Gad1, Gad2, Slc32a1</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>Cckbr, Gabbr1, Gabbr2, Grm1, Grm5</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
-      <c r="K30" s="9" t="n">
+      <c r="K31" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="L30" s="9" t="inlineStr">
+      <c r="L31" s="9" t="inlineStr">
         <is>
           <t>Cckbr=paper+allen_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="M30" s="9" t="inlineStr">
+      <c r="M31" s="9" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>ORBm</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>L5 IT / L5 ET/PT output neurons</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>005 L5 IT CTX Glut</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E32" s="10" t="n">
         <v>4419</v>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>OK: Allen ROI = PL-ILA-ORB (orbital + prelimbic + infralimbic).</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>Bcl11b, Crym, Deptor, Etv1, Fam84b, Fezf2, Pde1c, Satb2, Slc17a7</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>Cux1, Cux2, Gad1, Rorb</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>Gabbr1, Gabbr2, Grm5</t>
         </is>
       </c>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
-      <c r="K31" s="10" t="n">
+      <c r="K32" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="L31" s="10" t="inlineStr">
+      <c r="L32" s="10" t="inlineStr">
         <is>
           <t>Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="M31" s="10" t="inlineStr">
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>ORBm</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>L5 IT / L5 ET/PT output neurons</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>022 L5 ET CTX Glut</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>3739</v>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>OK: Allen ROI = PL-ILA-ORB (orbital + prelimbic + infralimbic).</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>Bcl11b, Crym, Deptor, Etv1, Fam84b, Fezf2, Pde1c, Satb2, Slc17a7</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>Cux1, Cux2, Gad1, Rorb</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1, Mc4r, Cckbr, Gabbr2, Grm5</t>
-        </is>
-      </c>
-      <c r="J32" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Mc4r: Setmelanotide (Imcivree) (FDA 2020) | Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
-        </is>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="L32" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr1=allen_only_keep; Mc4r=allen_only_keep; Cckbr=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="M32" s="9" t="inlineStr">
-        <is>
-          <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5615,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>032 L5 NP CTX Glut</t>
+          <t>022 L5 ET CTX Glut</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -5574,7 +5624,7 @@
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>3988</v>
+        <v>3739</v>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
@@ -5593,12 +5643,12 @@
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>Htr2c, Avpr1a, Chrm2, Gabbr1, Grm5</t>
+          <t>Gabbr1, Mc4r, Cckbr, Gabbr2, Grm5</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>Htr2c: Lorcaserin (Belviq) (FDA) | Avpr1a: Balovaptan (RG7314) (clinical-trial) | Chrm2: Donepezil (Aricept) (FDA 1996) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Mc4r: Setmelanotide (Imcivree) (FDA 2020) | Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
       <c r="K33" s="9" t="n">
@@ -5606,75 +5656,75 @@
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
+          <t>Gabbr1=allen_only_keep; Mc4r=allen_only_keep; Cckbr=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>L5 IT / L5 ET/PT output neurons</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>032 L5 NP CTX Glut</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>3988</v>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>OK: Allen ROI = PL-ILA-ORB (orbital + prelimbic + infralimbic).</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Bcl11b, Crym, Deptor, Etv1, Fam84b, Fezf2, Pde1c, Satb2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Htr2c, Avpr1a, Chrm2, Gabbr1, Grm5</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>Htr2c: Lorcaserin (Belviq) (FDA) | Avpr1a: Balovaptan (RG7314) (clinical-trial) | Chrm2: Donepezil (Aricept) (FDA 1996) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
           <t>Htr2c=allen_only_keep; Avpr1a=allen_only_keep; Chrm2=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="M33" s="9" t="inlineStr">
+      <c r="M34" s="9" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>ORBm</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>L6 CT / L6b</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>030 L6 CT CTX Glut</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>21453</v>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>OK: Allen ROI = PL-ILA-ORB (orbital + prelimbic + infralimbic).</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>Ccn2, Cplx3, Ctgf, Foxp2, Ntsr1, Nxph4, Slc17a7, Tle4</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>Cux1, Cux2, Gad1, Rorb</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Gabbr1, Gabbr2, Grm5, Htr1f, Oprm1</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Htr1f: Lasmiditan (Reyvow) (FDA 2019) | Oprm1: Morphine (FDA)</t>
-        </is>
-      </c>
-      <c r="K34" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L34" s="10" t="inlineStr">
-        <is>
-          <t>Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Htr1f=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="M34" s="10" t="inlineStr">
-        <is>
-          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5741,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>029 L6b CTX Glut</t>
+          <t>030 L6 CT CTX Glut</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -5700,7 +5750,7 @@
         </is>
       </c>
       <c r="E35" s="10" t="n">
-        <v>1586</v>
+        <v>21453</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -5719,20 +5769,20 @@
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>Cckbr, Gabbr1, Gabbr2, Oprm1</t>
+          <t>Gabbr1, Gabbr2, Grm5, Htr1f, Oprm1</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Oprm1: Morphine (FDA)</t>
+          <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Htr1f: Lasmiditan (Reyvow) (FDA 2019) | Oprm1: Morphine (FDA)</t>
         </is>
       </c>
       <c r="K35" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>Cckbr=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
+          <t>Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Htr1f=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="M35" s="10" t="inlineStr">
@@ -5754,179 +5804,179 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
+          <t>029 L6b CTX Glut</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>1586</v>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>OK: Allen ROI = PL-ILA-ORB (orbital + prelimbic + infralimbic).</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Ccn2, Cplx3, Ctgf, Foxp2, Ntsr1, Nxph4, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Cckbr, Gabbr1, Gabbr2, Oprm1</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Oprm1: Morphine (FDA)</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>Cckbr=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Oprm1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>L6 CT / L6b</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
           <t>004 L6 IT CTX Glut</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E36" s="10" t="n">
+      <c r="E37" s="10" t="n">
         <v>11338</v>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>OK: Allen ROI = PL-ILA-ORB (orbital + prelimbic + infralimbic).</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>Ccn2, Cplx3, Ctgf, Foxp2, Ntsr1, Nxph4, Slc17a7, Tle4</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>Cux1, Cux2, Gad1, Rorb</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Cckbr, Gabbr1, Gabbr2, Grm1, Grm5</t>
         </is>
       </c>
-      <c r="J36" s="10" t="inlineStr">
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
-      <c r="K36" s="10" t="n">
+      <c r="K37" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="L36" s="10" t="inlineStr">
+      <c r="L37" s="10" t="inlineStr">
         <is>
           <t>Cckbr=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="M36" s="10" t="inlineStr">
+      <c r="M37" s="10" t="inlineStr">
         <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>ORBm</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>Cortical interneurons</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>052 Pvalb Gaba</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E38" s="9" t="n">
         <v>2869</v>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>OK: Allen ROI = PL-ILA-ORB (orbital + prelimbic + infralimbic).</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H38" s="9" t="inlineStr">
         <is>
           <t>Cux1, Foxp2, Slc17a7</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>Oprd1, Adcyap1r1, Gabbr1, Gabbr2, Grm5</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>Oprd1: SNC80 (research) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K38" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="L37" s="9" t="inlineStr">
+      <c r="L38" s="9" t="inlineStr">
         <is>
           <t>Oprd1=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="M37" s="9" t="inlineStr">
+      <c r="M38" s="9" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>ORBm</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Cortical interneurons</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>053 Sst Gaba</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>5377</v>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>OK: Allen ROI = PL-ILA-ORB (orbital + prelimbic + infralimbic).</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>Cux1, Foxp2, Slc17a7</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5</t>
-        </is>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
-        <is>
-          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
-        </is>
-      </c>
-      <c r="K38" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L38" s="10" t="inlineStr">
-        <is>
-          <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="M38" s="10" t="inlineStr">
-        <is>
-          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
@@ -5943,133 +5993,133 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
+          <t>053 Sst Gaba</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>5377</v>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>OK: Allen ROI = PL-ILA-ORB (orbital + prelimbic + infralimbic).</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>ORBm</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
           <t>046 Vip Gaba</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E39" s="10" t="n">
+      <c r="E40" s="10" t="n">
         <v>3277</v>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>OK: Allen ROI = PL-ILA-ORB (orbital + prelimbic + infralimbic).</t>
         </is>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>Cux1, Foxp2, Slc17a7</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Adcyap1r1, Gabbr1, Npy1r</t>
         </is>
       </c>
-      <c r="J39" s="10" t="inlineStr">
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Npy1r: BIBP3226 (research)</t>
         </is>
       </c>
-      <c r="K39" s="10" t="n">
+      <c r="K40" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="L39" s="10" t="inlineStr">
+      <c r="L40" s="10" t="inlineStr">
         <is>
           <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Npy1r=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="M39" s="10" t="inlineStr">
+      <c r="M40" s="10" t="inlineStr">
         <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>ORBm</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>Cortical interneurons</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>049 Lamp5 Gaba</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>2339</v>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>OK: Allen ROI = PL-ILA-ORB (orbital + prelimbic + infralimbic).</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
-        </is>
-      </c>
-      <c r="H40" s="9" t="inlineStr">
-        <is>
-          <t>Cux1, Foxp2, Slc17a7</t>
-        </is>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr2, Adcyap1r1, Gabbr1, Grm5, Hcrtr2</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr2: Baclofen (FDA 1977) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Hcrtr2: Suvorexant (Belsomra) (FDA 2014)</t>
-        </is>
-      </c>
-      <c r="K40" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="L40" s="9" t="inlineStr">
-        <is>
-          <t>Gabbr2=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Hcrtr2=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="M40" s="9" t="inlineStr">
-        <is>
-          <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="60" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>AId</t>
+          <t>ORBm</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Upper-layer IT excitatory</t>
+          <t>Cortical interneurons</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>007 L2/3 IT CTX Glut</t>
+          <t>049 Lamp5 Gaba</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -6078,31 +6128,31 @@
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>7697</v>
+        <v>2339</v>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>OK: Allen ROI = AI (agranular insular).</t>
+          <t>OK: Allen ROI = PL-ILA-ORB (orbital + prelimbic + infralimbic).</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>Calb1, Cux1, Cux2, Rorb, Satb2, Slc17a6, Slc17a7</t>
+          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>Bcl11b, Foxp2, Gad1, Gad2, Slc32a1</t>
+          <t>Cux1, Foxp2, Slc17a7</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>Gpr88, Cckbr, Gabbr1, Gabbr2, Grm5</t>
+          <t>Gabbr2, Adcyap1r1, Gabbr1, Grm5, Hcrtr2</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>Gpr88: RTI-13951-33 (research) | Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+          <t>Gabbr2: Baclofen (FDA 1977) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Hcrtr2: Suvorexant (Belsomra) (FDA 2014)</t>
         </is>
       </c>
       <c r="K41" s="9" t="n">
@@ -6110,7 +6160,7 @@
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>Gpr88=allen_only_keep; Cckbr=paper+allen_broadly_detectable; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
+          <t>Gabbr2=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Hcrtr2=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="M41" s="9" t="inlineStr">
@@ -6132,7 +6182,7 @@
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>006 L4/5 IT CTX Glut</t>
+          <t>007 L2/3 IT CTX Glut</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
@@ -6141,7 +6191,7 @@
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>12177</v>
+        <v>7697</v>
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
@@ -6160,12 +6210,12 @@
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>Crhr1, Gabbr1, Gabbr2, Grm5, Htr2a</t>
+          <t>Gpr88, Cckbr, Gabbr1, Gabbr2, Grm5</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>Crhr1: Verucerfont (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Htr2a: Pimavanserin (Nuplazid) (FDA 2016)</t>
+          <t>Gpr88: RTI-13951-33 (research) | Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
       <c r="K42" s="9" t="n">
@@ -6173,138 +6223,138 @@
       </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
+          <t>Gpr88=allen_only_keep; Cckbr=paper+allen_broadly_detectable; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="M42" s="9" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Upper-layer IT excitatory</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>006 L4/5 IT CTX Glut</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>12177</v>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>OK: Allen ROI = AI (agranular insular).</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>Calb1, Cux1, Cux2, Rorb, Satb2, Slc17a6, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>Bcl11b, Foxp2, Gad1, Gad2, Slc32a1</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>Crhr1, Gabbr1, Gabbr2, Grm5, Htr2a</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>Crhr1: Verucerfont (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Htr2a: Pimavanserin (Nuplazid) (FDA 2016)</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
           <t>Crhr1=allen_only_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable; Htr2a=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="M42" s="9" t="inlineStr">
+      <c r="M43" s="9" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>AId</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>Deep-layer output neurons</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>030 L6 CT CTX Glut</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E44" s="10" t="n">
         <v>13072</v>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>OK: Allen ROI = AI (agranular insular).</t>
         </is>
       </c>
-      <c r="G43" s="10" t="inlineStr">
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>Bcl11b, Crym, Etv1, Fezf2, Foxp2, Ntsr1, Slc17a7, Tle4</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>Cux1, Cux2, Gad1, Rorb</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>Gabbr1, Gabbr2, Grm5, Htr1f</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr">
+      <c r="J44" s="10" t="inlineStr">
         <is>
           <t>Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Htr1f: Lasmiditan (Reyvow) (FDA 2019)</t>
         </is>
       </c>
-      <c r="K43" s="10" t="n">
+      <c r="K44" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="L43" s="10" t="inlineStr">
+      <c r="L44" s="10" t="inlineStr">
         <is>
           <t>Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Htr1f=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="M43" s="10" t="inlineStr">
+      <c r="M44" s="10" t="inlineStr">
         <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>AId</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>Deep-layer output neurons</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>022 L5 ET CTX Glut</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>1134</v>
-      </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>OK: Allen ROI = AI (agranular insular).</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>Bcl11b, Crym, Etv1, Fezf2, Foxp2, Ntsr1, Slc17a7, Tle4</t>
-        </is>
-      </c>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>Cux1, Cux2, Gad1, Rorb</t>
-        </is>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>Htr1f, Htr1b, Mc4r, Cckbr, Gabbr1</t>
-        </is>
-      </c>
-      <c r="J44" s="9" t="inlineStr">
-        <is>
-          <t>Htr1f: Lasmiditan (Reyvow) (FDA 2019) | Htr1b: Sumatriptan (FDA 1992) | Mc4r: Setmelanotide (Imcivree) (FDA 2020) | Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977)</t>
-        </is>
-      </c>
-      <c r="K44" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="L44" s="9" t="inlineStr">
-        <is>
-          <t>Htr1f=allen_only_keep; Htr1b=allen_only_keep; Mc4r=allen_only_keep; Cckbr=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="M44" s="9" t="inlineStr">
-        <is>
-          <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6371,7 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>032 L5 NP CTX Glut</t>
+          <t>022 L5 ET CTX Glut</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -6330,7 +6380,7 @@
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>3409</v>
+        <v>1134</v>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
@@ -6349,12 +6399,12 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>Grm5, Avpr1a, Chrm2, Gabbr1, Htr2c</t>
+          <t>Htr1f, Htr1b, Mc4r, Cckbr, Gabbr1</t>
         </is>
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>Grm5: Mavoglurant (AFQ056) (clinical-trial) | Avpr1a: Balovaptan (RG7314) (clinical-trial) | Chrm2: Donepezil (Aricept) (FDA 1996) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Htr2c: Lorcaserin (Belviq) (FDA)</t>
+          <t>Htr1f: Lasmiditan (Reyvow) (FDA 2019) | Htr1b: Sumatriptan (FDA 1992) | Mc4r: Setmelanotide (Imcivree) (FDA 2020) | Cckbr: Netazepide (YF476) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977)</t>
         </is>
       </c>
       <c r="K45" s="9" t="n">
@@ -6362,75 +6412,75 @@
       </c>
       <c r="L45" s="9" t="inlineStr">
         <is>
+          <t>Htr1f=allen_only_keep; Htr1b=allen_only_keep; Mc4r=allen_only_keep; Cckbr=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>Deep-layer output neurons</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>032 L5 NP CTX Glut</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>3409</v>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>OK: Allen ROI = AI (agranular insular).</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>Bcl11b, Crym, Etv1, Fezf2, Foxp2, Ntsr1, Slc17a7, Tle4</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>Grm5, Avpr1a, Chrm2, Gabbr1, Htr2c</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>Grm5: Mavoglurant (AFQ056) (clinical-trial) | Avpr1a: Balovaptan (RG7314) (clinical-trial) | Chrm2: Donepezil (Aricept) (FDA 1996) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Htr2c: Lorcaserin (Belviq) (FDA)</t>
+        </is>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
           <t>Grm5=allen_only_keep; Avpr1a=allen_only_keep; Chrm2=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Htr2c=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="M45" s="9" t="inlineStr">
+      <c r="M46" s="9" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>AId</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>Deep-layer output neurons</t>
-        </is>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t>029 L6b CTX Glut</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>439</v>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>OK: Allen ROI = AI (agranular insular).</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>Bcl11b, Crym, Etv1, Fezf2, Foxp2, Ntsr1, Slc17a7, Tle4</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>Cux1, Cux2, Gad1, Rorb</t>
-        </is>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>Cckbr, Drd1, Gabbr1, Gabbr2, Grm5</t>
-        </is>
-      </c>
-      <c r="J46" s="10" t="inlineStr">
-        <is>
-          <t>Cckbr: Netazepide (YF476) (clinical-trial) | Drd1: Apomorphine (FDA) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
-        </is>
-      </c>
-      <c r="K46" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L46" s="10" t="inlineStr">
-        <is>
-          <t>Cckbr=allen_only_broadly_detectable; Drd1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="M46" s="10" t="inlineStr">
-        <is>
-          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
       </c>
     </row>
@@ -6442,12 +6492,12 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Cortical interneurons</t>
+          <t>Deep-layer output neurons</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>053 Sst Gaba</t>
+          <t>029 L6b CTX Glut</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -6456,7 +6506,7 @@
         </is>
       </c>
       <c r="E47" s="10" t="n">
-        <v>5983</v>
+        <v>439</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -6465,22 +6515,22 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
+          <t>Bcl11b, Crym, Etv1, Fezf2, Foxp2, Ntsr1, Slc17a7, Tle4</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>Cux1, Foxp2, Slc17a7</t>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5</t>
+          <t>Cckbr, Drd1, Gabbr1, Gabbr2, Grm5</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+          <t>Cckbr: Netazepide (YF476) (clinical-trial) | Drd1: Apomorphine (FDA) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
       <c r="K47" s="10" t="n">
@@ -6488,7 +6538,7 @@
       </c>
       <c r="L47" s="10" t="inlineStr">
         <is>
-          <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+          <t>Cckbr=allen_only_broadly_detectable; Drd1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="M47" s="10" t="inlineStr">
@@ -6510,7 +6560,7 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>052 Pvalb Gaba</t>
+          <t>053 Sst Gaba</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
@@ -6519,7 +6569,7 @@
         </is>
       </c>
       <c r="E48" s="10" t="n">
-        <v>3617</v>
+        <v>5983</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -6538,12 +6588,12 @@
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm5, Oprd1</t>
+          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5</t>
         </is>
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Oprd1: SNC80 (research)</t>
+          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
       <c r="K48" s="10" t="n">
@@ -6551,75 +6601,75 @@
       </c>
       <c r="L48" s="10" t="inlineStr">
         <is>
+          <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="M48" s="10" t="inlineStr">
+        <is>
+          <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>AId</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Cortical interneurons</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>052 Pvalb Gaba</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>3617</v>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>OK: Allen ROI = AI (agranular insular).</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Gabbr1, Gabbr2, Grm5, Oprd1</t>
+        </is>
+      </c>
+      <c r="J49" s="10" t="inlineStr">
+        <is>
+          <t>Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Oprd1: SNC80 (research)</t>
+        </is>
+      </c>
+      <c r="K49" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L49" s="10" t="inlineStr">
+        <is>
           <t>Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Gabbr2=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Oprd1=allen_only_broadly_detectable</t>
         </is>
       </c>
-      <c r="M48" s="10" t="inlineStr">
+      <c r="M49" s="10" t="inlineStr">
         <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>AId</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>Cortical interneurons</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>046 Vip Gaba</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E49" s="9" t="n">
-        <v>3706</v>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>OK: Allen ROI = AI (agranular insular).</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
-        </is>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>Cux1, Foxp2, Slc17a7</t>
-        </is>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Gpr101, Adcyap1r1, Gabbr1, Grm5, Npy1r</t>
-        </is>
-      </c>
-      <c r="J49" s="9" t="inlineStr">
-        <is>
-          <t>Gpr101: (no clinical drugs) (research) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Npy1r: BIBP3226 (research)</t>
-        </is>
-      </c>
-      <c r="K49" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="L49" s="9" t="inlineStr">
-        <is>
-          <t>Gpr101=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Npy1r=allen_only_broadly_detectable</t>
-        </is>
-      </c>
-      <c r="M49" s="9" t="inlineStr">
-        <is>
-          <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6686,7 @@
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>049 Lamp5 Gaba</t>
+          <t>046 Vip Gaba</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -6645,7 +6695,7 @@
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
@@ -6664,12 +6714,12 @@
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>Gabbr2, Gpr6, Adcyap1r1, Gabbr1, Grm5</t>
+          <t>Gpr101, Adcyap1r1, Gabbr1, Grm5, Npy1r</t>
         </is>
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>Gabbr2: Baclofen (FDA 1977) | Gpr6: CVN424 (Cerevance) (clinical-trial) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+          <t>Gpr101: (no clinical drugs) (research) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial) | Npy1r: BIBP3226 (research)</t>
         </is>
       </c>
       <c r="K50" s="9" t="n">
@@ -6677,7 +6727,7 @@
       </c>
       <c r="L50" s="9" t="inlineStr">
         <is>
-          <t>Gabbr2=allen_only_keep; Gpr6=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
+          <t>Gpr101=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable; Npy1r=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="M50" s="9" t="inlineStr">
@@ -6689,17 +6739,17 @@
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>AId</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>CA1 pyramidal</t>
+          <t>Cortical interneurons</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>016 CA1-ProS Glut</t>
+          <t>049 Lamp5 Gaba</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -6708,31 +6758,31 @@
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>24868</v>
+        <v>3704</v>
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>GOOD: Allen ROI = HIP (hippocampus); subclass anchors split CA1 (016 CA1-ProS), CA2 (025 CA2-FC-IG), CA3 (017 CA3), and DG (037 DG) cleanly.</t>
+          <t>OK: Allen ROI = AI (agranular insular).</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>Fibcd1, Mpped1, Pou3f1, Slc17a7, Spink8, Wfs1</t>
+          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>Calb1, Cnih3, Prox1, Rgs14</t>
+          <t>Cux1, Foxp2, Slc17a7</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>Htr1a, Mc4r, Gabbr1, Gabbr2, Grm1</t>
+          <t>Gabbr2, Gpr6, Adcyap1r1, Gabbr1, Grm5</t>
         </is>
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>Htr1a: Buspirone (FDA 1986) | Mc4r: Setmelanotide (Imcivree) (FDA 2020) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research)</t>
+          <t>Gabbr2: Baclofen (FDA 1977) | Gpr6: CVN424 (Cerevance) (clinical-trial) | Adcyap1r1: AMG-301 (anti-PAC1 mAb) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
       <c r="K51" s="9" t="n">
@@ -6740,7 +6790,7 @@
       </c>
       <c r="L51" s="9" t="inlineStr">
         <is>
-          <t>Htr1a=paper+allen_keep; Mc4r=allen_only_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable</t>
+          <t>Gabbr2=allen_only_keep; Gpr6=allen_only_keep; Adcyap1r1=allen_only_broadly_detectable; Gabbr1=allen_only_broadly_detectable; Grm5=allen_only_broadly_detectable</t>
         </is>
       </c>
       <c r="M51" s="9" t="inlineStr">
@@ -6757,12 +6807,12 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>CA2 pyramidal</t>
+          <t>CA1 pyramidal</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>025 CA2-FC-IG Glut</t>
+          <t>016 CA1-ProS Glut</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
@@ -6771,7 +6821,7 @@
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>327</v>
+        <v>24868</v>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
@@ -6780,30 +6830,30 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>Amigo2, Avpr1b, Cacng5, Map3k15, Pcp4, Rgs14, Slc17a7</t>
+          <t>Fibcd1, Mpped1, Pou3f1, Slc17a7, Spink8, Wfs1</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>Cnih3, Prox1, Wfs1</t>
+          <t>Calb1, Cnih3, Prox1, Rgs14</t>
         </is>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>Avpr1b, Gabbr1, Gabbr2, Grm5</t>
+          <t>Htr1a, Mc4r, Gabbr1, Gabbr2, Grm1</t>
         </is>
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>Avpr1b: Nelivaptan (SSR149415) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+          <t>Htr1a: Buspirone (FDA 1986) | Mc4r: Setmelanotide (Imcivree) (FDA 2020) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research)</t>
         </is>
       </c>
       <c r="K52" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L52" s="9" t="inlineStr">
         <is>
-          <t>Avpr1b=paper+allen_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
+          <t>Htr1a=paper+allen_keep; Mc4r=allen_only_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable</t>
         </is>
       </c>
       <c r="M52" s="9" t="inlineStr">
@@ -6820,119 +6870,182 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
+          <t>CA2 pyramidal</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>025 CA2-FC-IG Glut</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>327</v>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>GOOD: Allen ROI = HIP (hippocampus); subclass anchors split CA1 (016 CA1-ProS), CA2 (025 CA2-FC-IG), CA3 (017 CA3), and DG (037 DG) cleanly.</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>Amigo2, Avpr1b, Cacng5, Map3k15, Pcp4, Rgs14, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>Cnih3, Prox1, Wfs1</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>Avpr1b, Gabbr1, Gabbr2, Grm5</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>Avpr1b: Nelivaptan (SSR149415) (clinical-trial) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>Avpr1b=paper+allen_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
+        </is>
+      </c>
+      <c r="M53" s="9" t="inlineStr">
+        <is>
+          <t>ORDER (cell-type-specific picks available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
           <t>CA3 pyramidal</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>017 CA3 Glut</t>
         </is>
       </c>
-      <c r="D53" s="9" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E53" s="9" t="n">
+      <c r="E54" s="9" t="n">
         <v>4799</v>
       </c>
-      <c r="F53" s="9" t="inlineStr">
+      <c r="F54" s="9" t="inlineStr">
         <is>
           <t>GOOD: Allen ROI = HIP (hippocampus); subclass anchors split CA1 (016 CA1-ProS), CA2 (025 CA2-FC-IG), CA3 (017 CA3), and DG (037 DG) cleanly.</t>
         </is>
       </c>
-      <c r="G53" s="9" t="inlineStr">
+      <c r="G54" s="9" t="inlineStr">
         <is>
           <t>Calb2, Cnih3, Coch, Lct, Slc17a7</t>
         </is>
       </c>
-      <c r="H53" s="9" t="inlineStr">
+      <c r="H54" s="9" t="inlineStr">
         <is>
           <t>Prox1, Rgs14, Wfs1</t>
         </is>
       </c>
-      <c r="I53" s="9" t="inlineStr">
+      <c r="I54" s="9" t="inlineStr">
         <is>
           <t>Npy2r, Hcrtr1, Gabbr1, Gabbr2, Grm1</t>
         </is>
       </c>
-      <c r="J53" s="9" t="inlineStr">
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>Npy2r: BIIE0246 (research) | Hcrtr1: SB-334867 (research) | Gabbr1: Baclofen (Lioresal) (FDA 1977) | Gabbr2: Baclofen (FDA 1977) | Grm1: JNJ-16259685 (research)</t>
         </is>
       </c>
-      <c r="K53" s="9" t="n">
+      <c r="K54" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="L53" s="9" t="inlineStr">
+      <c r="L54" s="9" t="inlineStr">
         <is>
           <t>Npy2r=allen_only_keep; Hcrtr1=allen_only_keep; Gabbr1=paper+allen_broadly_detectable; Gabbr2=paper+allen_broadly_detectable; Grm1=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="M53" s="9" t="inlineStr">
+      <c r="M54" s="9" t="inlineStr">
         <is>
           <t>ORDER (cell-type-specific picks available)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>DG granule cell</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>037 DG Glut</t>
         </is>
       </c>
-      <c r="D54" s="10" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E54" s="10" t="n">
+      <c r="E55" s="10" t="n">
         <v>80255</v>
       </c>
-      <c r="F54" s="10" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>GOOD: Allen ROI = HIP (hippocampus); subclass anchors split CA1 (016 CA1-ProS), CA2 (025 CA2-FC-IG), CA3 (017 CA3), and DG (037 DG) cleanly.</t>
         </is>
       </c>
-      <c r="G54" s="10" t="inlineStr">
+      <c r="G55" s="10" t="inlineStr">
         <is>
           <t>C1ql2, Calb1, Dock10, Dsp, Prox1, Slc17a7</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>Cnih3, Rgs14, Wfs1</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>Grm1, Grm5</t>
         </is>
       </c>
-      <c r="J54" s="10" t="inlineStr">
+      <c r="J55" s="10" t="inlineStr">
         <is>
           <t>Grm1: JNJ-16259685 (research) | Grm5: Mavoglurant (AFQ056) (clinical-trial)</t>
         </is>
       </c>
-      <c r="K54" s="10" t="n">
+      <c r="K55" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="L54" s="10" t="inlineStr">
+      <c r="L55" s="10" t="inlineStr">
         <is>
           <t>Grm1=paper+allen_broadly_detectable; Grm5=paper+allen_broadly_detectable</t>
         </is>
       </c>
-      <c r="M54" s="10" t="inlineStr">
+      <c r="M55" s="10" t="inlineStr">
         <is>
           <t>ORDER WITH SPATIAL CONSTRAINT (broadly detectable only)</t>
         </is>
@@ -6949,7 +7062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8347,12 +8460,12 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
+          <t>Calb2, Nox4, Slc17a6, Spon1</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Gad1, Gad2, Pvalb, Slc32a1</t>
+          <t>Adcyap1, Gad1, Gad2, Grin2c, Necab1, Nts, Pou4f1, Prkcd, Pvalb, Slc32a1, Sox1, Sp9, Tnnt1</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -8402,7 +8515,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>149 PVT-PT Ntrk1 Glut</t>
+          <t>151 TH Prkcd Grin2c Glut</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -8411,7 +8524,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>9854</v>
+        <v>68125</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -8420,12 +8533,12 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
+          <t>Calb2, Nox4, Slc17a6, Spon1</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Gad1, Gad2, Pvalb, Slc32a1</t>
+          <t>Adcyap1, Gad1, Gad2, Grin2c, Necab1, Nts, Pou4f1, Prkcd, Pvalb, Slc32a1, Sox1, Sp9, Tnnt1</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -8435,28 +8548,28 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Oprk1(spec=1.42, log2=4.18, pct=66%, status=keep); Galr1(spec=0.23, log2=2.12, pct=35%, status=keep); Oxtr(spec=0.50, log2=1.89, pct=34%, status=keep)</t>
+          <t>Grm1(spec=0.91, log2=10.01, pct=100%, status=keep)</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Oprk1[allen_only_keep, spec=+1.42, log2=4.18, pct=66%; drugs: Difelikefalin (Korsuva; FDA 2021)]; Galr1[allen_only_keep, spec=+0.23, log2=2.12, pct=35%; drugs: research_only_or_none]; Oxtr[allen_only_keep, spec=+0.50, log2=1.89, pct=34%; drugs: research_only_or_none]; Cnr1[allen_only_broadly_detectable, spec=-0.69, log2=5.48, pct=78%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Oprm1[allen_only_broadly_detectable, spec=-0.58, log2=6.85, pct=84%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Adcyap1r1[paper_only_allen_downgrade, spec=-2.91, log2=5.24, pct=81%; drugs: research_only_or_none]; Chrm2[paper_only_allen_downgrade, spec=-5.90, log2=3.30, pct=48%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Gabbr1[paper_only_allen_downgrade, spec=-2.30, log2=8.76, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper_only_allen_downgrade, spec=-2.01, log2=8.80, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper_only_allen_downgrade, spec=-2.93, log2=7.07, pct=87%; drugs: research_only_or_none]; Grm5[paper_only_allen_downgrade, spec=-2.67, log2=8.86, pct=99%; drugs: research_only_or_none]; Htr2a[paper_only_allen_downgrade, spec=-3.10, log2=0.03, pct=1%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Ntsr1[paper_only_allen_downgrade, spec=-1.24, log2=0.32, pct=6%; drugs: research_only_or_none]; Ntsr2[paper_only_allen_downgrade, spec=-8.68, log2=0.36, pct=7%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-4.18, log2=0.48, pct=9%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+          <t>Grm1[paper+allen_keep, spec=+0.91, log2=10.01, pct=100%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-1.55, log2=9.51, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.83, log2=9.98, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Adcyap1r1[paper_only_allen_downgrade, spec=-6.06, log2=2.09, pct=36%; drugs: research_only_or_none]; Chrm2[paper_only_allen_downgrade, spec=-5.59, log2=3.61, pct=53%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Grm5[paper_only_allen_downgrade, spec=-2.61, log2=8.91, pct=98%; drugs: research_only_or_none]; Htr2a[paper_only_allen_downgrade, spec=-3.12, log2=0.01, pct=0%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Ntsr1[paper_only_allen_downgrade, spec=-1.19, log2=0.37, pct=6%; drugs: research_only_or_none]; Ntsr2[paper_only_allen_downgrade, spec=-8.96, log2=0.08, pct=2%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-4.50, log2=0.16, pct=3%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Oprk1, Galr1, Oxtr | allen_only_broadly_detectable: Cnr1, Oprm1 | paper_only: Adcyap1r1(downgrade,spec=-2.91,log2=5.24); Chrm2(downgrade,spec=-5.90,log2=3.30); Gabbr1(downgrade,spec=-2.30,log2=8.76); Gabbr2(downgrade,spec=-2.01,log2=8.80); Grm1(downgrade,spec=-2.93,log2=7.07); Grm5(downgrade,spec=-2.67,log2=8.86); Htr2a(downgrade,spec=-3.10,log2=0.03); Ntsr1(downgrade,spec=-1.24,log2=0.32); Ntsr2(downgrade,spec=-8.68,log2=0.36); Sstr2(downgrade,spec=-4.18,log2=0.48)</t>
+          <t>both_keep: Grm1 | paper+broadly_detectable: Gabbr1, Gabbr2 | paper_only: Adcyap1r1(downgrade,spec=-6.06,log2=2.09); Chrm2(downgrade,spec=-5.59,log2=3.61); Grm5(downgrade,spec=-2.61,log2=8.91); Htr2a(downgrade,spec=-3.12,log2=0.01); Ntsr1(downgrade,spec=-1.19,log2=0.37); Ntsr2(downgrade,spec=-8.96,log2=0.08); Sstr2(downgrade,spec=-4.50,log2=0.16)</t>
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>2</v>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>Oprk1 | FDA: Difelikefalin (Korsuva; FDA 2021) | clinical/research: Nalfurafine (Japan); Buprenorphine (mixed); CR845 | indication: uremic pruritus (Difelikefalin); depression research || Galr1 | clinical/research: research only | indication: epilepsy; depression (preclinical) || Oxtr | clinical/research: Intranasal oxytocin (autism/social trials; mostly failed); Carbetocin (Pabal - postpartum hemorrhage outside USA) | indication: autism research; social cognition; postpartum hemorrhage (Carbetocin EU) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Ntsr1 | clinical/research: SR-48692 (research antagonist); SR-142948 | indication: thermal pain; addiction (preclinical) || Ntsr2 | clinical/research: research | indication: pain (preclinical) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
+          <t>Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Ntsr1 | clinical/research: SR-48692 (research antagonist); SR-142948 | indication: thermal pain; addiction (preclinical) || Ntsr2 | clinical/research: research | indication: pain (preclinical) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr"/>
@@ -8470,21 +8583,21 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Midline thalamic glutamatergic / reuniens</t>
+          <t>Reticular/inhibitory thalamic exclusion</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>145 MH Tac2 Glut</t>
+          <t>093 RT-ZI Gnb3 Gaba</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7972</v>
+        <v>7452</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -8493,47 +8606,43 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Calb2, Pcp4, Slc17a6, Spon1, Tcf7l2</t>
+          <t>Dlx1, Dlx2, Gad1, Gad2, Pvalb, Slc32a1, Sox14</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Gad1, Gad2, Pvalb, Slc32a1</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>Adcyap1r1, Chrm2, Gabbr1, Gabbr2, Grm1, Grm5, Htr2a, Ntsr1, Ntsr2, Sstr2</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>Gabbr1(spec=1.44, log2=11.06, pct=100%, status=keep); Gabbr2(spec=0.83, log2=10.81, pct=99%, status=keep); Tacr1(spec=1.61, log2=6.00, pct=78%, status=keep); Sstr2(spec=2.64, log2=4.66, pct=68%, status=keep)</t>
-        </is>
-      </c>
+          <t>Calb2, Pcp4, Slc17a6, Slc17a7, Tcf7l2</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1[paper+allen_keep, spec=+1.44, log2=11.06, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_keep, spec=+0.83, log2=10.81, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Sstr2[paper+allen_keep, spec=+2.64, log2=4.66, pct=68%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]; Tacr1[allen_only_keep, spec=+1.61, log2=6.00, pct=78%; drugs: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet)]; Adcyap1r1[paper_only_allen_downgrade, spec=-7.94, log2=0.22, pct=4%; drugs: research_only_or_none]; Chrm2[paper_only_allen_downgrade, spec=-8.87, log2=0.33, pct=5%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Grm1[paper_only_allen_downgrade, spec=-7.57, log2=2.43, pct=35%; drugs: research_only_or_none]; Grm5[paper_only_allen_downgrade, spec=-7.53, log2=3.99, pct=53%; drugs: research_only_or_none]; Htr2a[paper_only_allen_downgrade, spec=-2.68, log2=0.45, pct=7%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Ntsr1[paper_only_allen_downgrade, spec=-1.54, log2=0.02, pct=0%; drugs: research_only_or_none]; Ntsr2[paper_only_allen_downgrade, spec=-8.96, log2=0.08, pct=2%; drugs: research_only_or_none]</t>
+          <t>Chrm2[allen_only_broadly_detectable, spec=-1.96, log2=7.24, pct=88%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>both_keep: Gabbr1, Gabbr2, Sstr2 | allen_only_keep: Tacr1 | paper_only: Adcyap1r1(downgrade,spec=-7.94,log2=0.22); Chrm2(downgrade,spec=-8.87,log2=0.33); Grm1(downgrade,spec=-7.57,log2=2.43); Grm5(downgrade,spec=-7.53,log2=3.99); Htr2a(downgrade,spec=-2.68,log2=0.45); Ntsr1(downgrade,spec=-1.54,log2=0.02); Ntsr2(downgrade,spec=-8.96,log2=0.08)</t>
+          <t>allen_only_broadly_detectable: Chrm2</t>
         </is>
       </c>
       <c r="M22" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease || Tacr1 | FDA: Aprepitant (Emend); Fosaprepitant; Rolapitant; Netupitant; Maropitant (vet) | indication: chemotherapy-induced nausea/vomiting (CINV); postoperative nausea || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Ntsr1 | clinical/research: SR-48692 (research antagonist); SR-142948 | indication: thermal pain; addiction (preclinical) || Ntsr2 | clinical/research: research | indication: pain (preclinical)</t>
+          <t>Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 1 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="110" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -8548,7 +8657,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>093 RT-ZI Gnb3 Gaba</t>
+          <t>109 LGv-ZI Otx2 Gaba</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -8557,7 +8666,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7452</v>
+        <v>4380</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -8578,12 +8687,12 @@
       <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Chrm2[allen_only_broadly_detectable, spec=-1.96, log2=7.24, pct=88%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]</t>
+          <t>Grm5[allen_only_broadly_detectable, spec=-1.36, log2=10.17, pct=99%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>allen_only_broadly_detectable: Chrm2</t>
+          <t>allen_only_broadly_detectable: Grm5</t>
         </is>
       </c>
       <c r="M23" s="3" t="n">
@@ -8594,7 +8703,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder</t>
+          <t>Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
@@ -8607,69 +8716,73 @@
     <row r="24" ht="110" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>LM</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Reticular/inhibitory thalamic exclusion</t>
+          <t>Lateral mammillary excitatory</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>109 LGv-ZI Otx2 Gaba</t>
+          <t>138 PH Pitx2 Glut</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>neighbor_control</t>
+          <t>target</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>4380</v>
+        <v>1795</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>PARTIAL: Allen ROI = TH (entire thalamus); subclass `152 RE-Xi Nox4 Glut` is the most RE-specific transcriptomic class but it covers both nucleus reuniens AND xiphoid nucleus.</t>
+          <t>BROAD: Allen ROI = HY (entire hypothalamus). Subclass `144 MM Foxb1 Glut` and `143 MM-ant Foxb1 Glut` cover the WHOLE mammillary body (lateral + medial + supramammillary) - NOT lateral-specific. To restrict to LM, dissect lateral mammillary nucleus directly OR co-stain with LM-discriminating markers (Lhx5, Cck, Calb2 vs medial-mammillary markers).</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Dlx1, Dlx2, Gad1, Gad2, Pvalb, Slc32a1, Sox14</t>
+          <t>Foxa1, Lmx1a, Nr4a2, Pdyn, Pitx2, Slc17a6, Snap25, Tac2</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Calb2, Pcp4, Slc17a6, Slc17a7, Tcf7l2</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr"/>
+          <t>Avp, Cartpt, Foxb1, Gad1, Gad2, Lhx1, Lhx5, Nhlh2, Nkx2-4, Npy, Nts, Otp, Pnoc, Pomc, Slc32a1, Tbx3, Uncx</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Avpr1a, Cckbr, Gabbr1, Gabbr2, Grm1, Hcrtr1, Hcrtr2, Mc4r, Oxtr, Sstr2</t>
+        </is>
+      </c>
       <c r="J24" s="3" t="inlineStr"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Grm5[allen_only_broadly_detectable, spec=-1.36, log2=10.17, pct=99%; drugs: research_only_or_none]</t>
+          <t>Gabbr1[paper+allen_broadly_detectable, spec=-1.03, log2=8.24, pct=98%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-1.60, log2=9.67, pct=99%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-3.30, log2=4.10, pct=64%; drugs: research_only_or_none]; Avpr1a[paper_only_allen_downgrade, spec=-1.92, log2=0.24, pct=4%; drugs: research_only_or_none]; Cckbr[paper_only_allen_downgrade, spec=-3.65, log2=0.70, pct=13%; drugs: research_only_or_none]; Gabbr2[paper_only_allen_downgrade, spec=-2.71, log2=7.39, pct=92%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper_only_allen_downgrade, spec=-2.62, log2=7.22, pct=88%; drugs: research_only_or_none]; Hcrtr1[paper_only_allen_downgrade, spec=-1.09, log2=0.53, pct=10%; drugs: research_only_or_none]; Hcrtr2[paper_only_allen_downgrade, spec=-2.01, log2=3.59, pct=52%; drugs: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2]; Mc4r[paper_only_allen_downgrade, spec=-0.85, log2=0.35, pct=6%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Oxtr[paper_only_allen_downgrade, spec=-2.93, log2=0.70, pct=12%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-1.71, log2=0.85, pct=15%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>allen_only_broadly_detectable: Grm5</t>
+          <t>paper+broadly_detectable: Gabbr1 | allen_only_broadly_detectable: Grm5 | paper_only: Adcyap1r1(downgrade,spec=-3.30,log2=4.10); Avpr1a(downgrade,spec=-1.92,log2=0.24); Cckbr(downgrade,spec=-3.65,log2=0.70); Gabbr2(downgrade,spec=-2.71,log2=7.39); Grm1(downgrade,spec=-2.62,log2=7.22); Hcrtr1(downgrade,spec=-1.09,log2=0.53); Hcrtr2(downgrade,spec=-2.01,log2=3.59); Mc4r(downgrade,spec=-0.85,log2=0.35); Oxtr(downgrade,spec=-2.93,log2=0.70); Sstr2(downgrade,spec=-1.71,log2=0.85)</t>
         </is>
       </c>
       <c r="M24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Hcrtr1 | clinical/research: SB-334867 (research selective antagonist) | indication: addiction; anxiety (preclinical) || Hcrtr2 | FDA: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2 | clinical/research: JNJ-42847922 (selective OX2R) | indication: insomnia || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Oxtr | clinical/research: Intranasal oxytocin (autism/social trials; mostly failed); Carbetocin (Pabal - postpartum hemorrhage outside USA) | indication: autism research; social cognition; postpartum hemorrhage (Carbetocin EU) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr"/>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>no cell-type-specific GPCR; relying on 1 broadly_expressed_detectable candidates</t>
+          <t>no cell-type-specific GPCR; relying on 2 broadly_expressed_detectable candidates</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8799,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>144 MM Foxb1 Glut</t>
+          <t>141 PH-SUM Foxa1 Glut</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -8695,7 +8808,7 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>8270</v>
+        <v>2921</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -8704,12 +8817,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Esr1, Kcnc2, Nr4a2, Pdyn, Prlr, Slc17a6, Snap25, Syt4, Tac2</t>
+          <t>Foxa1, Lmx1a, Nr4a2, Pdyn, Pitx2, Slc17a6, Snap25, Tac2</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Foxb1, Gad1, Gad2, Slc32a1</t>
+          <t>Avp, Cartpt, Foxb1, Gad1, Gad2, Lhx1, Lhx5, Nhlh2, Nkx2-4, Npy, Nts, Otp, Pnoc, Pomc, Slc32a1, Tbx3, Uncx</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -8720,29 +8833,29 @@
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1[paper+allen_broadly_detectable, spec=-1.00, log2=8.28, pct=98%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.75, log2=8.35, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-0.13, log2=9.71, pct=100%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-4.76, log2=2.64, pct=47%; drugs: research_only_or_none]; Avpr1a[paper_only_allen_downgrade, spec=-2.15, log2=0.01, pct=0%; drugs: research_only_or_none]; Cckbr[paper_only_allen_downgrade, spec=-4.07, log2=0.28, pct=6%; drugs: research_only_or_none]; Hcrtr1[paper_only_allen_downgrade, spec=-1.61, log2=0.02, pct=0%; drugs: research_only_or_none]; Hcrtr2[paper_only_allen_downgrade, spec=-4.36, log2=1.25, pct=21%; drugs: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2]; Mc4r[paper_only_allen_downgrade, spec=-1.20, log2=0.00, pct=0%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Oxtr[paper_only_allen_downgrade, spec=-3.63, log2=0.01, pct=0%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-2.19, log2=0.37, pct=7%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+          <t>Gabbr1[paper+allen_broadly_detectable, spec=-1.39, log2=7.89, pct=96%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Adcyap1r1[paper_only_allen_downgrade, spec=-2.35, log2=5.04, pct=75%; drugs: research_only_or_none]; Avpr1a[paper_only_allen_downgrade, spec=-1.70, log2=0.46, pct=8%; drugs: research_only_or_none]; Cckbr[paper_only_allen_downgrade, spec=-4.14, log2=0.21, pct=4%; drugs: research_only_or_none]; Gabbr2[paper_only_allen_downgrade, spec=-2.65, log2=7.45, pct=93%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper_only_allen_downgrade, spec=-3.53, log2=6.30, pct=82%; drugs: research_only_or_none]; Hcrtr1[paper_only_allen_downgrade, spec=-1.24, log2=0.38, pct=7%; drugs: research_only_or_none]; Hcrtr2[paper_only_allen_downgrade, spec=-3.24, log2=2.37, pct=35%; drugs: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2]; Mc4r[paper_only_allen_downgrade, spec=-1.15, log2=0.05, pct=1%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Oxtr[paper_only_allen_downgrade, spec=-3.03, log2=0.60, pct=11%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-1.34, log2=1.21, pct=21%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>paper+broadly_detectable: Gabbr1, Gabbr2, Grm1 | paper_only: Adcyap1r1(downgrade,spec=-4.76,log2=2.64); Avpr1a(downgrade,spec=-2.15,log2=0.01); Cckbr(downgrade,spec=-4.07,log2=0.28); Hcrtr1(downgrade,spec=-1.61,log2=0.02); Hcrtr2(downgrade,spec=-4.36,log2=1.25); Mc4r(downgrade,spec=-1.20,log2=0.00); Oxtr(downgrade,spec=-3.63,log2=0.01); Sstr2(downgrade,spec=-2.19,log2=0.37)</t>
+          <t>paper+broadly_detectable: Gabbr1 | paper_only: Adcyap1r1(downgrade,spec=-2.35,log2=5.04); Avpr1a(downgrade,spec=-1.70,log2=0.46); Cckbr(downgrade,spec=-4.14,log2=0.21); Gabbr2(downgrade,spec=-2.65,log2=7.45); Grm1(downgrade,spec=-3.53,log2=6.30); Hcrtr1(downgrade,spec=-1.24,log2=0.38); Hcrtr2(downgrade,spec=-3.24,log2=2.37); Mc4r(downgrade,spec=-1.15,log2=0.05); Oxtr(downgrade,spec=-3.03,log2=0.60); Sstr2(downgrade,spec=-1.34,log2=1.21)</t>
         </is>
       </c>
       <c r="M25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Hcrtr1 | clinical/research: SB-334867 (research selective antagonist) | indication: addiction; anxiety (preclinical) || Hcrtr2 | FDA: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2 | clinical/research: JNJ-42847922 (selective OX2R) | indication: insomnia || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Oxtr | clinical/research: Intranasal oxytocin (autism/social trials; mostly failed); Carbetocin (Pabal - postpartum hemorrhage outside USA) | indication: autism research; social cognition; postpartum hemorrhage (Carbetocin EU) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Hcrtr1 | clinical/research: SB-334867 (research selective antagonist) | indication: addiction; anxiety (preclinical) || Hcrtr2 | FDA: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2 | clinical/research: JNJ-42847922 (selective OX2R) | indication: insomnia || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Oxtr | clinical/research: Intranasal oxytocin (autism/social trials; mostly failed); Carbetocin (Pabal - postpartum hemorrhage outside USA) | indication: autism research; social cognition; postpartum hemorrhage (Carbetocin EU) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr"/>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>no cell-type-specific GPCR; relying on 3 broadly_expressed_detectable candidates</t>
+          <t>no cell-type-specific GPCR; relying on 1 broadly_expressed_detectable candidates</t>
         </is>
       </c>
     </row>
@@ -8754,21 +8867,21 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Lateral mammillary excitatory</t>
+          <t>Nearby hypothalamic exclusion populations</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>143 MM-ant Foxb1 Glut</t>
+          <t>144 MM Foxb1 Glut</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>5437</v>
+        <v>8270</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -8777,47 +8890,43 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Esr1, Kcnc2, Nr4a2, Pdyn, Prlr, Slc17a6, Snap25, Syt4, Tac2</t>
+          <t>Avp, Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1, Lhx5, Nhlh2, Npy, Nts, Otp, Pnoc, Pomc, Uncx</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Foxb1, Gad1, Gad2, Slc32a1</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>Adcyap1r1, Avpr1a, Cckbr, Gabbr1, Gabbr2, Grm1, Hcrtr1, Hcrtr2, Mc4r, Oxtr, Sstr2</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>Htr2a(spec=1.70, log2=5.18, pct=73%, status=keep)</t>
-        </is>
-      </c>
+          <t>Foxa1, Lmx1a, Nr4a2, Pitx2, Slc17a6</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Htr2a[allen_only_keep, spec=+1.70, log2=5.18, pct=73%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Gabbr1[paper+allen_broadly_detectable, spec=-1.09, log2=8.19, pct=97%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.74, log2=8.36, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-0.99, log2=8.85, pct=97%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-4.46, log2=2.93, pct=49%; drugs: research_only_or_none]; Avpr1a[paper_only_allen_downgrade, spec=-2.15, log2=0.00, pct=0%; drugs: research_only_or_none]; Cckbr[paper_only_allen_downgrade, spec=-2.99, log2=1.36, pct=24%; drugs: research_only_or_none]; Hcrtr1[paper_only_allen_downgrade, spec=-1.58, log2=0.05, pct=1%; drugs: research_only_or_none]; Hcrtr2[paper_only_allen_downgrade, spec=-4.97, log2=0.64, pct=11%; drugs: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2]; Mc4r[paper_only_allen_downgrade, spec=-1.20, log2=0.01, pct=0%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Oxtr[paper_only_allen_downgrade, spec=-3.63, log2=0.00, pct=0%; drugs: research_only_or_none]; Sstr2[paper_only_allen_downgrade, spec=-1.93, log2=0.63, pct=12%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-1.00, log2=8.28, pct=98%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.75, log2=8.35, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[allen_only_broadly_detectable, spec=-0.13, log2=9.71, pct=100%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Htr2a | paper+broadly_detectable: Gabbr1, Gabbr2, Grm1 | paper_only: Adcyap1r1(downgrade,spec=-4.46,log2=2.93); Avpr1a(downgrade,spec=-2.15,log2=0.00); Cckbr(downgrade,spec=-2.99,log2=1.36); Hcrtr1(downgrade,spec=-1.58,log2=0.05); Hcrtr2(downgrade,spec=-4.97,log2=0.64); Mc4r(downgrade,spec=-1.20,log2=0.01); Oxtr(downgrade,spec=-3.63,log2=0.00); Sstr2(downgrade,spec=-1.93,log2=0.63)</t>
+          <t>allen_only_broadly_detectable: Gabbr1, Gabbr2, Grm1</t>
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>3</v>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Hcrtr1 | clinical/research: SB-334867 (research selective antagonist) | indication: addiction; anxiety (preclinical) || Hcrtr2 | FDA: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2 | clinical/research: JNJ-42847922 (selective OX2R) | indication: insomnia || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Oxtr | clinical/research: Intranasal oxytocin (autism/social trials; mostly failed); Carbetocin (Pabal - postpartum hemorrhage outside USA) | indication: autism research; social cognition; postpartum hemorrhage (Carbetocin EU) || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical)</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr"/>
-      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 3 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="110" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -8832,7 +8941,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>132 AHN-RCH-LHA Otp Fezf1 Glut</t>
+          <t>143 MM-ant Foxb1 Glut</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -8841,7 +8950,7 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4156</v>
+        <v>5437</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -8850,43 +8959,43 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1os, Otp, Pdrm12, Rprm</t>
+          <t>Avp, Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1, Lhx5, Nhlh2, Npy, Nts, Otp, Pnoc, Pomc, Uncx</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Nr4a2, Prlr, Slc17a6, Tac2</t>
+          <t>Foxa1, Lmx1a, Nr4a2, Pitx2, Slc17a6</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Htr2a(spec=1.70, log2=5.18, pct=73%, status=keep)</t>
+        </is>
+      </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.94, log2=8.33, pct=98%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-1.09, log2=10.18, pct=99%; drugs: research_only_or_none]</t>
+          <t>Htr2a[allen_only_keep, spec=+1.70, log2=5.18, pct=73%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Gabbr1[allen_only_broadly_detectable, spec=-1.09, log2=8.19, pct=97%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.74, log2=8.36, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[allen_only_broadly_detectable, spec=-0.99, log2=8.85, pct=97%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>allen_only_broadly_detectable: Gabbr1, Grm5</t>
+          <t>allen_only_keep: Htr2a | allen_only_broadly_detectable: Gabbr1, Gabbr2, Grm1</t>
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+          <t>Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical)</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t>no cell-type-specific GPCR; relying on 2 broadly_expressed_detectable candidates</t>
-        </is>
-      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="110" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
@@ -8901,7 +9010,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>098 AHN-SBPV-PVHd Pdrm12 Gaba</t>
+          <t>126 ARH-PVp Tbx3 Glut</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -8910,7 +9019,7 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>7028</v>
+        <v>4103</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -8919,41 +9028,41 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1os, Otp, Pdrm12, Rprm</t>
+          <t>Avp, Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1, Lhx5, Nhlh2, Npy, Nts, Otp, Pnoc, Pomc, Uncx</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Nr4a2, Prlr, Slc17a6, Tac2</t>
+          <t>Foxa1, Lmx1a, Nr4a2, Pitx2, Slc17a6</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="3" t="inlineStr"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1[allen_only_broadly_detectable, spec=-1.45, log2=7.83, pct=95%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-1.37, log2=9.89, pct=97%; drugs: research_only_or_none]</t>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-1.66, log2=7.62, pct=95%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>allen_only_broadly_detectable: Gabbr1, Grm5</t>
+          <t>allen_only_broadly_detectable: Gabbr1</t>
         </is>
       </c>
       <c r="M28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label)</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr"/>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>no cell-type-specific GPCR; relying on 2 broadly_expressed_detectable candidates</t>
+          <t>no cell-type-specific GPCR; relying on 1 broadly_expressed_detectable candidates</t>
         </is>
       </c>
     </row>
@@ -8970,7 +9079,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>102 DMH-LHA Gsx1 Gaba</t>
+          <t>132 AHN-RCH-LHA Otp Fezf1 Glut</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -8979,7 +9088,7 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>6768</v>
+        <v>4156</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -8988,116 +9097,112 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1os, Otp, Pdrm12, Rprm</t>
+          <t>Avp, Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1, Lhx5, Nhlh2, Npy, Nts, Otp, Pnoc, Pomc, Uncx</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Nr4a2, Prlr, Slc17a6, Tac2</t>
+          <t>Foxa1, Lmx1a, Nr4a2, Pitx2, Slc17a6</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr"/>
       <c r="J29" s="3" t="inlineStr"/>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1[allen_only_broadly_detectable, spec=-1.59, log2=7.69, pct=94%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]</t>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.94, log2=8.33, pct=98%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-1.09, log2=10.18, pct=99%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>allen_only_broadly_detectable: Gabbr1</t>
+          <t>allen_only_broadly_detectable: Gabbr1, Grm5</t>
         </is>
       </c>
       <c r="M29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label)</t>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr"/>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>no cell-type-specific GPCR; relying on 1 broadly_expressed_detectable candidates</t>
+          <t>no cell-type-specific GPCR; relying on 2 broadly_expressed_detectable candidates</t>
         </is>
       </c>
     </row>
     <row r="30" ht="110" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>ORBm</t>
+          <t>LM</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>L2/3 IT excitatory</t>
+          <t>Nearby hypothalamic exclusion populations</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>007 L2/3 IT CTX Glut</t>
+          <t>102 DMH-LHA Gsx1 Gaba</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>neighbor_control</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>8869</v>
+        <v>6768</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>OK: Allen ROI = PL-ILA-ORB (orbital + prelimbic + infralimbic).</t>
+          <t>BROAD: Allen ROI = HY (entire hypothalamus). Subclass `144 MM Foxb1 Glut` and `143 MM-ant Foxb1 Glut` cover the WHOLE mammillary body (lateral + medial + supramammillary) - NOT lateral-specific. To restrict to LM, dissect lateral mammillary nucleus directly OR co-stain with LM-discriminating markers (Lhx5, Cck, Calb2 vs medial-mammillary markers).</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Calb1, Cdh13, Cux1, Cux2, Fst, Rorb, Satb2, Slc17a6, Slc17a7</t>
+          <t>Avp, Cartpt, Cck, Fezf1, Foxb1, Gsx1, Lhx1, Lhx5, Nhlh2, Npy, Nts, Otp, Pnoc, Pomc, Uncx</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Bcl11b, Foxp2, Gad1, Gad2, Slc32a1</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>Cckbr, Cnr1, Gabbr1, Gabbr2, Grm1, Grm5, Htr2a, Npy1r, Oprd1, Oprm1, Sstr2</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>Cckbr(spec=0.08, log2=4.87, pct=73%, status=keep)</t>
-        </is>
-      </c>
+          <t>Foxa1, Lmx1a, Nr4a2, Pitx2, Slc17a6</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr"/>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>Cckbr[paper+allen_keep, spec=+0.08, log2=4.87, pct=73%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.34, log2=8.47, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.59, log2=9.02, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-0.90, log2=7.68, pct=94%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-0.82, log2=10.48, pct=100%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-6.50, log2=5.66, pct=83%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Htr2a[paper_only_allen_downgrade, spec=-4.91, log2=2.84, pct=45%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Npy1r[paper_only_allen_downgrade, spec=-2.34, log2=4.06, pct=64%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-3.19, log2=1.39, pct=25%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-3.60, log2=2.01, pct=35%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-7.42, log2=0.37, pct=7%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-1.59, log2=7.69, pct=94%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>both_keep: Cckbr | paper+broadly_detectable: Gabbr1, Gabbr2, Grm1, Grm5 | paper_only: Cnr1(downgrade,spec=-6.50,log2=5.66); Htr2a(downgrade,spec=-4.91,log2=2.84); Npy1r(downgrade,spec=-2.34,log2=4.06); Oprd1(downgrade,spec=-3.19,log2=1.39); Oprm1(downgrade,spec=-3.60,log2=2.01); Sstr2(downgrade,spec=-7.42,log2=0.37)</t>
+          <t>allen_only_broadly_detectable: Gabbr1</t>
         </is>
       </c>
       <c r="M30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N30" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label)</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 1 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="110" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -9107,12 +9212,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>L5 IT / L5 ET/PT output neurons</t>
+          <t>L2/3 IT excitatory</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>005 L5 IT CTX Glut</t>
+          <t>007 L2/3 IT CTX Glut</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -9121,7 +9226,7 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>4419</v>
+        <v>8869</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -9130,43 +9235,47 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Bcl11b, Crym, Deptor, Etv1, Fam84b, Fezf2, Pde1c, Satb2, Slc17a7</t>
+          <t>Calb1, Cdh13, Cux1, Cux2, Fst, Rorb, Satb2, Slc17a6, Slc17a7</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Cux1, Cux2, Gad1, Rorb</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="3" t="inlineStr"/>
+          <t>Bcl11b, Foxp2, Gad1, Gad2, Slc32a1</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Cckbr, Cnr1, Gabbr1, Gabbr2, Grm1, Grm5, Htr2a, Npy1r, Oprd1, Oprm1, Sstr2</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Cckbr(spec=0.08, log2=4.87, pct=73%, status=keep)</t>
+        </is>
+      </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.23, log2=8.58, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.38, log2=9.23, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-1.77, log2=9.53, pct=100%; drugs: research_only_or_none]</t>
+          <t>Cckbr[paper+allen_keep, spec=+0.08, log2=4.87, pct=73%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.34, log2=8.47, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.59, log2=9.02, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-0.90, log2=7.68, pct=94%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-0.82, log2=10.48, pct=100%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-6.50, log2=5.66, pct=83%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Htr2a[paper_only_allen_downgrade, spec=-4.91, log2=2.84, pct=45%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Npy1r[paper_only_allen_downgrade, spec=-2.34, log2=4.06, pct=64%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-3.19, log2=1.39, pct=25%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-3.60, log2=2.01, pct=35%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-7.42, log2=0.37, pct=7%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>allen_only_broadly_detectable: Gabbr1, Gabbr2, Grm5</t>
+          <t>both_keep: Cckbr | paper+broadly_detectable: Gabbr1, Gabbr2, Grm1, Grm5 | paper_only: Cnr1(downgrade,spec=-6.50,log2=5.66); Htr2a(downgrade,spec=-4.91,log2=2.84); Npy1r(downgrade,spec=-2.34,log2=4.06); Oprd1(downgrade,spec=-3.19,log2=1.39); Oprm1(downgrade,spec=-3.60,log2=2.01); Sstr2(downgrade,spec=-7.42,log2=0.37)</t>
         </is>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+          <t>Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr"/>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t>no cell-type-specific GPCR; relying on 3 broadly_expressed_detectable candidates</t>
-        </is>
-      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
     </row>
     <row r="32" ht="110" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -9181,7 +9290,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>022 L5 ET CTX Glut</t>
+          <t>005 L5 IT CTX Glut</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -9190,7 +9299,7 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>3739</v>
+        <v>4419</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -9208,34 +9317,34 @@
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>Gabbr1(spec=0.11, log2=8.81, pct=100%, status=keep); Mc4r(spec=0.81, log2=1.11, pct=20%, status=keep)</t>
-        </is>
-      </c>
+      <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1[allen_only_keep, spec=+0.11, log2=8.81, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Mc4r[allen_only_keep, spec=+0.81, log2=1.11, pct=20%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Cckbr[allen_only_broadly_detectable, spec=-0.08, log2=4.78, pct=74%; drugs: research_only_or_none]; Gabbr2[allen_only_broadly_detectable, spec=-1.65, log2=7.96, pct=98%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-0.87, log2=10.43, pct=100%; drugs: research_only_or_none]</t>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.23, log2=8.58, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.38, log2=9.23, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-1.77, log2=9.53, pct=100%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Gabbr1, Mc4r | allen_only_broadly_detectable: Cckbr, Gabbr2, Grm5</t>
+          <t>allen_only_broadly_detectable: Gabbr1, Gabbr2, Grm5</t>
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>3</v>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 3 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="110" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -9250,7 +9359,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>032 L5 NP CTX Glut</t>
+          <t>022 L5 ET CTX Glut</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -9259,7 +9368,7 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>3988</v>
+        <v>3739</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -9279,17 +9388,17 @@
       <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>Htr2c(spec=1.12, log2=8.34, pct=90%, status=keep); Avpr1a(spec=0.38, log2=0.46, pct=8%, status=candidate_to_validate)</t>
+          <t>Gabbr1(spec=0.11, log2=8.81, pct=100%, status=keep); Mc4r(spec=0.81, log2=1.11, pct=20%, status=keep)</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>Htr2c[allen_only_keep, spec=+1.12, log2=8.34, pct=90%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Avpr1a[allen_only_keep, spec=+0.38, log2=0.46, pct=8%; drugs: research_only_or_none]; Chrm2[allen_only_broadly_detectable, spec=-1.33, log2=7.84, pct=91%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Gabbr1[allen_only_broadly_detectable, spec=-0.98, log2=7.83, pct=96%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-0.25, log2=11.06, pct=100%; drugs: research_only_or_none]</t>
+          <t>Gabbr1[allen_only_keep, spec=+0.11, log2=8.81, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Mc4r[allen_only_keep, spec=+0.81, log2=1.11, pct=20%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Cckbr[allen_only_broadly_detectable, spec=-0.08, log2=4.78, pct=74%; drugs: research_only_or_none]; Gabbr2[allen_only_broadly_detectable, spec=-1.65, log2=7.96, pct=98%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-0.87, log2=10.43, pct=100%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Htr2c, Avpr1a | allen_only_broadly_detectable: Chrm2, Gabbr1, Grm5</t>
+          <t>allen_only_keep: Gabbr1, Mc4r | allen_only_broadly_detectable: Cckbr, Gabbr2, Grm5</t>
         </is>
       </c>
       <c r="M33" s="3" t="n">
@@ -9300,7 +9409,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr"/>
@@ -9314,12 +9423,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>L6 CT / L6b</t>
+          <t>L5 IT / L5 ET/PT output neurons</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>030 L6 CT CTX Glut</t>
+          <t>032 L5 NP CTX Glut</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -9328,7 +9437,7 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>21453</v>
+        <v>3988</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -9337,7 +9446,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Ccn2, Cplx3, Ctgf, Foxp2, Ntsr1, Nxph4, Slc17a7, Tle4</t>
+          <t>Bcl11b, Crym, Deptor, Etv1, Fam84b, Fezf2, Pde1c, Satb2, Slc17a7</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -9346,34 +9455,34 @@
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Htr2c(spec=1.12, log2=8.34, pct=90%, status=keep); Avpr1a(spec=0.38, log2=0.46, pct=8%, status=candidate_to_validate)</t>
+        </is>
+      </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.27, log2=8.53, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.48, log2=9.13, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-1.85, log2=9.46, pct=99%; drugs: research_only_or_none]; Htr1f[allen_only_broadly_detectable, spec=-1.80, log2=7.53, pct=94%; drugs: Lasmiditan (Reyvow; FDA 2019)]; Oprm1[allen_only_broadly_detectable, spec=-0.83, log2=4.77, pct=72%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
+          <t>Htr2c[allen_only_keep, spec=+1.12, log2=8.34, pct=90%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Avpr1a[allen_only_keep, spec=+0.38, log2=0.46, pct=8%; drugs: research_only_or_none]; Chrm2[allen_only_broadly_detectable, spec=-1.33, log2=7.84, pct=91%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Gabbr1[allen_only_broadly_detectable, spec=-0.98, log2=7.83, pct=96%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-0.25, log2=11.06, pct=100%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>allen_only_broadly_detectable: Gabbr1, Gabbr2, Grm5, Htr1f, Oprm1</t>
+          <t>allen_only_keep: Htr2c, Avpr1a | allen_only_broadly_detectable: Chrm2, Gabbr1, Grm5</t>
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr1f | FDA: Lasmiditan (Reyvow; FDA 2019) | indication: migraine (acute attack) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
+          <t>Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr"/>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t>no cell-type-specific GPCR; relying on 5 broadly_expressed_detectable candidates</t>
-        </is>
-      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
     </row>
     <row r="35" ht="110" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -9388,7 +9497,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>029 L6b CTX Glut</t>
+          <t>030 L6 CT CTX Glut</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -9397,7 +9506,7 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1586</v>
+        <v>21453</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -9418,29 +9527,29 @@
       <c r="J35" s="3" t="inlineStr"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>Cckbr[allen_only_broadly_detectable, spec=-0.08, log2=4.79, pct=73%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.11, log2=8.69, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.35, log2=8.26, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Oprm1[allen_only_broadly_detectable, spec=-0.09, log2=5.51, pct=80%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.27, log2=8.53, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.48, log2=9.13, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-1.85, log2=9.46, pct=99%; drugs: research_only_or_none]; Htr1f[allen_only_broadly_detectable, spec=-1.80, log2=7.53, pct=94%; drugs: Lasmiditan (Reyvow; FDA 2019)]; Oprm1[allen_only_broadly_detectable, spec=-0.83, log2=4.77, pct=72%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>allen_only_broadly_detectable: Cckbr, Gabbr1, Gabbr2, Oprm1</t>
+          <t>allen_only_broadly_detectable: Gabbr1, Gabbr2, Grm5, Htr1f, Oprm1</t>
         </is>
       </c>
       <c r="M35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr1f | FDA: Lasmiditan (Reyvow; FDA 2019) | indication: migraine (acute attack) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
+          <t>no cell-type-specific GPCR; relying on 5 broadly_expressed_detectable candidates</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9566,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>004 L6 IT CTX Glut</t>
+          <t>029 L6b CTX Glut</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -9466,7 +9575,7 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>11338</v>
+        <v>1586</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -9487,29 +9596,29 @@
       <c r="J36" s="3" t="inlineStr"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>Cckbr[allen_only_broadly_detectable, spec=-0.56, log2=4.31, pct=67%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.52, log2=8.29, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.26, log2=9.35, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[allen_only_broadly_detectable, spec=-1.93, log2=6.65, pct=88%; drugs: research_only_or_none]; Grm5[allen_only_broadly_detectable, spec=-1.57, log2=9.74, pct=100%; drugs: research_only_or_none]</t>
+          <t>Cckbr[allen_only_broadly_detectable, spec=-0.08, log2=4.79, pct=73%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.11, log2=8.69, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.35, log2=8.26, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Oprm1[allen_only_broadly_detectable, spec=-0.09, log2=5.51, pct=80%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>allen_only_broadly_detectable: Cckbr, Gabbr1, Gabbr2, Grm1, Grm5</t>
+          <t>allen_only_broadly_detectable: Cckbr, Gabbr1, Gabbr2, Oprm1</t>
         </is>
       </c>
       <c r="M36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+          <t>Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr"/>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>no cell-type-specific GPCR; relying on 5 broadly_expressed_detectable candidates</t>
+          <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9630,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Cortical interneurons</t>
+          <t>L6 CT / L6b</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>052 Pvalb Gaba</t>
+          <t>004 L6 IT CTX Glut</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -9535,7 +9644,7 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2869</v>
+        <v>11338</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -9544,43 +9653,43 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
+          <t>Ccn2, Cplx3, Ctgf, Foxp2, Ntsr1, Nxph4, Slc17a7, Tle4</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Cux1, Foxp2, Slc17a7</t>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>Oprd1(spec=0.17, log2=4.58, pct=68%, status=keep)</t>
-        </is>
-      </c>
+      <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>Oprd1[allen_only_keep, spec=+0.17, log2=4.58, pct=68%; drugs: research_only_or_none]; Adcyap1r1[allen_only_broadly_detectable, spec=-0.75, log2=5.35, pct=77%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.97, log2=7.84, pct=96%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.82, log2=8.79, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-0.84, log2=10.46, pct=100%; drugs: research_only_or_none]</t>
+          <t>Cckbr[allen_only_broadly_detectable, spec=-0.56, log2=4.31, pct=67%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.52, log2=8.29, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.26, log2=9.35, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[allen_only_broadly_detectable, spec=-1.93, log2=6.65, pct=88%; drugs: research_only_or_none]; Grm5[allen_only_broadly_detectable, spec=-1.57, log2=9.74, pct=100%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Oprd1 | allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Gabbr2, Grm5</t>
+          <t>allen_only_broadly_detectable: Cckbr, Gabbr1, Gabbr2, Grm1, Grm5</t>
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+          <t>Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 5 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="110" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
@@ -9595,7 +9704,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>053 Sst Gaba</t>
+          <t>052 Pvalb Gaba</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -9604,7 +9713,7 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>5377</v>
+        <v>2869</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -9622,34 +9731,34 @@
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr"/>
-      <c r="J38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>Oprd1(spec=0.17, log2=4.58, pct=68%, status=keep)</t>
+        </is>
+      </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1[allen_only_broadly_detectable, spec=-0.35, log2=5.75, pct=80%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.38, log2=8.43, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.24, log2=8.36, pct=98%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[allen_only_broadly_detectable, spec=-0.02, log2=8.56, pct=94%; drugs: research_only_or_none]; Grm5[allen_only_broadly_detectable, spec=-1.33, log2=9.97, pct=100%; drugs: research_only_or_none]; Oprm1[allen_only_broadly_detectable, spec=-0.82, log2=4.78, pct=67%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
+          <t>Oprd1[allen_only_keep, spec=+0.17, log2=4.58, pct=68%; drugs: research_only_or_none]; Adcyap1r1[allen_only_broadly_detectable, spec=-0.75, log2=5.35, pct=77%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.97, log2=7.84, pct=96%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.82, log2=8.79, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-0.84, log2=10.46, pct=100%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5, Oprm1</t>
+          <t>allen_only_keep: Oprd1 | allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Gabbr2, Grm5</t>
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
+          <t>Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr"/>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>no cell-type-specific GPCR; relying on 6 broadly_expressed_detectable candidates</t>
-        </is>
-      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
     </row>
     <row r="39" ht="110" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -9664,7 +9773,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>046 Vip Gaba</t>
+          <t>053 Sst Gaba</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -9673,7 +9782,7 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>3277</v>
+        <v>5377</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -9694,29 +9803,29 @@
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1[allen_only_broadly_detectable, spec=-2.00, log2=4.11, pct=57%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-1.02, log2=7.79, pct=93%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Npy1r[allen_only_broadly_detectable, spec=-1.29, log2=5.11, pct=68%; drugs: research_only_or_none]</t>
+          <t>Adcyap1r1[allen_only_broadly_detectable, spec=-0.35, log2=5.75, pct=80%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.38, log2=8.43, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.24, log2=8.36, pct=98%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[allen_only_broadly_detectable, spec=-0.02, log2=8.56, pct=94%; drugs: research_only_or_none]; Grm5[allen_only_broadly_detectable, spec=-1.33, log2=9.97, pct=100%; drugs: research_only_or_none]; Oprm1[allen_only_broadly_detectable, spec=-0.82, log2=4.78, pct=67%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Npy1r</t>
+          <t>allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5, Oprm1</t>
         </is>
       </c>
       <c r="M39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical)</t>
+          <t>Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr"/>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>no cell-type-specific GPCR; relying on 3 broadly_expressed_detectable candidates</t>
+          <t>no cell-type-specific GPCR; relying on 6 broadly_expressed_detectable candidates</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9842,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>049 Lamp5 Gaba</t>
+          <t>046 Vip Gaba</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -9742,7 +9851,7 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>2339</v>
+        <v>3277</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -9760,49 +9869,49 @@
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr"/>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>Gabbr2(spec=0.15, log2=9.61, pct=100%, status=keep)</t>
-        </is>
-      </c>
+      <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>Gabbr2[allen_only_keep, spec=+0.15, log2=9.61, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Adcyap1r1[allen_only_broadly_detectable, spec=-1.66, log2=4.45, pct=66%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.50, log2=8.30, pct=98%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-0.89, log2=10.41, pct=100%; drugs: research_only_or_none]; Hcrtr2[allen_only_broadly_detectable, spec=-1.94, log2=5.08, pct=67%; drugs: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2]</t>
+          <t>Adcyap1r1[allen_only_broadly_detectable, spec=-2.00, log2=4.11, pct=57%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-1.02, log2=7.79, pct=93%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Npy1r[allen_only_broadly_detectable, spec=-1.29, log2=5.11, pct=68%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Gabbr2 | allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Grm5, Hcrtr2</t>
+          <t>allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Npy1r</t>
         </is>
       </c>
       <c r="M40" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Hcrtr2 | FDA: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2 | clinical/research: JNJ-42847922 (selective OX2R) | indication: insomnia</t>
+          <t>Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical)</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 3 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="110" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>AId</t>
+          <t>ORBm</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Upper-layer IT excitatory</t>
+          <t>Cortical interneurons</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>007 L2/3 IT CTX Glut</t>
+          <t>049 Lamp5 Gaba</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -9811,52 +9920,48 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>7697</v>
+        <v>2339</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>OK: Allen ROI = AI (agranular insular).</t>
+          <t>OK: Allen ROI = PL-ILA-ORB (orbital + prelimbic + infralimbic).</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Calb1, Cux1, Cux2, Rorb, Satb2, Slc17a6, Slc17a7</t>
+          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Bcl11b, Foxp2, Gad1, Gad2, Slc32a1</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>Cckbr, Cnr1, Gabbr1, Gabbr2, Grm5, Htr2a, Npy1r, Oprd1, Oprm1, Sstr2</t>
-        </is>
-      </c>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Gpr88(spec=0.33, log2=4.77, pct=74%, status=keep)</t>
+          <t>Gabbr2(spec=0.15, log2=9.61, pct=100%, status=keep)</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>Gpr88[allen_only_keep, spec=+0.33, log2=4.77, pct=74%; drugs: research_only_or_none]; Cckbr[paper+allen_broadly_detectable, spec=-1.05, log2=4.52, pct=71%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.76, log2=8.52, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.45, log2=9.12, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-0.28, log2=10.52, pct=100%; drugs: research_only_or_none]; Grm1[allen_only_broadly_detectable, spec=-0.92, log2=7.76, pct=96%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-6.83, log2=5.24, pct=81%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Htr2a[paper_only_allen_downgrade, spec=-2.79, log2=4.48, pct=69%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Npy1r[paper_only_allen_downgrade, spec=-2.04, log2=3.75, pct=62%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-2.71, log2=1.63, pct=30%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-4.68, log2=2.21, pct=39%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-6.30, log2=0.56, pct=11%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+          <t>Gabbr2[allen_only_keep, spec=+0.15, log2=9.61, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Adcyap1r1[allen_only_broadly_detectable, spec=-1.66, log2=4.45, pct=66%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.50, log2=8.30, pct=98%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-0.89, log2=10.41, pct=100%; drugs: research_only_or_none]; Hcrtr2[allen_only_broadly_detectable, spec=-1.94, log2=5.08, pct=67%; drugs: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2]</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Gpr88 | paper+broadly_detectable: Cckbr, Gabbr1, Gabbr2, Grm5 | allen_only_broadly_detectable: Grm1 | paper_only: Cnr1(downgrade,spec=-6.83,log2=5.24); Htr2a(downgrade,spec=-2.79,log2=4.48); Npy1r(downgrade,spec=-2.04,log2=3.75); Oprd1(downgrade,spec=-2.71,log2=1.63); Oprm1(downgrade,spec=-4.68,log2=2.21); Sstr2(downgrade,spec=-6.30,log2=0.56)</t>
+          <t>allen_only_keep: Gabbr2 | allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Grm5, Hcrtr2</t>
         </is>
       </c>
       <c r="M41" s="3" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>Gpr88 | clinical/research: RTI-13951-33 (research agonist) | indication: obsessive-compulsive disorder; addiction (preclinical) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
+          <t>Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Hcrtr2 | FDA: Suvorexant (Belsomra); Lemborexant (Dayvigo); Daridorexant (Quviviq) - all Dual Orexin Receptor Antagonists hitting both 1+2 | clinical/research: JNJ-42847922 (selective OX2R) | indication: insomnia</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr"/>
@@ -9875,7 +9980,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>006 L4/5 IT CTX Glut</t>
+          <t>007 L2/3 IT CTX Glut</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -9884,7 +9989,7 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>12177</v>
+        <v>7697</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -9908,17 +10013,17 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Crhr1(spec=0.13, log2=3.94, pct=64%, status=keep)</t>
+          <t>Gpr88(spec=0.33, log2=4.77, pct=74%, status=keep)</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>Crhr1[allen_only_keep, spec=+0.13, log2=3.94, pct=64%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.58, log2=8.70, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.61, log2=8.96, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-1.07, log2=9.73, pct=100%; drugs: research_only_or_none]; Htr2a[paper+allen_broadly_detectable, spec=-0.69, log2=6.59, pct=91%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Htr1f[allen_only_broadly_detectable, spec=-1.26, log2=6.28, pct=86%; drugs: Lasmiditan (Reyvow; FDA 2019)]; Cckbr[paper_only_allen_downgrade, spec=-1.60, log2=3.96, pct=64%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-5.56, log2=6.51, pct=89%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Npy1r[paper_only_allen_downgrade, spec=-2.45, log2=3.34, pct=56%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-3.12, log2=1.22, pct=22%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-4.84, log2=2.05, pct=36%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-5.69, log2=1.16, pct=20%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+          <t>Gpr88[allen_only_keep, spec=+0.33, log2=4.77, pct=74%; drugs: research_only_or_none]; Cckbr[paper+allen_broadly_detectable, spec=-1.05, log2=4.52, pct=71%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.76, log2=8.52, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.45, log2=9.12, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-0.28, log2=10.52, pct=100%; drugs: research_only_or_none]; Grm1[allen_only_broadly_detectable, spec=-0.92, log2=7.76, pct=96%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-6.83, log2=5.24, pct=81%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Htr2a[paper_only_allen_downgrade, spec=-2.79, log2=4.48, pct=69%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Npy1r[paper_only_allen_downgrade, spec=-2.04, log2=3.75, pct=62%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-2.71, log2=1.63, pct=30%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-4.68, log2=2.21, pct=39%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-6.30, log2=0.56, pct=11%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Crhr1 | paper+broadly_detectable: Gabbr1, Gabbr2, Grm5, Htr2a | allen_only_broadly_detectable: Htr1f | paper_only: Cckbr(downgrade,spec=-1.60,log2=3.96); Cnr1(downgrade,spec=-5.56,log2=6.51); Npy1r(downgrade,spec=-2.45,log2=3.34); Oprd1(downgrade,spec=-3.12,log2=1.22); Oprm1(downgrade,spec=-4.84,log2=2.05); Sstr2(downgrade,spec=-5.69,log2=1.16)</t>
+          <t>allen_only_keep: Gpr88 | paper+broadly_detectable: Cckbr, Gabbr1, Gabbr2, Grm5 | allen_only_broadly_detectable: Grm1 | paper_only: Cnr1(downgrade,spec=-6.83,log2=5.24); Htr2a(downgrade,spec=-2.79,log2=4.48); Npy1r(downgrade,spec=-2.04,log2=3.75); Oprd1(downgrade,spec=-2.71,log2=1.63); Oprm1(downgrade,spec=-4.68,log2=2.21); Sstr2(downgrade,spec=-6.30,log2=0.56)</t>
         </is>
       </c>
       <c r="M42" s="3" t="n">
@@ -9929,7 +10034,7 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>Crhr1 | clinical/research: Verucerfont; Pexacerfont; Antalarmin; Emicerfont (depression/PTSD trials mostly failed) | indication: PTSD; major depression; alcohol use disorder (mostly failed) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Htr1f | FDA: Lasmiditan (Reyvow; FDA 2019) | indication: migraine (acute attack) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
+          <t>Gpr88 | clinical/research: RTI-13951-33 (research agonist) | indication: obsessive-compulsive disorder; addiction (preclinical) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr"/>
@@ -9943,12 +10048,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Deep-layer output neurons</t>
+          <t>Upper-layer IT excitatory</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>030 L6 CT CTX Glut</t>
+          <t>006 L4/5 IT CTX Glut</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -9957,7 +10062,7 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>13072</v>
+        <v>12177</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -9966,43 +10071,47 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Bcl11b, Crym, Etv1, Fezf2, Foxp2, Ntsr1, Slc17a7, Tle4</t>
+          <t>Calb1, Cux1, Cux2, Rorb, Satb2, Slc17a6, Slc17a7</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Cux1, Cux2, Gad1, Rorb</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr"/>
+          <t>Bcl11b, Foxp2, Gad1, Gad2, Slc32a1</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Cckbr, Cnr1, Gabbr1, Gabbr2, Grm5, Htr2a, Npy1r, Oprd1, Oprm1, Sstr2</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>Crhr1(spec=0.13, log2=3.94, pct=64%, status=keep)</t>
+        </is>
+      </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.73, log2=8.56, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.59, log2=8.98, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-1.39, log2=9.41, pct=99%; drugs: research_only_or_none]; Htr1f[allen_only_broadly_detectable, spec=-0.45, log2=7.10, pct=89%; drugs: Lasmiditan (Reyvow; FDA 2019)]</t>
+          <t>Crhr1[allen_only_keep, spec=+0.13, log2=3.94, pct=64%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.58, log2=8.70, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.61, log2=8.96, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-1.07, log2=9.73, pct=100%; drugs: research_only_or_none]; Htr2a[paper+allen_broadly_detectable, spec=-0.69, log2=6.59, pct=91%; drugs: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine]; Htr1f[allen_only_broadly_detectable, spec=-1.26, log2=6.28, pct=86%; drugs: Lasmiditan (Reyvow; FDA 2019)]; Cckbr[paper_only_allen_downgrade, spec=-1.60, log2=3.96, pct=64%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-5.56, log2=6.51, pct=89%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Npy1r[paper_only_allen_downgrade, spec=-2.45, log2=3.34, pct=56%; drugs: research_only_or_none]; Oprd1[paper_only_allen_downgrade, spec=-3.12, log2=1.22, pct=22%; drugs: research_only_or_none]; Oprm1[paper_only_allen_downgrade, spec=-4.84, log2=2.05, pct=36%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-5.69, log2=1.16, pct=20%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>allen_only_broadly_detectable: Gabbr1, Gabbr2, Grm5, Htr1f</t>
+          <t>allen_only_keep: Crhr1 | paper+broadly_detectable: Gabbr1, Gabbr2, Grm5, Htr2a | allen_only_broadly_detectable: Htr1f | paper_only: Cckbr(downgrade,spec=-1.60,log2=3.96); Cnr1(downgrade,spec=-5.56,log2=6.51); Npy1r(downgrade,spec=-2.45,log2=3.34); Oprd1(downgrade,spec=-3.12,log2=1.22); Oprm1(downgrade,spec=-4.84,log2=2.05); Sstr2(downgrade,spec=-5.69,log2=1.16)</t>
         </is>
       </c>
       <c r="M43" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr1f | FDA: Lasmiditan (Reyvow; FDA 2019) | indication: migraine (acute attack)</t>
+          <t>Crhr1 | clinical/research: Verucerfont; Pexacerfont; Antalarmin; Emicerfont (depression/PTSD trials mostly failed) | indication: PTSD; major depression; alcohol use disorder (mostly failed) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr2a | FDA: Pimavanserin (Nuplazid; FDA Parkinson psychosis); Risperidone; Olanzapine; Aripiprazole; Trazodone; Mirtazapine; Quetiapine; Clozapine | clinical/research: Psilocybin (FDA breakthrough for depression); MDMA-assisted therapy; Ketanserin (Europe) | indication: Parkinson psychosis; schizophrenia; treatment-resistant depression (psychedelic trials) || Htr1f | FDA: Lasmiditan (Reyvow; FDA 2019) | indication: migraine (acute attack) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
-        </is>
-      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
     </row>
     <row r="44" ht="110" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
@@ -10017,7 +10126,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>022 L5 ET CTX Glut</t>
+          <t>030 L6 CT CTX Glut</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -10026,7 +10135,7 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>1134</v>
+        <v>13072</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -10044,34 +10153,34 @@
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>Htr1f(spec=0.14, log2=7.55, pct=97%, status=keep); Htr1b(spec=0.03, log2=2.33, pct=44%, status=keep); Mc4r(spec=1.84, log2=2.16, pct=41%, status=keep)</t>
-        </is>
-      </c>
+      <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>Htr1f[allen_only_keep, spec=+0.14, log2=7.55, pct=97%; drugs: Lasmiditan (Reyvow; FDA 2019)]; Htr1b[allen_only_keep, spec=+0.03, log2=2.33, pct=44%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Mc4r[allen_only_keep, spec=+1.84, log2=2.16, pct=41%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Cckbr[allen_only_broadly_detectable, spec=-0.20, log2=5.36, pct=84%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.32, log2=8.96, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.58, log2=7.99, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-0.24, log2=10.56, pct=100%; drugs: research_only_or_none]</t>
+          <t>Gabbr1[allen_only_broadly_detectable, spec=-0.73, log2=8.56, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.59, log2=8.98, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-1.39, log2=9.41, pct=99%; drugs: research_only_or_none]; Htr1f[allen_only_broadly_detectable, spec=-0.45, log2=7.10, pct=89%; drugs: Lasmiditan (Reyvow; FDA 2019)]</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Htr1f, Htr1b, Mc4r | allen_only_broadly_detectable: Cckbr, Gabbr1, Gabbr2, Grm5</t>
+          <t>allen_only_broadly_detectable: Gabbr1, Gabbr2, Grm5, Htr1f</t>
         </is>
       </c>
       <c r="M44" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>4</v>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>Htr1f | FDA: Lasmiditan (Reyvow; FDA 2019) | indication: migraine (acute attack) || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+          <t>Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Htr1f | FDA: Lasmiditan (Reyvow; FDA 2019) | indication: migraine (acute attack)</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 4 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="110" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
@@ -10086,7 +10195,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>032 L5 NP CTX Glut</t>
+          <t>022 L5 ET CTX Glut</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -10095,7 +10204,7 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>3409</v>
+        <v>1134</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -10115,28 +10224,28 @@
       <c r="I45" s="3" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Grm5(spec=0.24, log2=10.80, pct=100%, status=keep); Avpr1a(spec=0.59, log2=0.63, pct=10%, status=keep_validate_spatially)</t>
+          <t>Htr1f(spec=0.14, log2=7.55, pct=97%, status=keep); Htr1b(spec=0.03, log2=2.33, pct=44%, status=keep); Mc4r(spec=1.84, log2=2.16, pct=41%, status=keep)</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>Grm5[allen_only_keep, spec=+0.24, log2=10.80, pct=100%; drugs: research_only_or_none]; Avpr1a[allen_only_keep, spec=+0.59, log2=0.63, pct=10%; drugs: research_only_or_none]; Chrm2[allen_only_broadly_detectable, spec=-0.44, log2=7.82, pct=89%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Gabbr1[allen_only_broadly_detectable, spec=-1.47, log2=7.82, pct=95%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Htr2c[allen_only_broadly_detectable, spec=-0.14, log2=7.39, pct=83%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]</t>
+          <t>Htr1f[allen_only_keep, spec=+0.14, log2=7.55, pct=97%; drugs: Lasmiditan (Reyvow; FDA 2019)]; Htr1b[allen_only_keep, spec=+0.03, log2=2.33, pct=44%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Mc4r[allen_only_keep, spec=+1.84, log2=2.16, pct=41%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Cckbr[allen_only_broadly_detectable, spec=-0.20, log2=5.36, pct=84%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.32, log2=8.96, pct=100%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.58, log2=7.99, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-0.24, log2=10.56, pct=100%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Grm5, Avpr1a | allen_only_broadly_detectable: Chrm2, Gabbr1, Htr2c</t>
+          <t>allen_only_keep: Htr1f, Htr1b, Mc4r | allen_only_broadly_detectable: Cckbr, Gabbr1, Gabbr2, Grm5</t>
         </is>
       </c>
       <c r="M45" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction</t>
+          <t>Htr1f | FDA: Lasmiditan (Reyvow; FDA 2019) | indication: migraine (acute attack) || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr"/>
@@ -10155,7 +10264,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>029 L6b CTX Glut</t>
+          <t>032 L5 NP CTX Glut</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -10164,7 +10273,7 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>439</v>
+        <v>3409</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -10182,34 +10291,34 @@
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>Grm5(spec=0.24, log2=10.80, pct=100%, status=keep); Avpr1a(spec=0.59, log2=0.63, pct=10%, status=keep_validate_spatially)</t>
+        </is>
+      </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>Cckbr[allen_only_broadly_detectable, spec=-0.41, log2=5.15, pct=78%; drugs: research_only_or_none]; Drd1[allen_only_broadly_detectable, spec=-0.56, log2=4.70, pct=74%; drugs: Apomorphine (mixed); Pergolide (partial)]; Gabbr1[allen_only_broadly_detectable, spec=-0.55, log2=8.74, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.39, log2=8.18, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-1.55, log2=9.25, pct=99%; drugs: research_only_or_none]; Oprm1[allen_only_broadly_detectable, spec=-1.78, log2=5.11, pct=76%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
+          <t>Grm5[allen_only_keep, spec=+0.24, log2=10.80, pct=100%; drugs: research_only_or_none]; Avpr1a[allen_only_keep, spec=+0.59, log2=0.63, pct=10%; drugs: research_only_or_none]; Chrm2[allen_only_broadly_detectable, spec=-0.44, log2=7.82, pct=89%; drugs: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic)]; Gabbr1[allen_only_broadly_detectable, spec=-1.47, log2=7.82, pct=95%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Htr2c[allen_only_broadly_detectable, spec=-0.14, log2=7.39, pct=83%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>allen_only_broadly_detectable: Cckbr, Drd1, Gabbr1, Gabbr2, Grm5, Oprm1</t>
+          <t>allen_only_keep: Grm5, Avpr1a | allen_only_broadly_detectable: Chrm2, Gabbr1, Htr2c</t>
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
+          <t>Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Chrm2 | FDA: Donepezil; Rivastigmine (broad cholinesterase; indirect); Solifenacin (broad antimuscarinic) | clinical/research: Methoctramine (research) | indication: Alzheimer disease; overactive bladder || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr"/>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>no cell-type-specific GPCR; relying on 6 broadly_expressed_detectable candidates</t>
-        </is>
-      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
     </row>
     <row r="47" ht="110" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
@@ -10219,12 +10328,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Cortical interneurons</t>
+          <t>Deep-layer output neurons</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>053 Sst Gaba</t>
+          <t>029 L6b CTX Glut</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -10233,7 +10342,7 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>5983</v>
+        <v>439</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -10242,41 +10351,41 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
+          <t>Bcl11b, Crym, Etv1, Fezf2, Foxp2, Ntsr1, Slc17a7, Tle4</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Cux1, Foxp2, Slc17a7</t>
+          <t>Cux1, Cux2, Gad1, Rorb</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr"/>
       <c r="J47" s="3" t="inlineStr"/>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1[allen_only_broadly_detectable, spec=-0.00, log2=6.18, pct=84%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.84, log2=8.44, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.15, log2=8.42, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[allen_only_broadly_detectable, spec=-0.21, log2=8.47, pct=94%; drugs: research_only_or_none]; Grm5[allen_only_broadly_detectable, spec=-0.93, log2=9.87, pct=99%; drugs: research_only_or_none]</t>
+          <t>Cckbr[allen_only_broadly_detectable, spec=-0.41, log2=5.15, pct=78%; drugs: research_only_or_none]; Drd1[allen_only_broadly_detectable, spec=-0.56, log2=4.70, pct=74%; drugs: Apomorphine (mixed); Pergolide (partial)]; Gabbr1[allen_only_broadly_detectable, spec=-0.55, log2=8.74, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.39, log2=8.18, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-1.55, log2=9.25, pct=99%; drugs: research_only_or_none]; Oprm1[allen_only_broadly_detectable, spec=-1.78, log2=5.11, pct=76%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5</t>
+          <t>allen_only_broadly_detectable: Cckbr, Drd1, Gabbr1, Gabbr2, Grm5, Oprm1</t>
         </is>
       </c>
       <c r="M47" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+          <t>Cckbr | clinical/research: Netazepide / YF476 (research antagonist) | indication: acid hypersecretion; anxiety (preclinical) || Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr"/>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>no cell-type-specific GPCR; relying on 5 broadly_expressed_detectable candidates</t>
+          <t>no cell-type-specific GPCR; relying on 6 broadly_expressed_detectable candidates</t>
         </is>
       </c>
     </row>
@@ -10293,7 +10402,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>052 Pvalb Gaba</t>
+          <t>053 Sst Gaba</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -10302,7 +10411,7 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3617</v>
+        <v>5983</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -10323,12 +10432,12 @@
       <c r="J48" s="3" t="inlineStr"/>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1[allen_only_broadly_detectable, spec=-0.74, log2=5.44, pct=77%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-1.33, log2=7.95, pct=97%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.74, log2=8.83, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-0.57, log2=10.24, pct=100%; drugs: research_only_or_none]; Oprd1[allen_only_broadly_detectable, spec=-0.24, log2=4.10, pct=61%; drugs: research_only_or_none]</t>
+          <t>Adcyap1r1[allen_only_broadly_detectable, spec=-0.00, log2=6.18, pct=84%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.84, log2=8.44, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-1.15, log2=8.42, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[allen_only_broadly_detectable, spec=-0.21, log2=8.47, pct=94%; drugs: research_only_or_none]; Grm5[allen_only_broadly_detectable, spec=-0.93, log2=9.87, pct=99%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Gabbr2, Grm5, Oprd1</t>
+          <t>allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Gabbr2, Grm1, Grm5</t>
         </is>
       </c>
       <c r="M48" s="3" t="n">
@@ -10339,7 +10448,7 @@
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical)</t>
+          <t>Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr"/>
@@ -10362,7 +10471,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>046 Vip Gaba</t>
+          <t>052 Pvalb Gaba</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -10371,7 +10480,7 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>3706</v>
+        <v>3617</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -10389,34 +10498,34 @@
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>Gpr101(spec=0.07, log2=0.31, pct=5%, status=candidate_to_validate)</t>
-        </is>
-      </c>
+      <c r="J49" s="3" t="inlineStr"/>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>Gpr101[allen_only_keep, spec=+0.07, log2=0.31, pct=5%; drugs: research_only_or_none]; Adcyap1r1[allen_only_broadly_detectable, spec=-1.85, log2=4.34, pct=60%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-1.43, log2=7.85, pct=94%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-1.72, log2=9.08, pct=97%; drugs: research_only_or_none]; Npy1r[allen_only_broadly_detectable, spec=-0.99, log2=4.80, pct=65%; drugs: research_only_or_none]</t>
+          <t>Adcyap1r1[allen_only_broadly_detectable, spec=-0.74, log2=5.44, pct=77%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-1.33, log2=7.95, pct=97%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[allen_only_broadly_detectable, spec=-0.74, log2=8.83, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[allen_only_broadly_detectable, spec=-0.57, log2=10.24, pct=100%; drugs: research_only_or_none]; Oprd1[allen_only_broadly_detectable, spec=-0.24, log2=4.10, pct=61%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Gpr101 | allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Grm5, Npy1r</t>
+          <t>allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Gabbr2, Grm5, Oprd1</t>
         </is>
       </c>
       <c r="M49" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>Gpr101 | clinical/research: research only (orphan) | indication: X-LAG / X-linked acrogigantism research || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical)</t>
+          <t>Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Oprd1 | clinical/research: DPDPE; ADL-5859; SNC-80 (research) | indication: depression; chronic pain (preclinical)</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr"/>
-      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>no cell-type-specific GPCR; relying on 5 broadly_expressed_detectable candidates</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="110" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
@@ -10431,7 +10540,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>049 Lamp5 Gaba</t>
+          <t>046 Vip Gaba</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -10440,7 +10549,7 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>3704</v>
+        <v>3706</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -10460,28 +10569,28 @@
       <c r="I50" s="3" t="inlineStr"/>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Gabbr2(spec=0.08, log2=9.57, pct=99%, status=keep); Gpr6(spec=0.20, log2=0.51, pct=9%, status=candidate_to_validate)</t>
+          <t>Gpr101(spec=0.07, log2=0.31, pct=5%, status=candidate_to_validate)</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>Gabbr2[allen_only_keep, spec=+0.08, log2=9.57, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Gpr6[allen_only_keep, spec=+0.20, log2=0.51, pct=9%; drugs: research_only_or_none]; Adcyap1r1[allen_only_broadly_detectable, spec=-1.69, log2=4.49, pct=67%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.96, log2=8.33, pct=98%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-0.63, log2=10.17, pct=99%; drugs: research_only_or_none]</t>
+          <t>Gpr101[allen_only_keep, spec=+0.07, log2=0.31, pct=5%; drugs: research_only_or_none]; Adcyap1r1[allen_only_broadly_detectable, spec=-1.85, log2=4.34, pct=60%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-1.43, log2=7.85, pct=94%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-1.72, log2=9.08, pct=97%; drugs: research_only_or_none]; Npy1r[allen_only_broadly_detectable, spec=-0.99, log2=4.80, pct=65%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Gabbr2, Gpr6 | allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Grm5</t>
+          <t>allen_only_keep: Gpr101 | allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Grm5, Npy1r</t>
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Gpr6 | clinical/research: research antagonists for Parkinson disease | indication: Parkinson research (preclinical) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
+          <t>Gpr101 | clinical/research: research only (orphan) | indication: X-LAG / X-linked acrogigantism research || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Npy1r | clinical/research: BIBP-3226 (research antagonist) | indication: obesity; pain (preclinical)</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr"/>
@@ -10490,17 +10599,17 @@
     <row r="51" ht="110" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>AId</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CA1 pyramidal</t>
+          <t>Cortical interneurons</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>016 CA1-ProS Glut</t>
+          <t>049 Lamp5 Gaba</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -10509,52 +10618,48 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>24868</v>
+        <v>3704</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>GOOD: Allen ROI = HIP (hippocampus); subclass anchors split CA1 (016 CA1-ProS), CA2 (025 CA2-FC-IG), CA3 (017 CA3), and DG (037 DG) cleanly.</t>
+          <t>OK: Allen ROI = AI (agranular insular).</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Fibcd1, Mpped1, Pou3f1, Slc17a7, Spink8, Wfs1</t>
+          <t>Cck, Gad1, Gad2, Lamp5, Npy, Pvalb, Reln, Slc32a1, Sncg, Sst, Vip</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Calb1, Cnih3, Prox1, Rgs14</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>Adcyap1r1, Cnr1, Drd1, Drd2, Gabbr1, Gabbr2, Grm1, Grm5, Htr1a, Htr1b, Htr2c, Oprm1, Sstr2</t>
-        </is>
-      </c>
+          <t>Cux1, Foxp2, Slc17a7</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr"/>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Htr1a(spec=0.96, log2=3.33, pct=55%, status=keep); Mc4r(spec=0.08, log2=1.12, pct=21%, status=keep)</t>
+          <t>Gabbr2(spec=0.08, log2=9.57, pct=99%, status=keep); Gpr6(spec=0.20, log2=0.51, pct=9%, status=candidate_to_validate)</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>Htr1a[paper+allen_keep, spec=+0.96, log2=3.33, pct=55%; drugs: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone]; Mc4r[allen_only_keep, spec=+0.08, log2=1.12, pct=21%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Gabbr1[paper+allen_broadly_detectable, spec=-0.45, log2=8.70, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.96, log2=7.93, pct=96%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-1.93, log2=6.56, pct=85%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-0.36, log2=10.79, pct=100%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-4.69, log2=1.63, pct=29%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-7.05, log2=5.38, pct=80%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Drd1[paper_only_allen_downgrade, spec=-1.77, log2=0.02, pct=0%; drugs: Apomorphine (mixed); Pergolide (partial)]; Drd2[paper_only_allen_downgrade, spec=-1.50, log2=0.01, pct=0%; drugs: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect)]; Htr1b[paper_only_allen_downgrade, spec=-1.27, log2=2.14, pct=38%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Htr2c[paper_only_allen_downgrade, spec=-10.14, log2=1.80, pct=29%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Oprm1[paper_only_allen_downgrade, spec=-6.78, log2=0.18, pct=3%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-3.27, log2=0.51, pct=10%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
+          <t>Gabbr2[allen_only_keep, spec=+0.08, log2=9.57, pct=99%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Gpr6[allen_only_keep, spec=+0.20, log2=0.51, pct=9%; drugs: research_only_or_none]; Adcyap1r1[allen_only_broadly_detectable, spec=-1.69, log2=4.49, pct=67%; drugs: research_only_or_none]; Gabbr1[allen_only_broadly_detectable, spec=-0.96, log2=8.33, pct=98%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Grm5[allen_only_broadly_detectable, spec=-0.63, log2=10.17, pct=99%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>both_keep: Htr1a | allen_only_keep: Mc4r | paper+broadly_detectable: Gabbr1, Gabbr2, Grm1, Grm5 | paper_only: Adcyap1r1(downgrade,spec=-4.69,log2=1.63); Cnr1(downgrade,spec=-7.05,log2=5.38); Drd1(downgrade,spec=-1.77,log2=0.02); Drd2(downgrade,spec=-1.50,log2=0.01); Htr1b(downgrade,spec=-1.27,log2=2.14); Htr2c(downgrade,spec=-10.14,log2=1.80); Oprm1(downgrade,spec=-6.78,log2=0.18); Sstr2(downgrade,spec=-3.27,log2=0.51)</t>
+          <t>allen_only_keep: Gabbr2, Gpr6 | allen_only_broadly_detectable: Adcyap1r1, Gabbr1, Grm5</t>
         </is>
       </c>
       <c r="M51" s="3" t="n">
         <v>2</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>Htr1a | FDA: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone | clinical/research: NLX-101 (depression) | indication: generalized anxiety; major depression || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Drd2 | FDA: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect) | clinical/research: many | indication: schizophrenia; bipolar; Parkinson disease; hyperprolactinemia || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
+          <t>Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Gpr6 | clinical/research: research antagonists for Parkinson disease | indication: Parkinson research (preclinical) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research)</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr"/>
@@ -10568,12 +10673,12 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CA2 pyramidal</t>
+          <t>CA1 pyramidal</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>025 CA2-FC-IG Glut</t>
+          <t>016 CA1-ProS Glut</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -10582,7 +10687,7 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>327</v>
+        <v>24868</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -10591,43 +10696,43 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Amigo2, Avpr1b, Cacng5, Map3k15, Pcp4, Rgs14, Slc17a7</t>
+          <t>Fibcd1, Mpped1, Pou3f1, Slc17a7, Spink8, Wfs1</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Cnih3, Prox1, Wfs1</t>
+          <t>Calb1, Cnih3, Prox1, Rgs14</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Avpr1a, Avpr1b, Cnr1, Drd1, Gabbr1, Gabbr2, Grm1, Grm5, Htr1a, Oxtr</t>
+          <t>Adcyap1r1, Cnr1, Drd1, Drd2, Gabbr1, Gabbr2, Grm1, Grm5, Htr1a, Htr1b, Htr2c, Oprm1, Sstr2</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Avpr1b(spec=0.77, log2=0.81, pct=17%, status=keep_validate_spatially)</t>
+          <t>Htr1a(spec=0.96, log2=3.33, pct=55%, status=keep); Mc4r(spec=0.08, log2=1.12, pct=21%, status=keep)</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Avpr1b[paper+allen_keep, spec=+0.77, log2=0.81, pct=17%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.99, log2=8.16, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.64, log2=8.25, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-0.81, log2=10.35, pct=100%; drugs: research_only_or_none]; Avpr1a[paper_only_allen_downgrade, spec=-0.08, log2=0.03, pct=1%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-6.66, log2=5.77, pct=87%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Drd1[paper_only_allen_downgrade, spec=-0.64, log2=1.15, pct=21%; drugs: Apomorphine (mixed); Pergolide (partial)]; Grm1[paper_only_allen_downgrade, spec=-2.06, log2=6.43, pct=89%; drugs: research_only_or_none]; Htr1a[paper_only_allen_downgrade, spec=-3.00, log2=0.33, pct=7%; drugs: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone]; Oxtr[paper_only_allen_downgrade, spec=-0.07, log2=1.27, pct=24%; drugs: research_only_or_none]</t>
+          <t>Htr1a[paper+allen_keep, spec=+0.96, log2=3.33, pct=55%; drugs: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone]; Mc4r[allen_only_keep, spec=+0.08, log2=1.12, pct=21%; drugs: Setmelanotide (Imcivree; FDA 2020)]; Gabbr1[paper+allen_broadly_detectable, spec=-0.45, log2=8.70, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.96, log2=7.93, pct=96%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-1.93, log2=6.56, pct=85%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-0.36, log2=10.79, pct=100%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-4.69, log2=1.63, pct=29%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-7.05, log2=5.38, pct=80%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Drd1[paper_only_allen_downgrade, spec=-1.77, log2=0.02, pct=0%; drugs: Apomorphine (mixed); Pergolide (partial)]; Drd2[paper_only_allen_downgrade, spec=-1.50, log2=0.01, pct=0%; drugs: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect)]; Htr1b[paper_only_allen_downgrade, spec=-1.27, log2=2.14, pct=38%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Htr2c[paper_only_allen_downgrade, spec=-10.14, log2=1.80, pct=29%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]; Oprm1[paper_only_allen_downgrade, spec=-6.78, log2=0.18, pct=3%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]; Sstr2[paper_only_allen_downgrade, spec=-3.27, log2=0.51, pct=10%; drugs: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy)]</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>both_keep: Avpr1b | paper+broadly_detectable: Gabbr1, Gabbr2, Grm5 | paper_only: Avpr1a(downgrade,spec=-0.08,log2=0.03); Cnr1(downgrade,spec=-6.66,log2=5.77); Drd1(downgrade,spec=-0.64,log2=1.15); Grm1(downgrade,spec=-2.06,log2=6.43); Htr1a(downgrade,spec=-3.00,log2=0.33); Oxtr(downgrade,spec=-0.07,log2=1.27)</t>
+          <t>both_keep: Htr1a | allen_only_keep: Mc4r | paper+broadly_detectable: Gabbr1, Gabbr2, Grm1, Grm5 | paper_only: Adcyap1r1(downgrade,spec=-4.69,log2=1.63); Cnr1(downgrade,spec=-7.05,log2=5.38); Drd1(downgrade,spec=-1.77,log2=0.02); Drd2(downgrade,spec=-1.50,log2=0.01); Htr1b(downgrade,spec=-1.27,log2=2.14); Htr2c(downgrade,spec=-10.14,log2=1.80); Oprm1(downgrade,spec=-6.78,log2=0.18); Sstr2(downgrade,spec=-3.27,log2=0.51)</t>
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>Avpr1b | clinical/research: Nelivaptan / SSR149415 (depression trials failed); ABT-558 | indication: major depression; PTSD; anxiety (failed/discontinued) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Htr1a | FDA: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone | clinical/research: NLX-101 (depression) | indication: generalized anxiety; major depression || Oxtr | clinical/research: Intranasal oxytocin (autism/social trials; mostly failed); Carbetocin (Pabal - postpartum hemorrhage outside USA) | indication: autism research; social cognition; postpartum hemorrhage (Carbetocin EU)</t>
+          <t>Htr1a | FDA: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone | clinical/research: NLX-101 (depression) | indication: generalized anxiety; major depression || Mc4r | FDA: Setmelanotide (Imcivree; FDA 2020) | clinical/research: Bremelanotide (Vyleesi PT-141 - MC4 partial agonist for HSDD) | indication: rare genetic obesity (POMC/LEPR/PCSK1 deficiency; Bardet-Biedl syndrome); female sexual dysfunction (Bremelanotide) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Drd2 | FDA: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect) | clinical/research: many | indication: schizophrenia; bipolar; Parkinson disease; hyperprolactinemia || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia || Sstr2 | FDA: Octreotide; Lanreotide; Pasireotide (broad SSTR); Lutetium Lu-177 dotatate (radiotherapy) | indication: acromegaly; neuroendocrine tumors (NETs); Cushing disease</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr"/>
@@ -10641,12 +10746,12 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>CA3 pyramidal</t>
+          <t>CA2 pyramidal</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>017 CA3 Glut</t>
+          <t>025 CA2-FC-IG Glut</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -10655,7 +10760,7 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>4799</v>
+        <v>327</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -10664,43 +10769,43 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>Calb2, Cnih3, Coch, Lct, Slc17a7</t>
+          <t>Amigo2, Avpr1b, Cacng5, Map3k15, Pcp4, Rgs14, Slc17a7</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>Prox1, Rgs14, Wfs1</t>
+          <t>Cnih3, Prox1, Wfs1</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Adcyap1r1, Cnr1, Drd2, Gabbr1, Gabbr2, Grm1, Grm5, Htr1a, Htr1b, Oprm1</t>
+          <t>Avpr1a, Avpr1b, Cnr1, Drd1, Gabbr1, Gabbr2, Grm1, Grm5, Htr1a, Oxtr</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>Npy2r(spec=2.24, log2=5.61, pct=85%, status=keep); Hcrtr1(spec=0.01, log2=0.28, pct=6%, status=candidate_to_validate)</t>
+          <t>Avpr1b(spec=0.77, log2=0.81, pct=17%, status=keep_validate_spatially)</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>Npy2r[allen_only_keep, spec=+2.24, log2=5.61, pct=85%; drugs: research_only_or_none]; Hcrtr1[allen_only_keep, spec=+0.01, log2=0.28, pct=6%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.90, log2=8.25, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.87, log2=9.02, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-1.10, log2=7.39, pct=93%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-0.96, log2=10.19, pct=100%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-5.28, log2=1.04, pct=20%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-5.87, log2=6.56, pct=94%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Drd2[paper_only_allen_downgrade, spec=-1.32, log2=0.19, pct=3%; drugs: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect)]; Htr1a[paper_only_allen_downgrade, spec=-1.93, log2=1.39, pct=28%; drugs: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone]; Htr1b[paper_only_allen_downgrade, spec=-3.36, log2=0.05, pct=1%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Oprm1[paper_only_allen_downgrade, spec=-6.77, log2=0.19, pct=4%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
+          <t>Avpr1b[paper+allen_keep, spec=+0.77, log2=0.81, pct=17%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.99, log2=8.16, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-1.64, log2=8.25, pct=97%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm5[paper+allen_broadly_detectable, spec=-0.81, log2=10.35, pct=100%; drugs: research_only_or_none]; Avpr1a[paper_only_allen_downgrade, spec=-0.08, log2=0.03, pct=1%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-6.66, log2=5.77, pct=87%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Drd1[paper_only_allen_downgrade, spec=-0.64, log2=1.15, pct=21%; drugs: Apomorphine (mixed); Pergolide (partial)]; Grm1[paper_only_allen_downgrade, spec=-2.06, log2=6.43, pct=89%; drugs: research_only_or_none]; Htr1a[paper_only_allen_downgrade, spec=-3.00, log2=0.33, pct=7%; drugs: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone]; Oxtr[paper_only_allen_downgrade, spec=-0.07, log2=1.27, pct=24%; drugs: research_only_or_none]</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>allen_only_keep: Npy2r, Hcrtr1 | paper+broadly_detectable: Gabbr1, Gabbr2, Grm1, Grm5 | paper_only: Adcyap1r1(downgrade,spec=-5.28,log2=1.04); Cnr1(downgrade,spec=-5.87,log2=6.56); Drd2(downgrade,spec=-1.32,log2=0.19); Htr1a(downgrade,spec=-1.93,log2=1.39); Htr1b(downgrade,spec=-3.36,log2=0.05); Oprm1(downgrade,spec=-6.77,log2=0.19)</t>
+          <t>both_keep: Avpr1b | paper+broadly_detectable: Gabbr1, Gabbr2, Grm5 | paper_only: Avpr1a(downgrade,spec=-0.08,log2=0.03); Cnr1(downgrade,spec=-6.66,log2=5.77); Drd1(downgrade,spec=-0.64,log2=1.15); Grm1(downgrade,spec=-2.06,log2=6.43); Htr1a(downgrade,spec=-3.00,log2=0.33); Oxtr(downgrade,spec=-0.07,log2=1.27)</t>
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>Npy2r | clinical/research: BIIE-0246 (research antagonist) | indication: food intake; anxiety (preclinical) || Hcrtr1 | clinical/research: SB-334867 (research selective antagonist) | indication: addiction; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Drd2 | FDA: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect) | clinical/research: many | indication: schizophrenia; bipolar; Parkinson disease; hyperprolactinemia || Htr1a | FDA: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone | clinical/research: NLX-101 (depression) | indication: generalized anxiety; major depression || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
+          <t>Avpr1b | clinical/research: Nelivaptan / SSR149415 (depression trials failed); ABT-558 | indication: major depression; PTSD; anxiety (failed/discontinued) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Avpr1a | clinical/research: Balovaptan / RG7314 (autism trials FAILED 2020) | indication: autism social-cognition trials || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Drd1 | FDA: Apomorphine (mixed); Pergolide (partial) | clinical/research: SKF-81297; SKF-38393 (research agonists); SCH-23390 (antagonist) | indication: Parkinson disease; addiction research || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Htr1a | FDA: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone | clinical/research: NLX-101 (depression) | indication: generalized anxiety; major depression || Oxtr | clinical/research: Intranasal oxytocin (autism/social trials; mostly failed); Carbetocin (Pabal - postpartum hemorrhage outside USA) | indication: autism research; social cognition; postpartum hemorrhage (Carbetocin EU)</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr"/>
@@ -10714,66 +10819,139 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
+          <t>CA3 pyramidal</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>017 CA3 Glut</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>4799</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>GOOD: Allen ROI = HIP (hippocampus); subclass anchors split CA1 (016 CA1-ProS), CA2 (025 CA2-FC-IG), CA3 (017 CA3), and DG (037 DG) cleanly.</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Calb2, Cnih3, Coch, Lct, Slc17a7</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Prox1, Rgs14, Wfs1</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>Adcyap1r1, Cnr1, Drd2, Gabbr1, Gabbr2, Grm1, Grm5, Htr1a, Htr1b, Oprm1</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>Npy2r(spec=2.24, log2=5.61, pct=85%, status=keep); Hcrtr1(spec=0.01, log2=0.28, pct=6%, status=candidate_to_validate)</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Npy2r[allen_only_keep, spec=+2.24, log2=5.61, pct=85%; drugs: research_only_or_none]; Hcrtr1[allen_only_keep, spec=+0.01, log2=0.28, pct=6%; drugs: research_only_or_none]; Gabbr1[paper+allen_broadly_detectable, spec=-0.90, log2=8.25, pct=99%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper+allen_broadly_detectable, spec=-0.87, log2=9.02, pct=100%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Grm1[paper+allen_broadly_detectable, spec=-1.10, log2=7.39, pct=93%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-0.96, log2=10.19, pct=100%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-5.28, log2=1.04, pct=20%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-5.87, log2=6.56, pct=94%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Drd2[paper_only_allen_downgrade, spec=-1.32, log2=0.19, pct=3%; drugs: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect)]; Htr1a[paper_only_allen_downgrade, spec=-1.93, log2=1.39, pct=28%; drugs: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone]; Htr1b[paper_only_allen_downgrade, spec=-3.36, log2=0.05, pct=1%; drugs: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan]; Oprm1[paper_only_allen_downgrade, spec=-6.77, log2=0.19, pct=4%; drugs: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide]</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>allen_only_keep: Npy2r, Hcrtr1 | paper+broadly_detectable: Gabbr1, Gabbr2, Grm1, Grm5 | paper_only: Adcyap1r1(downgrade,spec=-5.28,log2=1.04); Cnr1(downgrade,spec=-5.87,log2=6.56); Drd2(downgrade,spec=-1.32,log2=0.19); Htr1a(downgrade,spec=-1.93,log2=1.39); Htr1b(downgrade,spec=-3.36,log2=0.05); Oprm1(downgrade,spec=-6.77,log2=0.19)</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>Npy2r | clinical/research: BIIE-0246 (research antagonist) | indication: food intake; anxiety (preclinical) || Hcrtr1 | clinical/research: SB-334867 (research selective antagonist) | indication: addiction; anxiety (preclinical) || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Drd2 | FDA: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect) | clinical/research: many | indication: schizophrenia; bipolar; Parkinson disease; hyperprolactinemia || Htr1a | FDA: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone | clinical/research: NLX-101 (depression) | indication: generalized anxiety; major depression || Htr1b | FDA: Sumatriptan; Rizatriptan; Zolmitriptan; Eletriptan; Naratriptan; Frovatriptan; Almotriptan | indication: migraine (acute attack) || Oprm1 | FDA: Morphine; Oxycodone; Hydrocodone; Methadone; Buprenorphine; Fentanyl; Tramadol; Naloxone (antag); Naltrexone (antag); Loperamide | clinical/research: PZM21 (biased agonist research) | indication: chronic pain; opioid use disorder; analgesia</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr"/>
+      <c r="Q54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55" ht="110" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
           <t>DG granule cell</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>037 DG Glut</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>80255</v>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>GOOD: Allen ROI = HIP (hippocampus); subclass anchors split CA1 (016 CA1-ProS), CA2 (025 CA2-FC-IG), CA3 (017 CA3), and DG (037 DG) cleanly.</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>C1ql2, Calb1, Dock10, Dsp, Prox1, Slc17a7</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>Cnih3, Rgs14, Wfs1</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>Adcyap1r1, Cnr1, Drd2, Gabbr1, Gabbr2, Grm1, Grm5, Htr1a, Htr2c</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr"/>
-      <c r="K54" s="3" t="inlineStr">
+      <c r="J55" s="3" t="inlineStr"/>
+      <c r="K55" s="3" t="inlineStr">
         <is>
           <t>Grm1[paper+allen_broadly_detectable, spec=-0.06, log2=8.43, pct=93%; drugs: research_only_or_none]; Grm5[paper+allen_broadly_detectable, spec=-0.98, log2=10.17, pct=99%; drugs: research_only_or_none]; Adcyap1r1[paper_only_allen_downgrade, spec=-2.92, log2=3.40, pct=47%; drugs: research_only_or_none]; Cnr1[paper_only_allen_downgrade, spec=-11.77, log2=0.65, pct=10%; drugs: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action)]; Drd2[paper_only_allen_downgrade, spec=-1.50, log2=0.00, pct=0%; drugs: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect)]; Gabbr1[paper_only_allen_downgrade, spec=-2.51, log2=6.64, pct=82%; drugs: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem)]; Gabbr2[paper_only_allen_downgrade, spec=-2.13, log2=7.76, pct=89%; drugs: Baclofen (heterodimer with Gabbr1); Sodium oxybate]; Htr1a[paper_only_allen_downgrade, spec=-2.62, log2=0.71, pct=11%; drugs: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone]; Htr2c[paper_only_allen_downgrade, spec=-11.79, log2=0.14, pct=2%; drugs: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk)]</t>
         </is>
       </c>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="L55" s="3" t="inlineStr">
         <is>
           <t>paper+broadly_detectable: Grm1, Grm5 | paper_only: Adcyap1r1(downgrade,spec=-2.92,log2=3.40); Cnr1(downgrade,spec=-11.77,log2=0.65); Drd2(downgrade,spec=-1.50,log2=0.00); Gabbr1(downgrade,spec=-2.51,log2=6.64); Gabbr2(downgrade,spec=-2.13,log2=7.76); Htr1a(downgrade,spec=-2.62,log2=0.71); Htr2c(downgrade,spec=-11.79,log2=0.14)</t>
         </is>
       </c>
-      <c r="M54" s="3" t="n">
+      <c r="M55" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N54" s="3" t="n">
+      <c r="N55" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O54" s="3" t="inlineStr">
+      <c r="O55" s="3" t="inlineStr">
         <is>
           <t>Grm1 | clinical/research: research mGluR1 negative allosteric modulators (CFMTI) | indication: chronic pain; cerebellar ataxia (preclinical) || Grm5 | clinical/research: Mavoglurant; Basimglurant; ADX-48621 (mostly failed Fragile X trials); Fenobam | indication: Fragile X syndrome (failed); anxiety; addiction (research) || Adcyap1r1 | clinical/research: Maxadilan; Atrasentan-related (research) | indication: migraine research || Cnr1 | FDA: Dronabinol (Marinol; THC); Nabilone; Cannabidiol (CBD; partial action) | clinical/research: Rimonabant (withdrawn obesity drug); JZP-150 | indication: appetite stimulation (cancer/AIDS); chemotherapy nausea; epilepsy (CBD) || Drd2 | FDA: Risperidone; Olanzapine; Aripiprazole; Quetiapine; Clozapine; Haloperidol; Paliperidone; Lurasidone; Bromocriptine; Cabergoline; Pramipexole; Ropinirole; Levodopa+Carbidopa (indirect) | clinical/research: many | indication: schizophrenia; bipolar; Parkinson disease; hyperprolactinemia || Gabbr1 | FDA: Baclofen (Lioresal); Arbaclofen Placarbil; Sodium oxybate (Xyrem) | clinical/research: Lesogaberan | indication: spasticity (multiple sclerosis; spinal cord injury); narcolepsy (Xyrem); alcohol use disorder (off-label) || Gabbr2 | FDA: Baclofen (heterodimer with Gabbr1); Sodium oxybate | clinical/research: (see Gabbr1) | indication: (see Gabbr1) || Htr1a | FDA: Buspirone; Vilazodone; Vortioxetine (partial); Tandospirone (Japan); Gepirone | clinical/research: NLX-101 (depression) | indication: generalized anxiety; major depression || Htr2c | FDA: Lorcaserin (Belviq) WITHDRAWN 2020 (cancer risk) | clinical/research: CT-7080; agomelatine (mixed) | indication: (historic obesity); current research for addiction</t>
         </is>
       </c>
-      <c r="P54" s="3" t="inlineStr"/>
-      <c r="Q54" s="3" t="inlineStr">
+      <c r="P55" s="3" t="inlineStr"/>
+      <c r="Q55" s="3" t="inlineStr">
         <is>
           <t>no cell-type-specific GPCR; relying on 2 broadly_expressed_detectable candidates</t>
         </is>
@@ -17280,54 +17458,54 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>2282 ARH-PVp Tbx3 Glut_3</t>
+          <t>2554 PH-SUM Foxa1 Glut_5</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>126 ARH-PVp Tbx3 Glut</t>
+          <t>141 PH-SUM Foxa1 Glut</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>0556 ARH-PVp Tbx3 Glut_3</t>
+          <t>0626 PH-SUM Foxa1 Glut_5</t>
         </is>
       </c>
       <c r="G17" s="14" t="n">
-        <v>663</v>
+        <v>146</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J17" s="14" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K17" s="14" t="n">
-        <v>8.527699999999999</v>
+        <v>5.4559</v>
       </c>
       <c r="L17" s="14" t="n">
-        <v>1.1941</v>
+        <v>1.0365</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>96.61</v>
+        <v>67.55</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>18.55</v>
+        <v>16.96</v>
       </c>
       <c r="O17" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P17" s="14" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q17" s="14" t="n">
-        <v>7.8335</v>
+        <v>4.7945</v>
       </c>
       <c r="R17" s="14" t="n">
-        <v>6.5895</v>
+        <v>4.8007</v>
       </c>
       <c r="S17" s="14" t="n">
         <v>1</v>
@@ -17351,54 +17529,54 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>2281 ARH-PVp Tbx3 Glut_3</t>
+          <t>2496 PH Pitx2 Glut_2</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>126 ARH-PVp Tbx3 Glut</t>
+          <t>138 PH Pitx2 Glut</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>0556 ARH-PVp Tbx3 Glut_3</t>
+          <t>0611 PH Pitx2 Glut_2</t>
         </is>
       </c>
       <c r="G18" s="14" t="n">
-        <v>698</v>
+        <v>106</v>
       </c>
       <c r="H18" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I18" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>7.6839</v>
+        <v>4.9206</v>
       </c>
       <c r="L18" s="14" t="n">
-        <v>1.493</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="M18" s="14" t="n">
-        <v>89.7</v>
+        <v>61.67</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>22.06</v>
+        <v>8.44</v>
       </c>
       <c r="O18" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P18" s="14" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q18" s="14" t="n">
-        <v>6.6909</v>
+        <v>4.7911</v>
       </c>
       <c r="R18" s="14" t="n">
-        <v>4.8236</v>
+        <v>8.1402</v>
       </c>
       <c r="S18" s="14" t="n">
         <v>2</v>
@@ -17422,54 +17600,54 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>2487 PH Pitx2 Glut_2</t>
+          <t>2540 PH-SUM Foxa1 Glut_2</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>138 PH Pitx2 Glut</t>
+          <t>141 PH-SUM Foxa1 Glut</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>0611 PH Pitx2 Glut_2</t>
+          <t>0623 PH-SUM Foxa1 Glut_2</t>
         </is>
       </c>
       <c r="G19" s="14" t="n">
-        <v>38</v>
+        <v>171</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J19" s="14" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K19" s="14" t="n">
-        <v>5.5814</v>
+        <v>5.1448</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>0.1934</v>
+        <v>0.9224</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>68.13</v>
+        <v>66.3</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>3.95</v>
+        <v>14.55</v>
       </c>
       <c r="O19" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P19" s="14" t="n">
-        <v>0.778</v>
+        <v>0.75</v>
       </c>
       <c r="Q19" s="14" t="n">
-        <v>5.7769</v>
+        <v>4.5974</v>
       </c>
       <c r="R19" s="14" t="n">
-        <v>19.0244</v>
+        <v>5.0322</v>
       </c>
       <c r="S19" s="14" t="n">
         <v>3</v>
@@ -17493,7 +17671,7 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>2562 PH-SUM Foxa1 Glut_6</t>
+          <t>2545 PH-SUM Foxa1 Glut_3</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
@@ -17503,44 +17681,44 @@
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>0627 PH-SUM Foxa1 Glut_6</t>
+          <t>0624 PH-SUM Foxa1 Glut_3</t>
         </is>
       </c>
       <c r="G20" s="14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H20" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>5.6269</v>
+        <v>4.9733</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>0.3047</v>
+        <v>0.7302</v>
       </c>
       <c r="M20" s="14" t="n">
-        <v>70.27</v>
+        <v>63.59</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>5.63</v>
+        <v>12.79</v>
       </c>
       <c r="O20" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P20" s="14" t="n">
-        <v>0.778</v>
+        <v>0.625</v>
       </c>
       <c r="Q20" s="14" t="n">
-        <v>5.7111</v>
+        <v>4.5556</v>
       </c>
       <c r="R20" s="14" t="n">
-        <v>13.9043</v>
+        <v>5.9906</v>
       </c>
       <c r="S20" s="14" t="n">
         <v>4</v>
@@ -17564,54 +17742,54 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>2489 PH Pitx2 Glut_2</t>
+          <t>2440 STN-PSTN Pitx2 Glut_2</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>138 PH Pitx2 Glut</t>
+          <t>135 STN-PSTN Pitx2 Glut</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>0611 PH Pitx2 Glut_2</t>
+          <t>0599 STN-PSTN Pitx2 Glut_2</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
-        <v>142</v>
+        <v>24</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J21" s="14" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K21" s="14" t="n">
-        <v>5.6068</v>
+        <v>4.8827</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>0.4301</v>
+        <v>0.6685</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>66.51000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>7.39</v>
+        <v>12.75</v>
       </c>
       <c r="O21" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P21" s="14" t="n">
-        <v>0.667</v>
+        <v>0.625</v>
       </c>
       <c r="Q21" s="14" t="n">
-        <v>5.51</v>
+        <v>4.5267</v>
       </c>
       <c r="R21" s="14" t="n">
-        <v>10.5766</v>
+        <v>6.3538</v>
       </c>
       <c r="S21" s="14" t="n">
         <v>5</v>
@@ -17635,54 +17813,54 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>2568 MM-ant Foxb1 Glut_1</t>
+          <t>1723 ZI Pax6 Gaba_1</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>143 MM-ant Foxb1 Glut</t>
+          <t>101 ZI Pax6 Gaba</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>0629 MM-ant Foxb1 Glut_1</t>
+          <t>0459 ZI Pax6 Gaba_1</t>
         </is>
       </c>
       <c r="G22" s="11" t="n">
-        <v>2271</v>
+        <v>38</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>4.8759</v>
+        <v>1.8231</v>
       </c>
       <c r="L22" s="11" t="n">
-        <v>2.2519</v>
+        <v>0.1077</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>58.42</v>
+        <v>27.54</v>
       </c>
       <c r="N22" s="11" t="n">
-        <v>25.9</v>
+        <v>2.11</v>
       </c>
       <c r="O22" s="11" t="n">
         <v>5</v>
       </c>
       <c r="P22" s="11" t="n">
-        <v>0.625</v>
+        <v>0.333</v>
       </c>
       <c r="Q22" s="11" t="n">
-        <v>2.9365</v>
+        <v>1.882</v>
       </c>
       <c r="R22" s="11" t="n">
-        <v>2.0732</v>
+        <v>8.776199999999999</v>
       </c>
       <c r="S22" s="11" t="n">
         <v>1</v>
@@ -17706,54 +17884,54 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>2574 MM Foxb1 Glut_2</t>
+          <t>1287 MEA-BST Lhx6 Nfib Gaba_1</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>144 MM Foxb1 Glut</t>
+          <t>076 MEA-BST Lhx6 Nfib Gaba</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>0631 MM Foxb1 Glut_2</t>
+          <t>0357 MEA-BST Lhx6 Nfib Gaba_1</t>
         </is>
       </c>
       <c r="G23" s="11" t="n">
-        <v>3759</v>
+        <v>18</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J23" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>1.9209</v>
+      </c>
+      <c r="L23" s="11" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="M23" s="11" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="O23" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="K23" s="11" t="n">
-        <v>4.9588</v>
-      </c>
-      <c r="L23" s="11" t="n">
-        <v>2.3859</v>
-      </c>
-      <c r="M23" s="11" t="n">
-        <v>60.63</v>
-      </c>
-      <c r="N23" s="11" t="n">
-        <v>28.86</v>
-      </c>
-      <c r="O23" s="11" t="n">
-        <v>5</v>
-      </c>
       <c r="P23" s="11" t="n">
-        <v>0.625</v>
+        <v>0.267</v>
       </c>
       <c r="Q23" s="11" t="n">
-        <v>2.8853</v>
+        <v>1.8662</v>
       </c>
       <c r="R23" s="11" t="n">
-        <v>1.9947</v>
+        <v>6.669</v>
       </c>
       <c r="S23" s="11" t="n">
         <v>2</v>
@@ -17777,54 +17955,54 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>2569 MM-ant Foxb1 Glut_1</t>
+          <t>1876 PVpo-VMPO-MPN Hmx2 Gaba_1</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>143 MM-ant Foxb1 Glut</t>
+          <t>106 PVpo-VMPO-MPN Hmx2 Gaba</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>0629 MM-ant Foxb1 Glut_1</t>
+          <t>0482 PVpo-VMPO-MPN Hmx2 Gaba_1</t>
         </is>
       </c>
       <c r="G24" s="11" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>4.928</v>
+        <v>1.6897</v>
       </c>
       <c r="L24" s="11" t="n">
-        <v>2.3717</v>
+        <v>0.0704</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>59.44</v>
+        <v>23.28</v>
       </c>
       <c r="N24" s="11" t="n">
-        <v>25.9</v>
+        <v>1.31</v>
       </c>
       <c r="O24" s="11" t="n">
         <v>5</v>
       </c>
       <c r="P24" s="11" t="n">
-        <v>0.625</v>
+        <v>0.333</v>
       </c>
       <c r="Q24" s="11" t="n">
-        <v>2.8687</v>
+        <v>1.7859</v>
       </c>
       <c r="R24" s="11" t="n">
-        <v>1.9937</v>
+        <v>9.913399999999999</v>
       </c>
       <c r="S24" s="11" t="n">
         <v>3</v>
@@ -17848,54 +18026,54 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>2565 MM-ant Foxb1 Glut_1</t>
+          <t>1955 DMH Hmx2 Gaba_5</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>143 MM-ant Foxb1 Glut</t>
+          <t>107 DMH Hmx2 Gaba</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>0629 MM-ant Foxb1 Glut_1</t>
+          <t>0491 DMH Hmx2 Gaba_5</t>
         </is>
       </c>
       <c r="G25" s="11" t="n">
-        <v>846</v>
+        <v>190</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>4.8032</v>
+        <v>1.7859</v>
       </c>
       <c r="L25" s="11" t="n">
-        <v>2.2876</v>
+        <v>0.1497</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>59.06</v>
+        <v>22.21</v>
       </c>
       <c r="N25" s="11" t="n">
-        <v>26.15</v>
+        <v>2.84</v>
       </c>
       <c r="O25" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P25" s="11" t="n">
-        <v>0.625</v>
+        <v>0.2</v>
       </c>
       <c r="Q25" s="11" t="n">
-        <v>2.8281</v>
+        <v>1.7362</v>
       </c>
       <c r="R25" s="11" t="n">
-        <v>2.0117</v>
+        <v>7.1518</v>
       </c>
       <c r="S25" s="11" t="n">
         <v>4</v>
@@ -17919,54 +18097,54 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>2572 MM Foxb1 Glut_1</t>
+          <t>1870 PVpo-VMPO-MPN Hmx2 Gaba_1</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>144 MM Foxb1 Glut</t>
+          <t>106 PVpo-VMPO-MPN Hmx2 Gaba</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>0630 MM Foxb1 Glut_1</t>
+          <t>0482 PVpo-VMPO-MPN Hmx2 Gaba_1</t>
         </is>
       </c>
       <c r="G26" s="11" t="n">
-        <v>547</v>
+        <v>94</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>4.9711</v>
+        <v>1.7218</v>
       </c>
       <c r="L26" s="11" t="n">
-        <v>2.4648</v>
+        <v>0.168</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>60.47</v>
+        <v>22.91</v>
       </c>
       <c r="N26" s="11" t="n">
-        <v>26.69</v>
+        <v>3.19</v>
       </c>
       <c r="O26" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P26" s="11" t="n">
-        <v>0.625</v>
+        <v>0.2</v>
       </c>
       <c r="Q26" s="11" t="n">
-        <v>2.8188</v>
+        <v>1.6538</v>
       </c>
       <c r="R26" s="11" t="n">
-        <v>1.9382</v>
+        <v>6.4244</v>
       </c>
       <c r="S26" s="11" t="n">
         <v>5</v>
@@ -17990,54 +18168,54 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>2660 TH Prkcd Grin2c Glut_6</t>
+          <t>2701 RE-Xi Nox4 Glut_3</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>151 TH Prkcd Grin2c Glut</t>
+          <t>152 RE-Xi Nox4 Glut</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>0659 TH Prkcd Grin2c Glut_6</t>
+          <t>0670 RE-Xi Nox4 Glut_3</t>
         </is>
       </c>
       <c r="G27" s="14" t="n">
-        <v>2407</v>
+        <v>58</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="K27" s="14" t="n">
+        <v>7.4347</v>
+      </c>
+      <c r="L27" s="14" t="n">
+        <v>0.8298</v>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>88.36</v>
+      </c>
+      <c r="N27" s="14" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="O27" s="14" t="n">
         <v>4</v>
-      </c>
-      <c r="K27" s="14" t="n">
-        <v>9.663500000000001</v>
-      </c>
-      <c r="L27" s="14" t="n">
-        <v>0.1871</v>
-      </c>
-      <c r="M27" s="14" t="n">
-        <v>98.56</v>
-      </c>
-      <c r="N27" s="14" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="O27" s="14" t="n">
-        <v>5</v>
       </c>
       <c r="P27" s="14" t="n">
         <v>1</v>
       </c>
       <c r="Q27" s="14" t="n">
-        <v>9.9764</v>
+        <v>7.105</v>
       </c>
       <c r="R27" s="14" t="n">
-        <v>33.6548</v>
+        <v>7.9964</v>
       </c>
       <c r="S27" s="14" t="n">
         <v>1</v>
@@ -18061,54 +18239,54 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>2654 TH Prkcd Grin2c Glut_4</t>
+          <t>2702 RE-Xi Nox4 Glut_3</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>151 TH Prkcd Grin2c Glut</t>
+          <t>152 RE-Xi Nox4 Glut</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>0657 TH Prkcd Grin2c Glut_4</t>
+          <t>0670 RE-Xi Nox4 Glut_3</t>
         </is>
       </c>
       <c r="G28" s="14" t="n">
-        <v>724</v>
+        <v>58</v>
       </c>
       <c r="H28" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J28" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="K28" s="14" t="n">
+        <v>7.463</v>
+      </c>
+      <c r="L28" s="14" t="n">
+        <v>1.2437</v>
+      </c>
+      <c r="M28" s="14" t="n">
+        <v>89.66</v>
+      </c>
+      <c r="N28" s="14" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="O28" s="14" t="n">
         <v>4</v>
-      </c>
-      <c r="K28" s="14" t="n">
-        <v>9.7659</v>
-      </c>
-      <c r="L28" s="14" t="n">
-        <v>0.3246</v>
-      </c>
-      <c r="M28" s="14" t="n">
-        <v>98.06999999999999</v>
-      </c>
-      <c r="N28" s="14" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="O28" s="14" t="n">
-        <v>5</v>
       </c>
       <c r="P28" s="14" t="n">
         <v>1</v>
       </c>
       <c r="Q28" s="14" t="n">
-        <v>9.9413</v>
+        <v>6.7193</v>
       </c>
       <c r="R28" s="14" t="n">
-        <v>23.0002</v>
+        <v>5.5542</v>
       </c>
       <c r="S28" s="14" t="n">
         <v>2</v>
@@ -18132,54 +18310,54 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>2707 MG-POL-SGN Nts Glut_2</t>
+          <t>2703 RE-Xi Nox4 Glut_4</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>153 MG-POL-SGN Nts Glut</t>
+          <t>152 RE-Xi Nox4 Glut</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>0673 MG-POL-SGN Nts Glut_2</t>
+          <t>0671 RE-Xi Nox4 Glut_4</t>
         </is>
       </c>
       <c r="G29" s="14" t="n">
-        <v>48</v>
+        <v>152</v>
       </c>
       <c r="H29" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J29" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>6.6685</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>0.6163</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="N29" s="14" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="O29" s="14" t="n">
         <v>4</v>
-      </c>
-      <c r="K29" s="14" t="n">
-        <v>9.507899999999999</v>
-      </c>
-      <c r="L29" s="14" t="n">
-        <v>0.1914</v>
-      </c>
-      <c r="M29" s="14" t="n">
-        <v>97.92</v>
-      </c>
-      <c r="N29" s="14" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="O29" s="14" t="n">
-        <v>5</v>
       </c>
       <c r="P29" s="14" t="n">
         <v>1</v>
       </c>
       <c r="Q29" s="14" t="n">
-        <v>9.8164</v>
+        <v>6.5522</v>
       </c>
       <c r="R29" s="14" t="n">
-        <v>32.6244</v>
+        <v>9.31</v>
       </c>
       <c r="S29" s="14" t="n">
         <v>3</v>
@@ -18203,54 +18381,54 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>2667 TH Prkcd Grin2c Glut_7</t>
+          <t>2691 RE-Xi Nox4 Glut_1</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>151 TH Prkcd Grin2c Glut</t>
+          <t>152 RE-Xi Nox4 Glut</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>0660 TH Prkcd Grin2c Glut_7</t>
+          <t>0668 RE-Xi Nox4 Glut_1</t>
         </is>
       </c>
       <c r="G30" s="14" t="n">
-        <v>767</v>
+        <v>294</v>
       </c>
       <c r="H30" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>6.9519</v>
+      </c>
+      <c r="L30" s="14" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="M30" s="14" t="n">
+        <v>80.95</v>
+      </c>
+      <c r="N30" s="14" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="O30" s="14" t="n">
         <v>4</v>
-      </c>
-      <c r="K30" s="14" t="n">
-        <v>9.4495</v>
-      </c>
-      <c r="L30" s="14" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="M30" s="14" t="n">
-        <v>96.77</v>
-      </c>
-      <c r="N30" s="14" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="O30" s="14" t="n">
-        <v>5</v>
       </c>
       <c r="P30" s="14" t="n">
         <v>1</v>
       </c>
       <c r="Q30" s="14" t="n">
-        <v>9.7834</v>
+        <v>6.4308</v>
       </c>
       <c r="R30" s="14" t="n">
-        <v>35.5195</v>
+        <v>6.2012</v>
       </c>
       <c r="S30" s="14" t="n">
         <v>4</v>
@@ -18274,54 +18452,54 @@
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>2705 MG-POL-SGN Nts Glut_1</t>
+          <t>2698 RE-Xi Nox4 Glut_3</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>153 MG-POL-SGN Nts Glut</t>
+          <t>152 RE-Xi Nox4 Glut</t>
         </is>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>0672 MG-POL-SGN Nts Glut_1</t>
+          <t>0670 RE-Xi Nox4 Glut_3</t>
         </is>
       </c>
       <c r="G31" s="14" t="n">
-        <v>815</v>
+        <v>793</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J31" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>7.6688</v>
+      </c>
+      <c r="L31" s="14" t="n">
+        <v>1.8076</v>
+      </c>
+      <c r="M31" s="14" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="N31" s="14" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="O31" s="14" t="n">
         <v>4</v>
-      </c>
-      <c r="K31" s="14" t="n">
-        <v>9.5785</v>
-      </c>
-      <c r="L31" s="14" t="n">
-        <v>0.3002</v>
-      </c>
-      <c r="M31" s="14" t="n">
-        <v>97.15000000000001</v>
-      </c>
-      <c r="N31" s="14" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="O31" s="14" t="n">
-        <v>5</v>
       </c>
       <c r="P31" s="14" t="n">
         <v>1</v>
       </c>
       <c r="Q31" s="14" t="n">
-        <v>9.7783</v>
+        <v>6.3613</v>
       </c>
       <c r="R31" s="14" t="n">
-        <v>23.9346</v>
+        <v>4.0202</v>
       </c>
       <c r="S31" s="14" t="n">
         <v>5</v>
